--- a/catalogue_astronomie.xlsx
+++ b/catalogue_astronomie.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Derfence\Documents\Gatcha\client-android-standalone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0618CF5-FAFB-42B7-84BC-EDF44201BAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D430C3D1-E14E-42C9-A4BC-18A8404374E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogue" sheetId="1" r:id="rId1"/>
-    <sheet name="Donnees" sheetId="2" r:id="rId2"/>
-    <sheet name="Resultats" sheetId="3" r:id="rId3"/>
+    <sheet name="Equipements" sheetId="4" r:id="rId2"/>
+    <sheet name="Donnees" sheetId="2" r:id="rId3"/>
+    <sheet name="Resultats" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="795">
   <si>
     <t>rowType</t>
   </si>
@@ -2286,6 +2287,162 @@
   </si>
   <si>
     <t>percentEpicPerDay</t>
+  </si>
+  <si>
+    <t>equipmentCardId</t>
+  </si>
+  <si>
+    <t>equipmentType</t>
+  </si>
+  <si>
+    <t>displayName</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>packsAffected</t>
+  </si>
+  <si>
+    <t>bonusValue</t>
+  </si>
+  <si>
+    <t>bonusUnit</t>
+  </si>
+  <si>
+    <t>dropWeight</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>observatory-beginner</t>
+  </si>
+  <si>
+    <t>observatory</t>
+  </si>
+  <si>
+    <t>Observatoire debutant</t>
+  </si>
+  <si>
+    <t>equipment_observatory_1</t>
+  </si>
+  <si>
+    <t>rechargeMultiplier</t>
+  </si>
+  <si>
+    <t>Accelere legerement la recharge des packs.</t>
+  </si>
+  <si>
+    <t>observatory-advanced</t>
+  </si>
+  <si>
+    <t>Observatoire expert</t>
+  </si>
+  <si>
+    <t>equipment_observatory_2</t>
+  </si>
+  <si>
+    <t>Maintient une recharge plus rapide pendant plusieurs packs.</t>
+  </si>
+  <si>
+    <t>observatory-master</t>
+  </si>
+  <si>
+    <t>Observatoire legendaire</t>
+  </si>
+  <si>
+    <t>equipment_observatory_3</t>
+  </si>
+  <si>
+    <t>Double la vitesse de recharge pour une courte serie de packs.</t>
+  </si>
+  <si>
+    <t>telescope-beginner</t>
+  </si>
+  <si>
+    <t>telescope</t>
+  </si>
+  <si>
+    <t>Telescope debutant</t>
+  </si>
+  <si>
+    <t>equipment_telescope_1</t>
+  </si>
+  <si>
+    <t>holographicPercent</t>
+  </si>
+  <si>
+    <t>Ajoute une petite chance holographique supplementaire.</t>
+  </si>
+  <si>
+    <t>telescope-advanced</t>
+  </si>
+  <si>
+    <t>Telescope expert</t>
+  </si>
+  <si>
+    <t>equipment_telescope_2</t>
+  </si>
+  <si>
+    <t>Renforce sensiblement l'apparition des cartes holographiques.</t>
+  </si>
+  <si>
+    <t>telescope-master</t>
+  </si>
+  <si>
+    <t>Telescope legendaire</t>
+  </si>
+  <si>
+    <t>equipment_telescope_3</t>
+  </si>
+  <si>
+    <t>Offre une forte poussee holographique sur les prochains packs.</t>
+  </si>
+  <si>
+    <t>mount-beginner</t>
+  </si>
+  <si>
+    <t>mount</t>
+  </si>
+  <si>
+    <t>Monture debutante</t>
+  </si>
+  <si>
+    <t>equipment_mount_1</t>
+  </si>
+  <si>
+    <t>rarityBoost</t>
+  </si>
+  <si>
+    <t>Ajoute une chance moderee de promouvoir une carte d'un palier.</t>
+  </si>
+  <si>
+    <t>mount-advanced</t>
+  </si>
+  <si>
+    <t>Monture experte</t>
+  </si>
+  <si>
+    <t>equipment_mount_2</t>
+  </si>
+  <si>
+    <t>Augmente davantage la probabilite de gagner en rarete.</t>
+  </si>
+  <si>
+    <t>mount-master</t>
+  </si>
+  <si>
+    <t>Monture legendaire</t>
+  </si>
+  <si>
+    <t>equipment_mount_3</t>
+  </si>
+  <si>
+    <t>Pousse les tirages vers des cartes plus rares pendant plusieurs packs.</t>
+  </si>
+  <si>
+    <t>EquipmentChancePercent</t>
   </si>
 </sst>
 </file>
@@ -9488,8 +9645,350 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D42EB6-033C-42BF-9E1D-DED894C3BFBF}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="64.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B1" t="s">
+        <v>744</v>
+      </c>
+      <c r="C1" t="s">
+        <v>745</v>
+      </c>
+      <c r="D1" t="s">
+        <v>746</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>747</v>
+      </c>
+      <c r="G1" t="s">
+        <v>748</v>
+      </c>
+      <c r="H1" t="s">
+        <v>749</v>
+      </c>
+      <c r="I1" t="s">
+        <v>750</v>
+      </c>
+      <c r="J1" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>752</v>
+      </c>
+      <c r="B2" t="s">
+        <v>753</v>
+      </c>
+      <c r="C2" t="s">
+        <v>754</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>755</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1.25</v>
+      </c>
+      <c r="H2" t="s">
+        <v>756</v>
+      </c>
+      <c r="I2">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>758</v>
+      </c>
+      <c r="B3" t="s">
+        <v>753</v>
+      </c>
+      <c r="C3" t="s">
+        <v>759</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>760</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1.5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>756</v>
+      </c>
+      <c r="I3">
+        <v>10</v>
+      </c>
+      <c r="J3" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>762</v>
+      </c>
+      <c r="B4" t="s">
+        <v>753</v>
+      </c>
+      <c r="C4" t="s">
+        <v>763</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>764</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>756</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="J4" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>766</v>
+      </c>
+      <c r="B5" t="s">
+        <v>767</v>
+      </c>
+      <c r="C5" t="s">
+        <v>768</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>769</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5" t="s">
+        <v>770</v>
+      </c>
+      <c r="I5">
+        <v>16</v>
+      </c>
+      <c r="J5" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>772</v>
+      </c>
+      <c r="B6" t="s">
+        <v>767</v>
+      </c>
+      <c r="C6" t="s">
+        <v>773</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>774</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6" t="s">
+        <v>770</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>776</v>
+      </c>
+      <c r="B7" t="s">
+        <v>767</v>
+      </c>
+      <c r="C7" t="s">
+        <v>777</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>778</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7" t="s">
+        <v>770</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>780</v>
+      </c>
+      <c r="B8" t="s">
+        <v>781</v>
+      </c>
+      <c r="C8" t="s">
+        <v>782</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>783</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8" t="s">
+        <v>784</v>
+      </c>
+      <c r="I8">
+        <v>16</v>
+      </c>
+      <c r="J8" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>786</v>
+      </c>
+      <c r="B9" t="s">
+        <v>781</v>
+      </c>
+      <c r="C9" t="s">
+        <v>787</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>788</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s">
+        <v>784</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+      <c r="J9" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>790</v>
+      </c>
+      <c r="B10" t="s">
+        <v>781</v>
+      </c>
+      <c r="C10" t="s">
+        <v>791</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>792</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>784</v>
+      </c>
+      <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="J10" t="s">
+        <v>793</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
@@ -9677,12 +10176,20 @@
         <v>10</v>
       </c>
     </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>794</v>
+      </c>
+      <c r="B19" s="2">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/catalogue_astronomie.xlsx
+++ b/catalogue_astronomie.xlsx
@@ -9119,7 +9119,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dobson</t>
+          <t xml:space="preserve">Newton</t>
         </is>
       </c>
       <c r="D5">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dobson</t>
+          <t xml:space="preserve">Newton</t>
         </is>
       </c>
       <c r="D79">

--- a/catalogue_astronomie.xlsx
+++ b/catalogue_astronomie.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Derfence\Documents\Gatcha\client-android-standalone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40548AA9-55EC-4388-AF7C-48E4922297FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5625448-81B1-4631-A571-07EEC1ED1E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogue" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="804">
   <si>
     <t>rowType</t>
   </si>
@@ -1998,9 +1998,6 @@
     <t>normalisedDrawWeight</t>
   </si>
   <si>
-    <t>holographicMeanPerDay</t>
-  </si>
-  <si>
     <t>villeMeanPerDay</t>
   </si>
   <si>
@@ -2013,9 +2010,6 @@
     <t>mountainMeanPerDay</t>
   </si>
   <si>
-    <t>unholoMeanPerDay</t>
-  </si>
-  <si>
     <t>commonPerDay</t>
   </si>
   <si>
@@ -2040,30 +2034,18 @@
     <t>commonHoloMeanDays</t>
   </si>
   <si>
-    <t>cityHoloMD</t>
-  </si>
-  <si>
     <t>cityMD</t>
   </si>
   <si>
     <t>periMD</t>
   </si>
   <si>
-    <t>periHoloMD</t>
-  </si>
-  <si>
     <t>campMD</t>
   </si>
   <si>
-    <t>campHoloMD</t>
-  </si>
-  <si>
     <t>montMD</t>
   </si>
   <si>
-    <t>montHoloMD</t>
-  </si>
-  <si>
     <t>cardsPerDay</t>
   </si>
   <si>
@@ -2127,9 +2109,6 @@
     <t>Constellation très célèbre avec la Grande Casserole, idéale pour apprendre le ciel.</t>
   </si>
   <si>
-    <t>percentHoloMeanPerDay</t>
-  </si>
-  <si>
     <t>percentCommonPerDay</t>
   </si>
   <si>
@@ -2205,9 +2184,6 @@
     <t>equipment_telescope_1</t>
   </si>
   <si>
-    <t>holographicPercent</t>
-  </si>
-  <si>
     <t>telescope-advanced</t>
   </si>
   <si>
@@ -2461,6 +2437,39 @@
   </si>
   <si>
     <t>Monture harmonique</t>
+  </si>
+  <si>
+    <t>percentStampMeanPerDay</t>
+  </si>
+  <si>
+    <t>stampMeanPerDay</t>
+  </si>
+  <si>
+    <t>unstampMeanPerDay</t>
+  </si>
+  <si>
+    <t>holoMeanPerDay</t>
+  </si>
+  <si>
+    <t>cityStampMD</t>
+  </si>
+  <si>
+    <t>periStampMD</t>
+  </si>
+  <si>
+    <t>campStampMD</t>
+  </si>
+  <si>
+    <t>montStampMD</t>
+  </si>
+  <si>
+    <t>holoMD</t>
+  </si>
+  <si>
+    <t>holoStampMD</t>
+  </si>
+  <si>
+    <t>holographicSkyPercent</t>
   </si>
 </sst>
 </file>
@@ -2824,12 +2833,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -2944,15 +2953,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2998,7 +2998,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3022,7 +3022,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3669,7 +3668,7 @@
         <v>51</v>
       </c>
       <c r="F3" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="G3" t="s">
         <v>52</v>
@@ -3684,7 +3683,7 @@
         <v>54</v>
       </c>
       <c r="K3" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="L3" t="s">
         <v>55</v>
@@ -3735,7 +3734,7 @@
         <v>64</v>
       </c>
       <c r="AB3" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="AC3" t="s">
         <v>57</v>
@@ -3836,7 +3835,7 @@
         <v>78</v>
       </c>
       <c r="AB4" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="AC4" t="s">
         <v>57</v>
@@ -3937,7 +3936,7 @@
         <v>89</v>
       </c>
       <c r="AB5" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="AC5" t="s">
         <v>57</v>
@@ -3972,7 +3971,7 @@
         <v>93</v>
       </c>
       <c r="F6" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="G6" t="s">
         <v>52</v>
@@ -3987,7 +3986,7 @@
         <v>54</v>
       </c>
       <c r="K6" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="L6" t="s">
         <v>55</v>
@@ -4038,7 +4037,7 @@
         <v>100</v>
       </c>
       <c r="AB6" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="AC6" t="s">
         <v>57</v>
@@ -4073,7 +4072,7 @@
         <v>104</v>
       </c>
       <c r="F7" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="G7" t="s">
         <v>52</v>
@@ -4088,7 +4087,7 @@
         <v>54</v>
       </c>
       <c r="K7" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="L7" t="s">
         <v>106</v>
@@ -4139,7 +4138,7 @@
         <v>111</v>
       </c>
       <c r="AB7" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="AC7" t="s">
         <v>15</v>
@@ -4255,7 +4254,7 @@
         <v>124</v>
       </c>
       <c r="AB8" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="AC8" t="s">
         <v>57</v>
@@ -4290,7 +4289,7 @@
         <v>127</v>
       </c>
       <c r="F9" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="G9" t="s">
         <v>128</v>
@@ -4305,7 +4304,7 @@
         <v>54</v>
       </c>
       <c r="K9" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="L9" t="s">
         <v>130</v>
@@ -4356,7 +4355,7 @@
         <v>138</v>
       </c>
       <c r="AB9" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="AC9" t="s">
         <v>132</v>
@@ -4406,7 +4405,7 @@
         <v>142</v>
       </c>
       <c r="F10" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="G10" t="s">
         <v>52</v>
@@ -4421,7 +4420,7 @@
         <v>54</v>
       </c>
       <c r="K10" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="L10" t="s">
         <v>55</v>
@@ -4472,7 +4471,7 @@
         <v>150</v>
       </c>
       <c r="AB10" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="AC10" t="s">
         <v>57</v>
@@ -4573,7 +4572,7 @@
         <v>162</v>
       </c>
       <c r="AB11" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="AC11" t="s">
         <v>57</v>
@@ -4608,7 +4607,7 @@
         <v>166</v>
       </c>
       <c r="F12" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="G12" t="s">
         <v>52</v>
@@ -4623,7 +4622,7 @@
         <v>54</v>
       </c>
       <c r="K12" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="L12" t="s">
         <v>106</v>
@@ -4674,7 +4673,7 @@
         <v>171</v>
       </c>
       <c r="AB12" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="AC12" t="s">
         <v>15</v>
@@ -4790,7 +4789,7 @@
         <v>185</v>
       </c>
       <c r="AB13" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="AC13" t="s">
         <v>180</v>
@@ -4858,7 +4857,7 @@
         <v>191</v>
       </c>
       <c r="F14" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="G14" t="s">
         <v>128</v>
@@ -4873,7 +4872,7 @@
         <v>54</v>
       </c>
       <c r="K14" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="L14" t="s">
         <v>193</v>
@@ -4924,7 +4923,7 @@
         <v>198</v>
       </c>
       <c r="AB14" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="AC14" t="s">
         <v>132</v>
@@ -5007,7 +5006,7 @@
         <v>204</v>
       </c>
       <c r="AB15" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="AC15" t="s">
         <v>15</v>
@@ -5057,7 +5056,7 @@
         <v>208</v>
       </c>
       <c r="F16" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="G16" t="s">
         <v>52</v>
@@ -5072,7 +5071,7 @@
         <v>54</v>
       </c>
       <c r="K16" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="L16" t="s">
         <v>210</v>
@@ -5123,7 +5122,7 @@
         <v>215</v>
       </c>
       <c r="AB16" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="AC16" t="s">
         <v>180</v>
@@ -5191,7 +5190,7 @@
         <v>222</v>
       </c>
       <c r="F17" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="G17" t="s">
         <v>52</v>
@@ -5206,7 +5205,7 @@
         <v>54</v>
       </c>
       <c r="K17" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="L17" t="s">
         <v>106</v>
@@ -5257,7 +5256,7 @@
         <v>228</v>
       </c>
       <c r="AB17" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="AC17" t="s">
         <v>15</v>
@@ -5307,7 +5306,7 @@
         <v>231</v>
       </c>
       <c r="F18" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="G18" t="s">
         <v>70</v>
@@ -5322,7 +5321,7 @@
         <v>54</v>
       </c>
       <c r="K18" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="L18" t="s">
         <v>233</v>
@@ -5373,7 +5372,7 @@
         <v>237</v>
       </c>
       <c r="AB18" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="AC18" t="s">
         <v>132</v>
@@ -5423,7 +5422,7 @@
         <v>241</v>
       </c>
       <c r="F19" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="G19" t="s">
         <v>128</v>
@@ -5438,7 +5437,7 @@
         <v>54</v>
       </c>
       <c r="K19" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="L19" t="s">
         <v>243</v>
@@ -5489,7 +5488,7 @@
         <v>198</v>
       </c>
       <c r="AB19" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="AC19" t="s">
         <v>132</v>
@@ -5572,7 +5571,7 @@
         <v>255</v>
       </c>
       <c r="AB20" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="AC20" t="s">
         <v>180</v>
@@ -5640,7 +5639,7 @@
         <v>259</v>
       </c>
       <c r="F21" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="G21" t="s">
         <v>70</v>
@@ -5655,7 +5654,7 @@
         <v>54</v>
       </c>
       <c r="K21" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="L21" t="s">
         <v>233</v>
@@ -5706,7 +5705,7 @@
         <v>264</v>
       </c>
       <c r="AB21" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="AC21" t="s">
         <v>132</v>
@@ -5822,7 +5821,7 @@
         <v>272</v>
       </c>
       <c r="AB22" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="AC22" t="s">
         <v>15</v>
@@ -5938,7 +5937,7 @@
         <v>284</v>
       </c>
       <c r="AB23" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="AC23" t="s">
         <v>180</v>
@@ -6072,7 +6071,7 @@
         <v>298</v>
       </c>
       <c r="AB24" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="AC24" t="s">
         <v>180</v>
@@ -6140,7 +6139,7 @@
         <v>304</v>
       </c>
       <c r="F25" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="G25" t="s">
         <v>305</v>
@@ -6155,7 +6154,7 @@
         <v>54</v>
       </c>
       <c r="K25" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="L25" t="s">
         <v>278</v>
@@ -6206,7 +6205,7 @@
         <v>312</v>
       </c>
       <c r="AB25" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="AC25" t="s">
         <v>180</v>
@@ -6274,7 +6273,7 @@
         <v>318</v>
       </c>
       <c r="F26" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="G26" t="s">
         <v>305</v>
@@ -6289,7 +6288,7 @@
         <v>54</v>
       </c>
       <c r="K26" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="L26" t="s">
         <v>278</v>
@@ -6340,7 +6339,7 @@
         <v>325</v>
       </c>
       <c r="AB26" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="AC26" t="s">
         <v>180</v>
@@ -6474,7 +6473,7 @@
         <v>336</v>
       </c>
       <c r="AB27" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="AC27" t="s">
         <v>180</v>
@@ -6557,7 +6556,7 @@
         <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="L28" t="s">
         <v>278</v>
@@ -6608,7 +6607,7 @@
         <v>348</v>
       </c>
       <c r="AB28" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="AC28" t="s">
         <v>180</v>
@@ -6670,7 +6669,7 @@
         <v>353</v>
       </c>
       <c r="F29" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="G29" t="s">
         <v>70</v>
@@ -6685,7 +6684,7 @@
         <v>54</v>
       </c>
       <c r="K29" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="L29" t="s">
         <v>278</v>
@@ -6736,7 +6735,7 @@
         <v>359</v>
       </c>
       <c r="AB29" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="AC29" t="s">
         <v>180</v>
@@ -6804,7 +6803,7 @@
         <v>366</v>
       </c>
       <c r="F30" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="G30" t="s">
         <v>52</v>
@@ -6819,7 +6818,7 @@
         <v>54</v>
       </c>
       <c r="K30" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="L30" t="s">
         <v>278</v>
@@ -6870,7 +6869,7 @@
         <v>372</v>
       </c>
       <c r="AB30" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="AC30" t="s">
         <v>180</v>
@@ -7004,7 +7003,7 @@
         <v>384</v>
       </c>
       <c r="AB31" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="AC31" t="s">
         <v>180</v>
@@ -7138,7 +7137,7 @@
         <v>396</v>
       </c>
       <c r="AB32" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="AC32" t="s">
         <v>180</v>
@@ -7272,7 +7271,7 @@
         <v>405</v>
       </c>
       <c r="AB33" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="AC33" t="s">
         <v>180</v>
@@ -7406,7 +7405,7 @@
         <v>415</v>
       </c>
       <c r="AB34" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="AC34" t="s">
         <v>180</v>
@@ -7540,7 +7539,7 @@
         <v>426</v>
       </c>
       <c r="AB35" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="AC35" t="s">
         <v>180</v>
@@ -7608,7 +7607,7 @@
         <v>430</v>
       </c>
       <c r="F36" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="G36" t="s">
         <v>52</v>
@@ -7623,7 +7622,7 @@
         <v>54</v>
       </c>
       <c r="K36" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="L36" t="s">
         <v>278</v>
@@ -7674,7 +7673,7 @@
         <v>436</v>
       </c>
       <c r="AB36" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="AC36" t="s">
         <v>180</v>
@@ -7742,7 +7741,7 @@
         <v>442</v>
       </c>
       <c r="F37" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="G37" t="s">
         <v>52</v>
@@ -7757,7 +7756,7 @@
         <v>54</v>
       </c>
       <c r="K37" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="L37" t="s">
         <v>278</v>
@@ -7808,7 +7807,7 @@
         <v>447</v>
       </c>
       <c r="AB37" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="AC37" t="s">
         <v>180</v>
@@ -7942,7 +7941,7 @@
         <v>459</v>
       </c>
       <c r="AB38" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="AC38" t="s">
         <v>180</v>
@@ -8010,7 +8009,7 @@
         <v>464</v>
       </c>
       <c r="F39" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="G39" t="s">
         <v>305</v>
@@ -8025,7 +8024,7 @@
         <v>54</v>
       </c>
       <c r="K39" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="L39" t="s">
         <v>278</v>
@@ -8076,7 +8075,7 @@
         <v>469</v>
       </c>
       <c r="AB39" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="AC39" t="s">
         <v>180</v>
@@ -8210,7 +8209,7 @@
         <v>482</v>
       </c>
       <c r="AB40" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="AC40" t="s">
         <v>180</v>
@@ -8293,7 +8292,7 @@
         <v>54</v>
       </c>
       <c r="K41" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="L41" t="s">
         <v>278</v>
@@ -8344,7 +8343,7 @@
         <v>493</v>
       </c>
       <c r="AB41" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="AC41" t="s">
         <v>180</v>
@@ -8478,7 +8477,7 @@
         <v>506</v>
       </c>
       <c r="AB42" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="AC42" t="s">
         <v>180</v>
@@ -8612,7 +8611,7 @@
         <v>520</v>
       </c>
       <c r="AB43" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="AC43" t="s">
         <v>180</v>
@@ -8746,7 +8745,7 @@
         <v>535</v>
       </c>
       <c r="AB44" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="AC44" t="s">
         <v>57</v>
@@ -8847,7 +8846,7 @@
         <v>546</v>
       </c>
       <c r="AB45" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="AC45" t="s">
         <v>57</v>
@@ -8882,7 +8881,7 @@
         <v>549</v>
       </c>
       <c r="F46" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="G46" t="s">
         <v>305</v>
@@ -8897,7 +8896,7 @@
         <v>54</v>
       </c>
       <c r="K46" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="L46" t="s">
         <v>551</v>
@@ -8948,7 +8947,7 @@
         <v>555</v>
       </c>
       <c r="AB46" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="AC46" t="s">
         <v>180</v>
@@ -9082,7 +9081,7 @@
         <v>564</v>
       </c>
       <c r="AB47" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="AC47" t="s">
         <v>15</v>
@@ -9132,7 +9131,7 @@
         <v>568</v>
       </c>
       <c r="F48" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="G48" t="s">
         <v>52</v>
@@ -9147,7 +9146,7 @@
         <v>54</v>
       </c>
       <c r="K48" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="L48" t="s">
         <v>233</v>
@@ -9198,7 +9197,7 @@
         <v>573</v>
       </c>
       <c r="AB48" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="AC48" t="s">
         <v>132</v>
@@ -9248,7 +9247,7 @@
         <v>574</v>
       </c>
       <c r="F49" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="G49" t="s">
         <v>52</v>
@@ -9263,7 +9262,7 @@
         <v>54</v>
       </c>
       <c r="K49" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="L49" t="s">
         <v>106</v>
@@ -9314,7 +9313,7 @@
         <v>578</v>
       </c>
       <c r="AB49" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="AC49" t="s">
         <v>15</v>
@@ -9364,7 +9363,7 @@
         <v>580</v>
       </c>
       <c r="F50" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="G50" t="s">
         <v>52</v>
@@ -9379,7 +9378,7 @@
         <v>54</v>
       </c>
       <c r="K50" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="L50" t="s">
         <v>55</v>
@@ -9430,7 +9429,7 @@
         <v>588</v>
       </c>
       <c r="AB50" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="AC50" t="s">
         <v>57</v>
@@ -9531,7 +9530,7 @@
         <v>599</v>
       </c>
       <c r="AB51" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="AC51" t="s">
         <v>57</v>
@@ -9632,7 +9631,7 @@
         <v>608</v>
       </c>
       <c r="AB52" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="AC52" t="s">
         <v>15</v>
@@ -9691,58 +9690,58 @@
     <col min="5" max="5" width="23.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="64.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B1" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="C1" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="D1" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="E1" t="s">
         <v>8</v>
       </c>
       <c r="F1" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="G1" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="H1" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="I1" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="J1" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="B2" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="C2" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -9751,30 +9750,30 @@
         <v>1.25</v>
       </c>
       <c r="H2" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="I2">
         <v>16</v>
       </c>
       <c r="J2" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="B3" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="C3" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -9783,30 +9782,30 @@
         <v>1.5</v>
       </c>
       <c r="H3" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="I3">
         <v>10</v>
       </c>
       <c r="J3" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="B4" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="C4" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="F4">
         <v>4</v>
@@ -9815,30 +9814,30 @@
         <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="I4">
         <v>4</v>
       </c>
       <c r="J4" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="B5" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="C5" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -9847,30 +9846,30 @@
         <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>715</v>
+        <v>803</v>
       </c>
       <c r="I5">
         <v>16</v>
       </c>
       <c r="J5" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="B6" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="C6" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -9879,30 +9878,30 @@
         <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>715</v>
+        <v>803</v>
       </c>
       <c r="I6">
         <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="B7" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="C7" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="D7">
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="F7">
         <v>4</v>
@@ -9911,30 +9910,30 @@
         <v>18</v>
       </c>
       <c r="H7" t="s">
-        <v>715</v>
+        <v>803</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="B8" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="C8" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="F8">
         <v>2</v>
@@ -9943,30 +9942,30 @@
         <v>6</v>
       </c>
       <c r="H8" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="I8">
         <v>16</v>
       </c>
       <c r="J8" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="B9" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="C9" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="F9">
         <v>3</v>
@@ -9975,30 +9974,30 @@
         <v>10</v>
       </c>
       <c r="H9" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="I9">
         <v>10</v>
       </c>
       <c r="J9" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="B10" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="C10" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="F10">
         <v>4</v>
@@ -10007,13 +10006,13 @@
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="I10">
         <v>4</v>
       </c>
       <c r="J10" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
     </row>
   </sheetData>
@@ -10048,7 +10047,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -10065,16 +10064,16 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B6" s="1">
-        <f>B3*24/B4-SUM(B7:B9)</f>
-        <v>10</v>
+        <f>B3*24/B4-SUM(B7:B10)</f>
+        <v>9.8571428571428577</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
@@ -10082,7 +10081,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B8" s="2">
         <v>3</v>
@@ -10090,20 +10089,27 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B9" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>796</v>
+      </c>
+      <c r="B10" s="2">
+        <f>1/7</f>
+        <v>0.14285714285714285</v>
+      </c>
       <c r="D10" t="s">
-        <v>689</v>
+        <v>793</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>651</v>
+        <v>795</v>
       </c>
       <c r="B11" s="1">
         <f>D4-B12</f>
@@ -10115,7 +10121,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>646</v>
+        <v>794</v>
       </c>
       <c r="B12" s="1">
         <f>D11*D4/100</f>
@@ -10124,21 +10130,21 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B14" s="1">
         <f>$D$4*E14/100</f>
         <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="E14" s="1">
         <f>100-SUM(E15:E17)</f>
         <v>50</v>
       </c>
       <c r="G14" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="H14" s="1">
         <f>1/(B14*$D$11/100)</f>
@@ -10147,20 +10153,20 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B15" s="1">
         <f t="shared" ref="B15:B17" si="0">$D$4*E15/100</f>
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="E15" s="2">
         <v>30</v>
       </c>
       <c r="G15" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="H15" s="1">
         <f>1/(B15*$D$11/100)</f>
@@ -10169,20 +10175,20 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="E16" s="2">
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="H16" s="1">
         <f>1/(B16*$D$11/100)</f>
@@ -10191,20 +10197,20 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="E17" s="2">
         <v>5</v>
       </c>
       <c r="G17" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H17" s="1">
         <f>1/(B17*$D$11/100)</f>
@@ -10213,7 +10219,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -10226,7 +10232,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:P71"/>
+  <dimension ref="A1:R72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
@@ -10237,15 +10243,16 @@
     <col min="6" max="6" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10295,19 +10302,19 @@
       </c>
       <c r="E3">
         <f>Donnees!B6</f>
-        <v>10</v>
+        <v>9.8571428571428577</v>
       </c>
       <c r="F3">
         <f>E3/SUMPRODUCT($E$3:$E$6)</f>
-        <v>0.5</v>
+        <v>0.49640287769784175</v>
       </c>
       <c r="G3">
-        <f>F3*Donnees!$B$3</f>
-        <v>2.5</v>
+        <f>1/(F3*Donnees!$B$3)</f>
+        <v>0.40289855072463765</v>
       </c>
       <c r="H3">
-        <f>G3*24/Donnees!$B$4</f>
-        <v>10</v>
+        <f>1/(1/G3*24/Donnees!$B$4)</f>
+        <v>0.10072463768115941</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -10329,15 +10336,15 @@
       </c>
       <c r="F4">
         <f t="shared" ref="F4:F6" si="0">E4/SUMPRODUCT($E$3:$E$6)</f>
-        <v>0.3</v>
+        <v>0.30215827338129497</v>
       </c>
       <c r="G4">
-        <f>F4*Donnees!$B$3</f>
-        <v>1.5</v>
+        <f>1/(F4*Donnees!$B$3)</f>
+        <v>0.66190476190476188</v>
       </c>
       <c r="H4">
-        <f>G4*24/Donnees!$B$4</f>
-        <v>6</v>
+        <f>1/(1/G4*24/Donnees!$B$4)</f>
+        <v>0.16547619047619047</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -10359,15 +10366,15 @@
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>0.15</v>
+        <v>0.15107913669064749</v>
       </c>
       <c r="G5">
-        <f>F5*Donnees!$B$3</f>
-        <v>0.75</v>
+        <f>1/(F5*Donnees!$B$3)</f>
+        <v>1.3238095238095238</v>
       </c>
       <c r="H5">
-        <f>G5*24/Donnees!$B$4</f>
-        <v>3</v>
+        <f>1/(1/G5*24/Donnees!$B$4)</f>
+        <v>0.33095238095238094</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -10389,15 +10396,15 @@
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>5.0359712230215826E-2</v>
       </c>
       <c r="G6">
-        <f>F6*Donnees!$B$3</f>
-        <v>0.25</v>
+        <f>1/(F6*Donnees!$B$3)</f>
+        <v>3.9714285714285715</v>
       </c>
       <c r="H6">
-        <f>G6*24/Donnees!$B$4</f>
-        <v>1</v>
+        <f>1/(1/G6*24/Donnees!$B$4)</f>
+        <v>0.99285714285714288</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -10405,29 +10412,29 @@
         <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="C7" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D7" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E7">
-        <f>Donnees!B11</f>
-        <v>18</v>
+        <f>Donnees!B10</f>
+        <v>0.14285714285714285</v>
       </c>
       <c r="F7">
-        <f>E7/SUMPRODUCT(E$7:E$8)</f>
-        <v>0.9</v>
+        <f t="shared" ref="F7" si="1">E7/SUMPRODUCT($E$3:$E$6)</f>
+        <v>7.1942446043165463E-3</v>
       </c>
       <c r="G7">
-        <f>F7*Donnees!$B$3</f>
-        <v>4.5</v>
+        <f>1/(F7*Donnees!$B$3)</f>
+        <v>27.8</v>
       </c>
       <c r="H7">
-        <f>G7*24/Donnees!$B$4</f>
-        <v>18</v>
+        <f>1/(1/G7*24/Donnees!$B$4)</f>
+        <v>6.95</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -10438,351 +10445,333 @@
         <v>631</v>
       </c>
       <c r="C8" t="s">
+        <v>632</v>
+      </c>
+      <c r="D8" t="s">
+        <v>633</v>
+      </c>
+      <c r="E8">
+        <f>Donnees!B11</f>
+        <v>18</v>
+      </c>
+      <c r="F8">
+        <f>E8/SUMPRODUCT(E$8:E$9)</f>
+        <v>0.9</v>
+      </c>
+      <c r="G8">
+        <f>F8*Donnees!$B$3</f>
+        <v>4.5</v>
+      </c>
+      <c r="H8">
+        <f>G8*24/Donnees!$B$4</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>631</v>
+      </c>
+      <c r="C9" t="s">
         <v>634</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>635</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <f>Donnees!B12</f>
         <v>2</v>
       </c>
-      <c r="F8">
-        <f>E8/SUMPRODUCT(E$7:E$8)</f>
+      <c r="F9">
+        <f>E9/SUMPRODUCT(E$8:E$9)</f>
         <v>0.1</v>
       </c>
-      <c r="G8">
-        <f>F8*Donnees!$B$3</f>
+      <c r="G9">
+        <f>F9*Donnees!$B$3</f>
         <v>0.5</v>
       </c>
-      <c r="H8">
-        <f>G8*24/Donnees!$B$4</f>
+      <c r="H9">
+        <f>G9*24/Donnees!$B$4</f>
         <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" t="s">
-        <v>637</v>
-      </c>
-      <c r="C11" t="s">
-        <v>638</v>
-      </c>
-      <c r="D11" t="s">
-        <v>639</v>
-      </c>
-      <c r="E11" t="s">
-        <v>640</v>
-      </c>
-      <c r="F11" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>637</v>
+      </c>
+      <c r="C12" t="s">
+        <v>638</v>
+      </c>
+      <c r="D12" t="s">
+        <v>639</v>
+      </c>
+      <c r="E12" t="s">
+        <v>640</v>
+      </c>
+      <c r="F12" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>52</v>
       </c>
-      <c r="B12" cm="1">
-        <f t="array" ref="B12">SUMPRODUCT(--(Table1[rowType]="card"),--(Table1[rarityLabel]=A12))</f>
+      <c r="B13" cm="1">
+        <f t="array" ref="B13">SUMPRODUCT(--(Table1[rowType]="card"),--(Table1[rarityLabel]=A13))</f>
         <v>25</v>
       </c>
-      <c r="C12" cm="1">
-        <f t="array" ref="C12">SUMPRODUCT((Table1[rowType]="card")*(Table1[rarityLabel]=A12)*(Table1[cardRarityMultiplier]))*Donnees!B14</f>
+      <c r="C13" cm="1">
+        <f t="array" ref="C13">SUMPRODUCT((Table1[rowType]="card")*(Table1[rarityLabel]=A13)*(Table1[cardRarityMultiplier]))*Donnees!B14</f>
         <v>250</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <f>Donnees!E14/100</f>
         <v>0.5</v>
       </c>
-      <c r="E12">
-        <f>D12/B12</f>
+      <c r="E13">
+        <f>D13/B13</f>
         <v>0.02</v>
       </c>
-      <c r="F12">
-        <f>Donnees!$D$4*E12*B12</f>
+      <c r="F13">
+        <f>Donnees!$D$4*E13*B13</f>
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>70</v>
       </c>
-      <c r="B13" cm="1">
-        <f t="array" ref="B13">SUMPRODUCT(--(Table1[rowType]="card"),--(Table1[rarityLabel]=A13))</f>
+      <c r="B14" cm="1">
+        <f t="array" ref="B14">SUMPRODUCT(--(Table1[rowType]="card"),--(Table1[rarityLabel]=A14))</f>
         <v>14</v>
       </c>
-      <c r="C13" cm="1">
-        <f t="array" ref="C13">SUMPRODUCT((Table1[rowType]="card")*(Table1[rarityLabel]=A13)*(Table1[cardRarityMultiplier]))*Donnees!B15</f>
+      <c r="C14" cm="1">
+        <f t="array" ref="C14">SUMPRODUCT((Table1[rowType]="card")*(Table1[rarityLabel]=A14)*(Table1[cardRarityMultiplier]))*Donnees!B15</f>
         <v>84</v>
       </c>
-      <c r="D13">
+      <c r="D14">
         <f>Donnees!E15/100</f>
         <v>0.3</v>
       </c>
-      <c r="E13">
-        <f t="shared" ref="E13:E15" si="1">D13/B13</f>
+      <c r="E14">
+        <f t="shared" ref="E14:E16" si="2">D14/B14</f>
         <v>2.1428571428571429E-2</v>
       </c>
-      <c r="F13">
-        <f>Donnees!$D$4*E13*B13</f>
+      <c r="F14">
+        <f>Donnees!$D$4*E14*B14</f>
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>305</v>
       </c>
-      <c r="B14" cm="1">
-        <f t="array" ref="B14">SUMPRODUCT(--(Table1[rowType]="card"),--(Table1[rarityLabel]=A14))</f>
+      <c r="B15" cm="1">
+        <f t="array" ref="B15">SUMPRODUCT(--(Table1[rowType]="card"),--(Table1[rarityLabel]=A15))</f>
         <v>8</v>
       </c>
-      <c r="C14" cm="1">
-        <f t="array" ref="C14">SUMPRODUCT((Table1[rowType]="card")*(Table1[rarityLabel]=A14)*(Table1[cardRarityMultiplier]))*Donnees!B16</f>
+      <c r="C15" cm="1">
+        <f t="array" ref="C15">SUMPRODUCT((Table1[rowType]="card")*(Table1[rarityLabel]=A15)*(Table1[cardRarityMultiplier]))*Donnees!B16</f>
         <v>24</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <f>Donnees!E16/100</f>
         <v>0.15</v>
       </c>
-      <c r="E14">
-        <f t="shared" si="1"/>
+      <c r="E15">
+        <f t="shared" si="2"/>
         <v>1.8749999999999999E-2</v>
       </c>
-      <c r="F14">
-        <f>Donnees!$D$4*E14*B14</f>
+      <c r="F15">
+        <f>Donnees!$D$4*E15*B15</f>
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>128</v>
       </c>
-      <c r="B15" cm="1">
-        <f t="array" ref="B15">SUMPRODUCT(--(Table1[rowType]="card"),--(Table1[rarityLabel]=A15))</f>
+      <c r="B16" cm="1">
+        <f t="array" ref="B16">SUMPRODUCT(--(Table1[rowType]="card"),--(Table1[rarityLabel]=A16))</f>
         <v>3</v>
       </c>
-      <c r="C15" cm="1">
-        <f t="array" ref="C15">SUMPRODUCT((Table1[rowType]="card")*(Table1[rarityLabel]=A15)*(Table1[cardRarityMultiplier]))*Donnees!B17</f>
+      <c r="C16" cm="1">
+        <f t="array" ref="C16">SUMPRODUCT((Table1[rowType]="card")*(Table1[rarityLabel]=A16)*(Table1[cardRarityMultiplier]))*Donnees!B17</f>
         <v>3</v>
       </c>
-      <c r="D15">
+      <c r="D16">
         <f>Donnees!E17/100</f>
         <v>0.05</v>
       </c>
-      <c r="E15">
-        <f t="shared" si="1"/>
+      <c r="E16">
+        <f t="shared" si="2"/>
         <v>1.6666666666666666E-2</v>
       </c>
-      <c r="F15">
-        <f>Donnees!$D$4*E15*B15</f>
+      <c r="F16">
+        <f>Donnees!$D$4*E16*B16</f>
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>1</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>4</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C19" t="s">
         <v>5</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D19" t="s">
         <v>6</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E19" t="s">
         <v>644</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F19" t="s">
         <v>645</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G19" t="s">
         <v>643</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H19" t="s">
         <v>621</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I19" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>797</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>798</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N19" s="11" t="s">
+        <v>799</v>
+      </c>
+      <c r="O19" s="5" t="s">
         <v>661</v>
       </c>
-      <c r="J18" s="7" t="s">
-        <v>660</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>662</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>663</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>664</v>
-      </c>
-      <c r="N18" s="11" t="s">
-        <v>665</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>666</v>
-      </c>
-      <c r="P18" s="5" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" t="s">
-        <v>731</v>
-      </c>
-      <c r="D19" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="3">
-        <f>VLOOKUP(D19,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C19,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>0.02</v>
-      </c>
-      <c r="F19" s="3">
-        <f>E19/$E$69</f>
-        <v>1.9999999999999987E-2</v>
-      </c>
-      <c r="G19" s="3">
-        <f>1-POWER(1-E19,Donnees!$D$4)</f>
-        <v>0.33239202824490588</v>
-      </c>
-      <c r="H19" s="3">
-        <f t="shared" ref="H19:H50" si="2">1/G19</f>
-        <v>3.0084957370373568</v>
-      </c>
-      <c r="I19" s="8">
-        <f>1/(1-POWER(1-$F19*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
-      </c>
-      <c r="J19" s="8">
-        <f>1/(1-POWER(1-$F19*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
-      </c>
-      <c r="K19" s="10">
-        <f>1/(1-POWER(1-$F19*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
-      </c>
-      <c r="L19" s="10">
-        <f>1/(1-POWER(1-$F19*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
-      </c>
-      <c r="M19" s="12">
-        <f>1/(1-POWER(1-$F19*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
-      </c>
-      <c r="N19" s="12">
-        <f>1/(1-POWER(1-$F19*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
-      </c>
-      <c r="O19" s="6">
-        <f>1/(1-POWER(1-$F19*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
-      </c>
-      <c r="P19" s="6">
-        <f>1/(1-POWER(1-$F19*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P19" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="Q19" s="16" t="s">
+        <v>801</v>
+      </c>
+      <c r="R19" s="16" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>69</v>
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>723</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E20" s="3">
-        <f>VLOOKUP(D20,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C20,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>2.1428571428571429E-2</v>
+        <f>VLOOKUP(D20,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C20,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>0.02</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" ref="F20:F68" si="3">E20/$E$69</f>
-        <v>2.1428571428571415E-2</v>
+        <f>E20/$E$70</f>
+        <v>1.9999999999999987E-2</v>
       </c>
       <c r="G20" s="3">
         <f>1-POWER(1-E20,Donnees!$D$4)</f>
-        <v>0.35158861821263243</v>
+        <v>0.33239202824490588</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" si="2"/>
-        <v>2.8442331412310504</v>
+        <f t="shared" ref="H20:H51" si="3">1/G20</f>
+        <v>3.0084957370373568</v>
       </c>
       <c r="I20" s="8">
-        <f>1/(1-POWER(1-$F20*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>5.6762841299274625</v>
+        <f>1/(1-POWER(1-$F20*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J20" s="8">
-        <f>1/(1-POWER(1-$F20*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>47.143448857901362</v>
+        <f>1/(1-POWER(1-$F20*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K20" s="10">
-        <f>1/(1-POWER(1-$F20*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.126619822082489</v>
+        <f>1/(1-POWER(1-$F20*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L20" s="10">
-        <f>1/(1-POWER(1-$F20*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>78.253846868491379</v>
+        <f>1/(1-POWER(1-$F20*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M20" s="12">
-        <f>1/(1-POWER(1-$F20*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>17.763766692007298</v>
+        <f>1/(1-POWER(1-$F20*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N20" s="12">
-        <f>1/(1-POWER(1-$F20*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>156.03109001607743</v>
+        <f>1/(1-POWER(1-$F20*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O20" s="6">
-        <f>1/(1-POWER(1-$F20*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>52.328455740305785</v>
+        <f>1/(1-POWER(1-$F20*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P20" s="6">
-        <f>1/(1-POWER(1-$F20*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>467.14184480110237</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F20*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q20" s="16">
+        <f>1/(1-POWER(1-$F20*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R20" s="16">
+        <f>1/(1-POWER(1-$F20*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
         <v>70</v>
       </c>
       <c r="E21" s="3">
-        <f>VLOOKUP(D21,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C21,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D21,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C21,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F21" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F21:F69" si="4">E21/$E$70</f>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G21" s="3">
@@ -10790,123 +10779,139 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H21" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I21" s="8">
-        <f>1/(1-POWER(1-$F21*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>5.6762841299274625</v>
+        <f>1/(1-POWER(1-$F21*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>5.7137417013118368</v>
       </c>
       <c r="J21" s="8">
-        <f>1/(1-POWER(1-$F21*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>47.143448857901362</v>
+        <f>1/(1-POWER(1-$F21*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>47.481600280957529</v>
       </c>
       <c r="K21" s="10">
-        <f>1/(1-POWER(1-$F21*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.126619822082489</v>
+        <f>1/(1-POWER(1-$F21*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.064960983515661</v>
       </c>
       <c r="L21" s="10">
-        <f>1/(1-POWER(1-$F21*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>78.253846868491379</v>
+        <f>1/(1-POWER(1-$F21*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>77.698299006688089</v>
       </c>
       <c r="M21" s="12">
-        <f>1/(1-POWER(1-$F21*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>17.763766692007298</v>
+        <f>1/(1-POWER(1-$F21*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>17.640344596567786</v>
       </c>
       <c r="N21" s="12">
-        <f>1/(1-POWER(1-$F21*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>156.03109001607743</v>
+        <f>1/(1-POWER(1-$F21*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>154.9199827506408</v>
       </c>
       <c r="O21" s="6">
-        <f>1/(1-POWER(1-$F21*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>52.328455740305785</v>
+        <f>1/(1-POWER(1-$F21*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>51.95809691416796</v>
       </c>
       <c r="P21" s="6">
-        <f>1/(1-POWER(1-$F21*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>467.14184480110237</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F21*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="Q21" s="16">
+        <f>1/(1-POWER(1-$F21*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>360.84560105190172</v>
+      </c>
+      <c r="R21" s="16">
+        <f>1/(1-POWER(1-$F21*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3243.8083589698131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>735</v>
+        <v>82</v>
+      </c>
+      <c r="C22" t="s">
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E22" s="3">
-        <f>VLOOKUP(D22,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C22,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>0.02</v>
+        <f>VLOOKUP(D22,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C22,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>2.1428571428571429E-2</v>
       </c>
       <c r="F22" s="3">
-        <f t="shared" si="3"/>
-        <v>1.9999999999999987E-2</v>
+        <f t="shared" si="4"/>
+        <v>2.1428571428571415E-2</v>
       </c>
       <c r="G22" s="3">
         <f>1-POWER(1-E22,Donnees!$D$4)</f>
-        <v>0.33239202824490588</v>
+        <v>0.35158861821263243</v>
       </c>
       <c r="H22" s="3">
-        <f t="shared" si="2"/>
-        <v>3.0084957370373568</v>
+        <f t="shared" si="3"/>
+        <v>2.8442331412310504</v>
       </c>
       <c r="I22" s="8">
-        <f>1/(1-POWER(1-$F22*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F22*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>5.7137417013118368</v>
       </c>
       <c r="J22" s="8">
-        <f>1/(1-POWER(1-$F22*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F22*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>47.481600280957529</v>
       </c>
       <c r="K22" s="10">
-        <f>1/(1-POWER(1-$F22*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F22*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.064960983515661</v>
       </c>
       <c r="L22" s="10">
-        <f>1/(1-POWER(1-$F22*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F22*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>77.698299006688089</v>
       </c>
       <c r="M22" s="12">
-        <f>1/(1-POWER(1-$F22*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F22*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>17.640344596567786</v>
       </c>
       <c r="N22" s="12">
-        <f>1/(1-POWER(1-$F22*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F22*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>154.9199827506408</v>
       </c>
       <c r="O22" s="6">
-        <f>1/(1-POWER(1-$F22*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F22*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>51.95809691416796</v>
       </c>
       <c r="P22" s="6">
-        <f>1/(1-POWER(1-$F22*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F22*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="Q22" s="16">
+        <f>1/(1-POWER(1-$F22*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>360.84560105190172</v>
+      </c>
+      <c r="R22" s="16">
+        <f>1/(1-POWER(1-$F22*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3243.8083589698131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="D23" t="s">
         <v>52</v>
       </c>
       <c r="E23" s="3">
-        <f>VLOOKUP(D23,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C23,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D23,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C23,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>0.02</v>
       </c>
       <c r="F23" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G23" s="3">
@@ -10914,61 +10919,69 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H23" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I23" s="8">
-        <f>1/(1-POWER(1-$F23*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F23*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J23" s="8">
-        <f>1/(1-POWER(1-$F23*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F23*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K23" s="10">
-        <f>1/(1-POWER(1-$F23*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F23*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L23" s="10">
-        <f>1/(1-POWER(1-$F23*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F23*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M23" s="12">
-        <f>1/(1-POWER(1-$F23*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F23*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N23" s="12">
-        <f>1/(1-POWER(1-$F23*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F23*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O23" s="6">
-        <f>1/(1-POWER(1-$F23*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F23*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P23" s="6">
-        <f>1/(1-POWER(1-$F23*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F23*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q23" s="16">
+        <f>1/(1-POWER(1-$F23*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R23" s="16">
+        <f>1/(1-POWER(1-$F23*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>115</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>116</v>
+        <v>104</v>
+      </c>
+      <c r="C24" t="s">
+        <v>729</v>
       </c>
       <c r="D24" t="s">
         <v>52</v>
       </c>
       <c r="E24" s="3">
-        <f>VLOOKUP(D24,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C24,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D24,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C24,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>0.02</v>
       </c>
       <c r="F24" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G24" s="3">
@@ -10976,185 +10989,209 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I24" s="8">
-        <f>1/(1-POWER(1-$F24*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F24*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J24" s="8">
-        <f>1/(1-POWER(1-$F24*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F24*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K24" s="10">
-        <f>1/(1-POWER(1-$F24*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F24*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L24" s="10">
-        <f>1/(1-POWER(1-$F24*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F24*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M24" s="12">
-        <f>1/(1-POWER(1-$F24*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F24*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N24" s="12">
-        <f>1/(1-POWER(1-$F24*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F24*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O24" s="6">
-        <f>1/(1-POWER(1-$F24*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F24*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P24" s="6">
-        <f>1/(1-POWER(1-$F24*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F24*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q24" s="16">
+        <f>1/(1-POWER(1-$F24*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R24" s="16">
+        <f>1/(1-POWER(1-$F24*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>740</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="E25" s="3">
-        <f>VLOOKUP(D25,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C25,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>1.6666666666666666E-2</v>
+        <f>VLOOKUP(D25,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C25,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>0.02</v>
       </c>
       <c r="F25" s="3">
-        <f t="shared" si="3"/>
-        <v>1.6666666666666656E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.9999999999999987E-2</v>
       </c>
       <c r="G25" s="3">
         <f>1-POWER(1-E25,Donnees!$D$4)</f>
-        <v>0.28547862520944578</v>
+        <v>0.33239202824490588</v>
       </c>
       <c r="H25" s="3">
-        <f t="shared" si="2"/>
-        <v>3.5028892242504481</v>
+        <f t="shared" si="3"/>
+        <v>3.0084957370373568</v>
       </c>
       <c r="I25" s="8">
-        <f>1/(1-POWER(1-$F25*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>7.1541776714787559</v>
+        <f>1/(1-POWER(1-$F25*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J25" s="8">
-        <f>1/(1-POWER(1-$F25*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>60.476385987802111</v>
+        <f>1/(1-POWER(1-$F25*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K25" s="10">
-        <f>1/(1-POWER(1-$F25*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>11.593608225426648</v>
+        <f>1/(1-POWER(1-$F25*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L25" s="10">
-        <f>1/(1-POWER(1-$F25*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>100.47583145650593</v>
+        <f>1/(1-POWER(1-$F25*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M25" s="12">
-        <f>1/(1-POWER(1-$F25*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>22.700966934764622</v>
+        <f>1/(1-POWER(1-$F25*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N25" s="12">
-        <f>1/(1-POWER(1-$F25*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>200.47541567679099</v>
+        <f>1/(1-POWER(1-$F25*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O25" s="6">
-        <f>1/(1-POWER(1-$F25*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>67.142914004784032</v>
+        <f>1/(1-POWER(1-$F25*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P25" s="6">
-        <f>1/(1-POWER(1-$F25*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>600.4751385476535</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F25*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q25" s="16">
+        <f>1/(1-POWER(1-$F25*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R25" s="16">
+        <f>1/(1-POWER(1-$F25*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>741</v>
+        <v>127</v>
+      </c>
+      <c r="C26" t="s">
+        <v>732</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="E26" s="3">
-        <f>VLOOKUP(D26,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C26,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>0.02</v>
+        <f>VLOOKUP(D26,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C26,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>1.6666666666666666E-2</v>
       </c>
       <c r="F26" s="3">
-        <f t="shared" si="3"/>
-        <v>1.9999999999999987E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.6666666666666656E-2</v>
       </c>
       <c r="G26" s="3">
         <f>1-POWER(1-E26,Donnees!$D$4)</f>
-        <v>0.33239202824490588</v>
+        <v>0.28547862520944578</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" si="2"/>
-        <v>3.0084957370373568</v>
+        <f t="shared" si="3"/>
+        <v>3.5028892242504481</v>
       </c>
       <c r="I26" s="8">
-        <f>1/(1-POWER(1-$F26*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F26*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>7.2023965734528721</v>
       </c>
       <c r="J26" s="8">
-        <f>1/(1-POWER(1-$F26*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F26*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>60.911158621330586</v>
       </c>
       <c r="K26" s="10">
-        <f>1/(1-POWER(1-$F26*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F26*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>11.514297189973696</v>
       </c>
       <c r="L26" s="10">
-        <f>1/(1-POWER(1-$F26*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F26*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>99.761551725391485</v>
       </c>
       <c r="M26" s="12">
-        <f>1/(1-POWER(1-$F26*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F26*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>22.542263745146919</v>
       </c>
       <c r="N26" s="12">
-        <f>1/(1-POWER(1-$F26*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F26*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>199.04684723903111</v>
       </c>
       <c r="O26" s="6">
-        <f>1/(1-POWER(1-$F26*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F26*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>66.666732505570209</v>
       </c>
       <c r="P26" s="6">
-        <f>1/(1-POWER(1-$F26*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F26*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>596.1894252587216</v>
+      </c>
+      <c r="Q26" s="16">
+        <f>1/(1-POWER(1-$F26*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="R26" s="16">
+        <f>1/(1-POWER(1-$F26*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>4170.4750199394775</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>47</v>
       </c>
       <c r="B27" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C27" t="s">
-        <v>155</v>
+        <v>733</v>
       </c>
       <c r="D27" t="s">
         <v>52</v>
       </c>
       <c r="E27" s="3">
-        <f>VLOOKUP(D27,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C27,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D27,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C27,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>0.02</v>
       </c>
       <c r="F27" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G27" s="3">
@@ -11162,61 +11199,69 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H27" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I27" s="8">
-        <f>1/(1-POWER(1-$F27*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F27*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J27" s="8">
-        <f>1/(1-POWER(1-$F27*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F27*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K27" s="10">
-        <f>1/(1-POWER(1-$F27*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F27*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L27" s="10">
-        <f>1/(1-POWER(1-$F27*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F27*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M27" s="12">
-        <f>1/(1-POWER(1-$F27*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F27*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N27" s="12">
-        <f>1/(1-POWER(1-$F27*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F27*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O27" s="6">
-        <f>1/(1-POWER(1-$F27*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F27*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P27" s="6">
-        <f>1/(1-POWER(1-$F27*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F27*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q27" s="16">
+        <f>1/(1-POWER(1-$F27*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R27" s="16">
+        <f>1/(1-POWER(1-$F27*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>47</v>
       </c>
       <c r="B28" t="s">
-        <v>166</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>744</v>
+        <v>154</v>
+      </c>
+      <c r="C28" t="s">
+        <v>155</v>
       </c>
       <c r="D28" t="s">
         <v>52</v>
       </c>
       <c r="E28" s="3">
-        <f>VLOOKUP(D28,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C28,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D28,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C28,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>0.02</v>
       </c>
       <c r="F28" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G28" s="3">
@@ -11224,247 +11269,279 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H28" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I28" s="8">
-        <f>1/(1-POWER(1-$F28*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F28*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J28" s="8">
-        <f>1/(1-POWER(1-$F28*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F28*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K28" s="10">
-        <f>1/(1-POWER(1-$F28*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F28*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L28" s="10">
-        <f>1/(1-POWER(1-$F28*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F28*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M28" s="12">
-        <f>1/(1-POWER(1-$F28*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F28*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N28" s="12">
-        <f>1/(1-POWER(1-$F28*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F28*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O28" s="6">
-        <f>1/(1-POWER(1-$F28*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F28*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P28" s="6">
-        <f>1/(1-POWER(1-$F28*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F28*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q28" s="16">
+        <f>1/(1-POWER(1-$F28*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R28" s="16">
+        <f>1/(1-POWER(1-$F28*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>47</v>
       </c>
       <c r="B29" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s">
-        <v>176</v>
+        <v>736</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E29" s="3">
-        <f>VLOOKUP(D29,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C29,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>2.1428571428571429E-2</v>
+        <f>VLOOKUP(D29,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C29,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>0.02</v>
       </c>
       <c r="F29" s="3">
-        <f t="shared" si="3"/>
-        <v>2.1428571428571415E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.9999999999999987E-2</v>
       </c>
       <c r="G29" s="3">
         <f>1-POWER(1-E29,Donnees!$D$4)</f>
-        <v>0.35158861821263243</v>
+        <v>0.33239202824490588</v>
       </c>
       <c r="H29" s="3">
-        <f t="shared" si="2"/>
-        <v>2.8442331412310504</v>
+        <f t="shared" si="3"/>
+        <v>3.0084957370373568</v>
       </c>
       <c r="I29" s="8">
-        <f>1/(1-POWER(1-$F29*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>5.6762841299274625</v>
+        <f>1/(1-POWER(1-$F29*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J29" s="8">
-        <f>1/(1-POWER(1-$F29*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>47.143448857901362</v>
+        <f>1/(1-POWER(1-$F29*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K29" s="10">
-        <f>1/(1-POWER(1-$F29*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.126619822082489</v>
+        <f>1/(1-POWER(1-$F29*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L29" s="10">
-        <f>1/(1-POWER(1-$F29*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>78.253846868491379</v>
+        <f>1/(1-POWER(1-$F29*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M29" s="12">
-        <f>1/(1-POWER(1-$F29*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>17.763766692007298</v>
+        <f>1/(1-POWER(1-$F29*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N29" s="12">
-        <f>1/(1-POWER(1-$F29*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>156.03109001607743</v>
+        <f>1/(1-POWER(1-$F29*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O29" s="6">
-        <f>1/(1-POWER(1-$F29*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>52.328455740305785</v>
+        <f>1/(1-POWER(1-$F29*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P29" s="6">
-        <f>1/(1-POWER(1-$F29*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>467.14184480110237</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F29*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q29" s="16">
+        <f>1/(1-POWER(1-$F29*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R29" s="16">
+        <f>1/(1-POWER(1-$F29*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>47</v>
       </c>
       <c r="B30" t="s">
-        <v>191</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>746</v>
+        <v>175</v>
+      </c>
+      <c r="C30" t="s">
+        <v>176</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="E30" s="3">
-        <f>VLOOKUP(D30,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C30,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>1.6666666666666666E-2</v>
+        <f>VLOOKUP(D30,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C30,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>2.1428571428571429E-2</v>
       </c>
       <c r="F30" s="3">
-        <f t="shared" si="3"/>
-        <v>1.6666666666666656E-2</v>
+        <f t="shared" si="4"/>
+        <v>2.1428571428571415E-2</v>
       </c>
       <c r="G30" s="3">
         <f>1-POWER(1-E30,Donnees!$D$4)</f>
-        <v>0.28547862520944578</v>
+        <v>0.35158861821263243</v>
       </c>
       <c r="H30" s="3">
-        <f t="shared" si="2"/>
-        <v>3.5028892242504481</v>
+        <f t="shared" si="3"/>
+        <v>2.8442331412310504</v>
       </c>
       <c r="I30" s="8">
-        <f>1/(1-POWER(1-$F30*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>7.1541776714787559</v>
+        <f>1/(1-POWER(1-$F30*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>5.7137417013118368</v>
       </c>
       <c r="J30" s="8">
-        <f>1/(1-POWER(1-$F30*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>60.476385987802111</v>
+        <f>1/(1-POWER(1-$F30*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>47.481600280957529</v>
       </c>
       <c r="K30" s="10">
-        <f>1/(1-POWER(1-$F30*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>11.593608225426648</v>
+        <f>1/(1-POWER(1-$F30*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.064960983515661</v>
       </c>
       <c r="L30" s="10">
-        <f>1/(1-POWER(1-$F30*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>100.47583145650593</v>
+        <f>1/(1-POWER(1-$F30*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>77.698299006688089</v>
       </c>
       <c r="M30" s="12">
-        <f>1/(1-POWER(1-$F30*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>22.700966934764622</v>
+        <f>1/(1-POWER(1-$F30*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>17.640344596567786</v>
       </c>
       <c r="N30" s="12">
-        <f>1/(1-POWER(1-$F30*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>200.47541567679099</v>
+        <f>1/(1-POWER(1-$F30*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>154.9199827506408</v>
       </c>
       <c r="O30" s="6">
-        <f>1/(1-POWER(1-$F30*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>67.142914004784032</v>
+        <f>1/(1-POWER(1-$F30*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>51.95809691416796</v>
       </c>
       <c r="P30" s="6">
-        <f>1/(1-POWER(1-$F30*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>600.4751385476535</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F30*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="Q30" s="16">
+        <f>1/(1-POWER(1-$F30*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>360.84560105190172</v>
+      </c>
+      <c r="R30" s="16">
+        <f>1/(1-POWER(1-$F30*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3243.8083589698131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>47</v>
       </c>
       <c r="B31" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C31" t="s">
-        <v>59</v>
+        <v>738</v>
       </c>
       <c r="D31" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="E31" s="3">
-        <f>VLOOKUP(D31,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C31,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>0.02</v>
+        <f>VLOOKUP(D31,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C31,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>1.6666666666666666E-2</v>
       </c>
       <c r="F31" s="3">
-        <f t="shared" si="3"/>
-        <v>1.9999999999999987E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.6666666666666656E-2</v>
       </c>
       <c r="G31" s="3">
         <f>1-POWER(1-E31,Donnees!$D$4)</f>
-        <v>0.33239202824490588</v>
+        <v>0.28547862520944578</v>
       </c>
       <c r="H31" s="3">
-        <f t="shared" si="2"/>
-        <v>3.0084957370373568</v>
+        <f t="shared" si="3"/>
+        <v>3.5028892242504481</v>
       </c>
       <c r="I31" s="8">
-        <f>1/(1-POWER(1-$F31*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F31*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>7.2023965734528721</v>
       </c>
       <c r="J31" s="8">
-        <f>1/(1-POWER(1-$F31*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F31*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>60.911158621330586</v>
       </c>
       <c r="K31" s="10">
-        <f>1/(1-POWER(1-$F31*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F31*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>11.514297189973696</v>
       </c>
       <c r="L31" s="10">
-        <f>1/(1-POWER(1-$F31*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F31*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>99.761551725391485</v>
       </c>
       <c r="M31" s="12">
-        <f>1/(1-POWER(1-$F31*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F31*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>22.542263745146919</v>
       </c>
       <c r="N31" s="12">
-        <f>1/(1-POWER(1-$F31*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F31*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>199.04684723903111</v>
       </c>
       <c r="O31" s="6">
-        <f>1/(1-POWER(1-$F31*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F31*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>66.666732505570209</v>
       </c>
       <c r="P31" s="6">
-        <f>1/(1-POWER(1-$F31*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F31*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>596.1894252587216</v>
+      </c>
+      <c r="Q31" s="16">
+        <f>1/(1-POWER(1-$F31*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="R31" s="16">
+        <f>1/(1-POWER(1-$F31*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>4170.4750199394775</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>208</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>747</v>
+        <v>199</v>
+      </c>
+      <c r="C32" t="s">
+        <v>59</v>
       </c>
       <c r="D32" t="s">
         <v>52</v>
       </c>
       <c r="E32" s="3">
-        <f>VLOOKUP(D32,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C32,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D32,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C32,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>0.02</v>
       </c>
       <c r="F32" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G32" s="3">
@@ -11472,61 +11549,69 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H32" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I32" s="8">
-        <f>1/(1-POWER(1-$F32*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F32*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J32" s="8">
-        <f>1/(1-POWER(1-$F32*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F32*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K32" s="10">
-        <f>1/(1-POWER(1-$F32*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F32*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L32" s="10">
-        <f>1/(1-POWER(1-$F32*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F32*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M32" s="12">
-        <f>1/(1-POWER(1-$F32*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F32*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N32" s="12">
-        <f>1/(1-POWER(1-$F32*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F32*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O32" s="6">
-        <f>1/(1-POWER(1-$F32*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F32*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P32" s="6">
-        <f>1/(1-POWER(1-$F32*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F32*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q32" s="16">
+        <f>1/(1-POWER(1-$F32*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R32" s="16">
+        <f>1/(1-POWER(1-$F32*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>47</v>
       </c>
       <c r="B33" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="C33" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="D33" t="s">
         <v>52</v>
       </c>
       <c r="E33" s="3">
-        <f>VLOOKUP(D33,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C33,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D33,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C33,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>0.02</v>
       </c>
       <c r="F33" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G33" s="3">
@@ -11534,433 +11619,489 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H33" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I33" s="8">
-        <f>1/(1-POWER(1-$F33*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F33*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J33" s="8">
-        <f>1/(1-POWER(1-$F33*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F33*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K33" s="10">
-        <f>1/(1-POWER(1-$F33*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F33*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L33" s="10">
-        <f>1/(1-POWER(1-$F33*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F33*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M33" s="12">
-        <f>1/(1-POWER(1-$F33*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F33*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N33" s="12">
-        <f>1/(1-POWER(1-$F33*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F33*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O33" s="6">
-        <f>1/(1-POWER(1-$F33*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F33*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P33" s="6">
-        <f>1/(1-POWER(1-$F33*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F33*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q33" s="16">
+        <f>1/(1-POWER(1-$F33*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R33" s="16">
+        <f>1/(1-POWER(1-$F33*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>47</v>
       </c>
       <c r="B34" t="s">
-        <v>231</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>750</v>
+        <v>222</v>
+      </c>
+      <c r="C34" t="s">
+        <v>741</v>
       </c>
       <c r="D34" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E34" s="3">
-        <f>VLOOKUP(D34,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C34,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>2.1428571428571429E-2</v>
+        <f>VLOOKUP(D34,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C34,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>0.02</v>
       </c>
       <c r="F34" s="3">
-        <f t="shared" si="3"/>
-        <v>2.1428571428571415E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.9999999999999987E-2</v>
       </c>
       <c r="G34" s="3">
         <f>1-POWER(1-E34,Donnees!$D$4)</f>
-        <v>0.35158861821263243</v>
+        <v>0.33239202824490588</v>
       </c>
       <c r="H34" s="3">
-        <f t="shared" si="2"/>
-        <v>2.8442331412310504</v>
+        <f t="shared" si="3"/>
+        <v>3.0084957370373568</v>
       </c>
       <c r="I34" s="8">
-        <f>1/(1-POWER(1-$F34*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>5.6762841299274625</v>
+        <f>1/(1-POWER(1-$F34*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J34" s="8">
-        <f>1/(1-POWER(1-$F34*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>47.143448857901362</v>
+        <f>1/(1-POWER(1-$F34*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K34" s="10">
-        <f>1/(1-POWER(1-$F34*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.126619822082489</v>
+        <f>1/(1-POWER(1-$F34*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L34" s="10">
-        <f>1/(1-POWER(1-$F34*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>78.253846868491379</v>
+        <f>1/(1-POWER(1-$F34*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M34" s="12">
-        <f>1/(1-POWER(1-$F34*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>17.763766692007298</v>
+        <f>1/(1-POWER(1-$F34*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N34" s="12">
-        <f>1/(1-POWER(1-$F34*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>156.03109001607743</v>
+        <f>1/(1-POWER(1-$F34*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O34" s="6">
-        <f>1/(1-POWER(1-$F34*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>52.328455740305785</v>
+        <f>1/(1-POWER(1-$F34*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P34" s="6">
-        <f>1/(1-POWER(1-$F34*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>467.14184480110237</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F34*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q34" s="16">
+        <f>1/(1-POWER(1-$F34*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R34" s="16">
+        <f>1/(1-POWER(1-$F34*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>47</v>
       </c>
       <c r="B35" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C35" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="D35" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="E35" s="3">
-        <f>VLOOKUP(D35,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C35,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>1.6666666666666666E-2</v>
+        <f>VLOOKUP(D35,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C35,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>2.1428571428571429E-2</v>
       </c>
       <c r="F35" s="3">
-        <f t="shared" si="3"/>
-        <v>1.6666666666666656E-2</v>
+        <f t="shared" si="4"/>
+        <v>2.1428571428571415E-2</v>
       </c>
       <c r="G35" s="3">
         <f>1-POWER(1-E35,Donnees!$D$4)</f>
-        <v>0.28547862520944578</v>
+        <v>0.35158861821263243</v>
       </c>
       <c r="H35" s="3">
-        <f t="shared" si="2"/>
-        <v>3.5028892242504481</v>
+        <f t="shared" si="3"/>
+        <v>2.8442331412310504</v>
       </c>
       <c r="I35" s="8">
-        <f>1/(1-POWER(1-$F35*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>7.1541776714787559</v>
+        <f>1/(1-POWER(1-$F35*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>5.7137417013118368</v>
       </c>
       <c r="J35" s="8">
-        <f>1/(1-POWER(1-$F35*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>60.476385987802111</v>
+        <f>1/(1-POWER(1-$F35*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>47.481600280957529</v>
       </c>
       <c r="K35" s="10">
-        <f>1/(1-POWER(1-$F35*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>11.593608225426648</v>
+        <f>1/(1-POWER(1-$F35*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.064960983515661</v>
       </c>
       <c r="L35" s="10">
-        <f>1/(1-POWER(1-$F35*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>100.47583145650593</v>
+        <f>1/(1-POWER(1-$F35*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>77.698299006688089</v>
       </c>
       <c r="M35" s="12">
-        <f>1/(1-POWER(1-$F35*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>22.700966934764622</v>
+        <f>1/(1-POWER(1-$F35*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>17.640344596567786</v>
       </c>
       <c r="N35" s="12">
-        <f>1/(1-POWER(1-$F35*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>200.47541567679099</v>
+        <f>1/(1-POWER(1-$F35*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>154.9199827506408</v>
       </c>
       <c r="O35" s="6">
-        <f>1/(1-POWER(1-$F35*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>67.142914004784032</v>
+        <f>1/(1-POWER(1-$F35*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>51.95809691416796</v>
       </c>
       <c r="P35" s="6">
-        <f>1/(1-POWER(1-$F35*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>600.4751385476535</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F35*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="Q35" s="16">
+        <f>1/(1-POWER(1-$F35*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>360.84560105190172</v>
+      </c>
+      <c r="R35" s="16">
+        <f>1/(1-POWER(1-$F35*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3243.8083589698131</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>246</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>247</v>
+        <v>241</v>
+      </c>
+      <c r="C36" t="s">
+        <v>743</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="E36" s="3">
-        <f>VLOOKUP(D36,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C36,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>0.02</v>
+        <f>VLOOKUP(D36,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C36,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>1.6666666666666666E-2</v>
       </c>
       <c r="F36" s="3">
-        <f t="shared" si="3"/>
-        <v>1.9999999999999987E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.6666666666666656E-2</v>
       </c>
       <c r="G36" s="3">
         <f>1-POWER(1-E36,Donnees!$D$4)</f>
-        <v>0.33239202824490588</v>
+        <v>0.28547862520944578</v>
       </c>
       <c r="H36" s="3">
-        <f t="shared" si="2"/>
-        <v>3.0084957370373568</v>
+        <f t="shared" si="3"/>
+        <v>3.5028892242504481</v>
       </c>
       <c r="I36" s="8">
-        <f>1/(1-POWER(1-$F36*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F36*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>7.2023965734528721</v>
       </c>
       <c r="J36" s="8">
-        <f>1/(1-POWER(1-$F36*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F36*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>60.911158621330586</v>
       </c>
       <c r="K36" s="10">
-        <f>1/(1-POWER(1-$F36*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F36*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>11.514297189973696</v>
       </c>
       <c r="L36" s="10">
-        <f>1/(1-POWER(1-$F36*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F36*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>99.761551725391485</v>
       </c>
       <c r="M36" s="12">
-        <f>1/(1-POWER(1-$F36*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F36*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>22.542263745146919</v>
       </c>
       <c r="N36" s="12">
-        <f>1/(1-POWER(1-$F36*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F36*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>199.04684723903111</v>
       </c>
       <c r="O36" s="6">
-        <f>1/(1-POWER(1-$F36*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F36*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>66.666732505570209</v>
       </c>
       <c r="P36" s="6">
-        <f>1/(1-POWER(1-$F36*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F36*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>596.1894252587216</v>
+      </c>
+      <c r="Q36" s="16">
+        <f>1/(1-POWER(1-$F36*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="R36" s="16">
+        <f>1/(1-POWER(1-$F36*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>4170.4750199394775</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="C37" t="s">
-        <v>753</v>
+        <v>247</v>
       </c>
       <c r="D37" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E37" s="3">
-        <f>VLOOKUP(D37,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C37,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>2.1428571428571429E-2</v>
+        <f>VLOOKUP(D37,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C37,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>0.02</v>
       </c>
       <c r="F37" s="3">
-        <f t="shared" si="3"/>
-        <v>2.1428571428571415E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.9999999999999987E-2</v>
       </c>
       <c r="G37" s="3">
         <f>1-POWER(1-E37,Donnees!$D$4)</f>
-        <v>0.35158861821263243</v>
+        <v>0.33239202824490588</v>
       </c>
       <c r="H37" s="3">
-        <f t="shared" si="2"/>
-        <v>2.8442331412310504</v>
+        <f t="shared" si="3"/>
+        <v>3.0084957370373568</v>
       </c>
       <c r="I37" s="8">
-        <f>1/(1-POWER(1-$F37*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>5.6762841299274625</v>
+        <f>1/(1-POWER(1-$F37*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J37" s="8">
-        <f>1/(1-POWER(1-$F37*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>47.143448857901362</v>
+        <f>1/(1-POWER(1-$F37*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K37" s="10">
-        <f>1/(1-POWER(1-$F37*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.126619822082489</v>
+        <f>1/(1-POWER(1-$F37*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L37" s="10">
-        <f>1/(1-POWER(1-$F37*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>78.253846868491379</v>
+        <f>1/(1-POWER(1-$F37*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M37" s="12">
-        <f>1/(1-POWER(1-$F37*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>17.763766692007298</v>
+        <f>1/(1-POWER(1-$F37*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N37" s="12">
-        <f>1/(1-POWER(1-$F37*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>156.03109001607743</v>
+        <f>1/(1-POWER(1-$F37*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O37" s="6">
-        <f>1/(1-POWER(1-$F37*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>52.328455740305785</v>
+        <f>1/(1-POWER(1-$F37*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P37" s="6">
-        <f>1/(1-POWER(1-$F37*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>467.14184480110237</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F37*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q37" s="16">
+        <f>1/(1-POWER(1-$F37*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R37" s="16">
+        <f>1/(1-POWER(1-$F37*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>266</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>267</v>
+        <v>259</v>
+      </c>
+      <c r="C38" t="s">
+        <v>745</v>
       </c>
       <c r="D38" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E38" s="3">
-        <f>VLOOKUP(D38,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C38,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>0.02</v>
+        <f>VLOOKUP(D38,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C38,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>2.1428571428571429E-2</v>
       </c>
       <c r="F38" s="3">
-        <f t="shared" si="3"/>
-        <v>1.9999999999999987E-2</v>
+        <f t="shared" si="4"/>
+        <v>2.1428571428571415E-2</v>
       </c>
       <c r="G38" s="3">
         <f>1-POWER(1-E38,Donnees!$D$4)</f>
-        <v>0.33239202824490588</v>
+        <v>0.35158861821263243</v>
       </c>
       <c r="H38" s="3">
-        <f t="shared" si="2"/>
-        <v>3.0084957370373568</v>
+        <f t="shared" si="3"/>
+        <v>2.8442331412310504</v>
       </c>
       <c r="I38" s="8">
-        <f>1/(1-POWER(1-$F38*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F38*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>5.7137417013118368</v>
       </c>
       <c r="J38" s="8">
-        <f>1/(1-POWER(1-$F38*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F38*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>47.481600280957529</v>
       </c>
       <c r="K38" s="10">
-        <f>1/(1-POWER(1-$F38*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F38*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.064960983515661</v>
       </c>
       <c r="L38" s="10">
-        <f>1/(1-POWER(1-$F38*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F38*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>77.698299006688089</v>
       </c>
       <c r="M38" s="12">
-        <f>1/(1-POWER(1-$F38*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F38*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>17.640344596567786</v>
       </c>
       <c r="N38" s="12">
-        <f>1/(1-POWER(1-$F38*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F38*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>154.9199827506408</v>
       </c>
       <c r="O38" s="6">
-        <f>1/(1-POWER(1-$F38*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F38*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>51.95809691416796</v>
       </c>
       <c r="P38" s="6">
-        <f>1/(1-POWER(1-$F38*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F38*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="Q38" s="16">
+        <f>1/(1-POWER(1-$F38*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>360.84560105190172</v>
+      </c>
+      <c r="R38" s="16">
+        <f>1/(1-POWER(1-$F38*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3243.8083589698131</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
       <c r="B39" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="C39" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E39" s="3">
-        <f>VLOOKUP(D39,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C39,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>2.1428571428571429E-2</v>
+        <f>VLOOKUP(D39,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C39,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>0.02</v>
       </c>
       <c r="F39" s="3">
-        <f t="shared" si="3"/>
-        <v>2.1428571428571415E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.9999999999999987E-2</v>
       </c>
       <c r="G39" s="3">
         <f>1-POWER(1-E39,Donnees!$D$4)</f>
-        <v>0.35158861821263243</v>
+        <v>0.33239202824490588</v>
       </c>
       <c r="H39" s="3">
-        <f t="shared" si="2"/>
-        <v>2.8442331412310504</v>
+        <f t="shared" si="3"/>
+        <v>3.0084957370373568</v>
       </c>
       <c r="I39" s="8">
-        <f>1/(1-POWER(1-$F39*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>5.6762841299274625</v>
+        <f>1/(1-POWER(1-$F39*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J39" s="8">
-        <f>1/(1-POWER(1-$F39*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>47.143448857901362</v>
+        <f>1/(1-POWER(1-$F39*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K39" s="10">
-        <f>1/(1-POWER(1-$F39*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.126619822082489</v>
+        <f>1/(1-POWER(1-$F39*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L39" s="10">
-        <f>1/(1-POWER(1-$F39*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>78.253846868491379</v>
+        <f>1/(1-POWER(1-$F39*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M39" s="12">
-        <f>1/(1-POWER(1-$F39*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>17.763766692007298</v>
+        <f>1/(1-POWER(1-$F39*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N39" s="12">
-        <f>1/(1-POWER(1-$F39*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>156.03109001607743</v>
+        <f>1/(1-POWER(1-$F39*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O39" s="6">
-        <f>1/(1-POWER(1-$F39*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>52.328455740305785</v>
+        <f>1/(1-POWER(1-$F39*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P39" s="6">
-        <f>1/(1-POWER(1-$F39*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>467.14184480110237</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F39*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q39" s="16">
+        <f>1/(1-POWER(1-$F39*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R39" s="16">
+        <f>1/(1-POWER(1-$F39*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>290</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>291</v>
+        <v>275</v>
+      </c>
+      <c r="C40" t="s">
+        <v>276</v>
       </c>
       <c r="D40" t="s">
         <v>70</v>
       </c>
       <c r="E40" s="3">
-        <f>VLOOKUP(D40,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C40,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D40,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C40,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F40" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G40" s="3">
@@ -11968,123 +12109,139 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H40" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I40" s="8">
-        <f>1/(1-POWER(1-$F40*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>5.6762841299274625</v>
+        <f>1/(1-POWER(1-$F40*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>5.7137417013118368</v>
       </c>
       <c r="J40" s="8">
-        <f>1/(1-POWER(1-$F40*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>47.143448857901362</v>
+        <f>1/(1-POWER(1-$F40*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>47.481600280957529</v>
       </c>
       <c r="K40" s="10">
-        <f>1/(1-POWER(1-$F40*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.126619822082489</v>
+        <f>1/(1-POWER(1-$F40*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.064960983515661</v>
       </c>
       <c r="L40" s="10">
-        <f>1/(1-POWER(1-$F40*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>78.253846868491379</v>
+        <f>1/(1-POWER(1-$F40*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>77.698299006688089</v>
       </c>
       <c r="M40" s="12">
-        <f>1/(1-POWER(1-$F40*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>17.763766692007298</v>
+        <f>1/(1-POWER(1-$F40*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>17.640344596567786</v>
       </c>
       <c r="N40" s="12">
-        <f>1/(1-POWER(1-$F40*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>156.03109001607743</v>
+        <f>1/(1-POWER(1-$F40*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>154.9199827506408</v>
       </c>
       <c r="O40" s="6">
-        <f>1/(1-POWER(1-$F40*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>52.328455740305785</v>
+        <f>1/(1-POWER(1-$F40*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>51.95809691416796</v>
       </c>
       <c r="P40" s="6">
-        <f>1/(1-POWER(1-$F40*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>467.14184480110237</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F40*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="Q40" s="16">
+        <f>1/(1-POWER(1-$F40*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>360.84560105190172</v>
+      </c>
+      <c r="R40" s="16">
+        <f>1/(1-POWER(1-$F40*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3243.8083589698131</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="C41" t="s">
-        <v>756</v>
+        <v>291</v>
       </c>
       <c r="D41" t="s">
-        <v>305</v>
+        <v>70</v>
       </c>
       <c r="E41" s="3">
-        <f>VLOOKUP(D41,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C41,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>1.8749999999999999E-2</v>
+        <f>VLOOKUP(D41,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C41,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>2.1428571428571429E-2</v>
       </c>
       <c r="F41" s="3">
-        <f t="shared" si="3"/>
-        <v>1.8749999999999985E-2</v>
+        <f t="shared" si="4"/>
+        <v>2.1428571428571415E-2</v>
       </c>
       <c r="G41" s="3">
         <f>1-POWER(1-E41,Donnees!$D$4)</f>
-        <v>0.31515325639173553</v>
+        <v>0.35158861821263243</v>
       </c>
       <c r="H41" s="3">
-        <f t="shared" si="2"/>
-        <v>3.1730593916408716</v>
+        <f t="shared" si="3"/>
+        <v>2.8442331412310504</v>
       </c>
       <c r="I41" s="8">
-        <f>1/(1-POWER(1-$F41*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.4150060276858722</v>
+        <f>1/(1-POWER(1-$F41*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>5.7137417013118368</v>
       </c>
       <c r="J41" s="8">
-        <f>1/(1-POWER(1-$F41*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>53.809892648961679</v>
+        <f>1/(1-POWER(1-$F41*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>47.481600280957529</v>
       </c>
       <c r="K41" s="10">
-        <f>1/(1-POWER(1-$F41*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>10.359979540057177</v>
+        <f>1/(1-POWER(1-$F41*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.064960983515661</v>
       </c>
       <c r="L41" s="10">
-        <f>1/(1-POWER(1-$F41*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>89.364824306266769</v>
+        <f>1/(1-POWER(1-$F41*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>77.698299006688089</v>
       </c>
       <c r="M41" s="12">
-        <f>1/(1-POWER(1-$F41*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>20.232299777012749</v>
+        <f>1/(1-POWER(1-$F41*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>17.640344596567786</v>
       </c>
       <c r="N41" s="12">
-        <f>1/(1-POWER(1-$F41*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>178.25324542143156</v>
+        <f>1/(1-POWER(1-$F41*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>154.9199827506408</v>
       </c>
       <c r="O41" s="6">
-        <f>1/(1-POWER(1-$F41*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>59.73566257905977</v>
+        <f>1/(1-POWER(1-$F41*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>51.95809691416796</v>
       </c>
       <c r="P41" s="6">
-        <f>1/(1-POWER(1-$F41*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>533.80848919998323</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F41*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="Q41" s="16">
+        <f>1/(1-POWER(1-$F41*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>360.84560105190172</v>
+      </c>
+      <c r="R41" s="16">
+        <f>1/(1-POWER(1-$F41*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3243.8083589698131</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>318</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>758</v>
+        <v>304</v>
+      </c>
+      <c r="C42" t="s">
+        <v>748</v>
       </c>
       <c r="D42" t="s">
         <v>305</v>
       </c>
       <c r="E42" s="3">
-        <f>VLOOKUP(D42,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C42,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D42,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C42,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>1.8749999999999999E-2</v>
       </c>
       <c r="F42" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.8749999999999985E-2</v>
       </c>
       <c r="G42" s="3">
@@ -12092,433 +12249,489 @@
         <v>0.31515325639173553</v>
       </c>
       <c r="H42" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.1730593916408716</v>
       </c>
       <c r="I42" s="8">
-        <f>1/(1-POWER(1-$F42*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.4150060276858722</v>
+        <f>1/(1-POWER(1-$F42*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.4578458934330172</v>
       </c>
       <c r="J42" s="8">
-        <f>1/(1-POWER(1-$F42*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>53.809892648961679</v>
+        <f>1/(1-POWER(1-$F42*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>54.196354855722817</v>
       </c>
       <c r="K42" s="10">
-        <f>1/(1-POWER(1-$F42*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>10.359979540057177</v>
+        <f>1/(1-POWER(1-$F42*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>10.289493630089176</v>
       </c>
       <c r="L42" s="10">
-        <f>1/(1-POWER(1-$F42*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>89.364824306266769</v>
+        <f>1/(1-POWER(1-$F42*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>88.729910402846656</v>
       </c>
       <c r="M42" s="12">
-        <f>1/(1-POWER(1-$F42*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>20.232299777012749</v>
+        <f>1/(1-POWER(1-$F42*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>20.091236650595796</v>
       </c>
       <c r="N42" s="12">
-        <f>1/(1-POWER(1-$F42*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>178.25324542143156</v>
+        <f>1/(1-POWER(1-$F42*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>176.98340751640595</v>
       </c>
       <c r="O42" s="6">
-        <f>1/(1-POWER(1-$F42*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>59.73566257905977</v>
+        <f>1/(1-POWER(1-$F42*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>59.312392255803132</v>
       </c>
       <c r="P42" s="6">
-        <f>1/(1-POWER(1-$F42*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>533.80848919998323</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F42*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>529.99896651203778</v>
+      </c>
+      <c r="Q42" s="16">
+        <f>1/(1-POWER(1-$F42*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>412.3270536965432</v>
+      </c>
+      <c r="R42" s="16">
+        <f>1/(1-POWER(1-$F42*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3707.1416890942214</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="C43" t="s">
-        <v>332</v>
+        <v>750</v>
       </c>
       <c r="D43" t="s">
-        <v>70</v>
+        <v>305</v>
       </c>
       <c r="E43" s="3">
-        <f>VLOOKUP(D43,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C43,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>2.1428571428571429E-2</v>
+        <f>VLOOKUP(D43,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C43,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>1.8749999999999999E-2</v>
       </c>
       <c r="F43" s="3">
-        <f t="shared" si="3"/>
-        <v>2.1428571428571415E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.8749999999999985E-2</v>
       </c>
       <c r="G43" s="3">
         <f>1-POWER(1-E43,Donnees!$D$4)</f>
-        <v>0.35158861821263243</v>
+        <v>0.31515325639173553</v>
       </c>
       <c r="H43" s="3">
-        <f t="shared" si="2"/>
-        <v>2.8442331412310504</v>
+        <f t="shared" si="3"/>
+        <v>3.1730593916408716</v>
       </c>
       <c r="I43" s="8">
-        <f>1/(1-POWER(1-$F43*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>5.6762841299274625</v>
+        <f>1/(1-POWER(1-$F43*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.4578458934330172</v>
       </c>
       <c r="J43" s="8">
-        <f>1/(1-POWER(1-$F43*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>47.143448857901362</v>
+        <f>1/(1-POWER(1-$F43*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>54.196354855722817</v>
       </c>
       <c r="K43" s="10">
-        <f>1/(1-POWER(1-$F43*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.126619822082489</v>
+        <f>1/(1-POWER(1-$F43*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>10.289493630089176</v>
       </c>
       <c r="L43" s="10">
-        <f>1/(1-POWER(1-$F43*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>78.253846868491379</v>
+        <f>1/(1-POWER(1-$F43*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>88.729910402846656</v>
       </c>
       <c r="M43" s="12">
-        <f>1/(1-POWER(1-$F43*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>17.763766692007298</v>
+        <f>1/(1-POWER(1-$F43*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>20.091236650595796</v>
       </c>
       <c r="N43" s="12">
-        <f>1/(1-POWER(1-$F43*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>156.03109001607743</v>
+        <f>1/(1-POWER(1-$F43*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>176.98340751640595</v>
       </c>
       <c r="O43" s="6">
-        <f>1/(1-POWER(1-$F43*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>52.328455740305785</v>
+        <f>1/(1-POWER(1-$F43*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>59.312392255803132</v>
       </c>
       <c r="P43" s="6">
-        <f>1/(1-POWER(1-$F43*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>467.14184480110237</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F43*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>529.99896651203778</v>
+      </c>
+      <c r="Q43" s="16">
+        <f>1/(1-POWER(1-$F43*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>412.3270536965432</v>
+      </c>
+      <c r="R43" s="16">
+        <f>1/(1-POWER(1-$F43*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3707.1416890942214</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>341</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>342</v>
+        <v>331</v>
+      </c>
+      <c r="C44" t="s">
+        <v>332</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E44" s="3">
-        <f>VLOOKUP(D44,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C44,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>0.02</v>
+        <f>VLOOKUP(D44,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C44,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>2.1428571428571429E-2</v>
       </c>
       <c r="F44" s="3">
-        <f t="shared" si="3"/>
-        <v>1.9999999999999987E-2</v>
+        <f t="shared" si="4"/>
+        <v>2.1428571428571415E-2</v>
       </c>
       <c r="G44" s="3">
         <f>1-POWER(1-E44,Donnees!$D$4)</f>
-        <v>0.33239202824490588</v>
+        <v>0.35158861821263243</v>
       </c>
       <c r="H44" s="3">
-        <f t="shared" si="2"/>
-        <v>3.0084957370373568</v>
+        <f t="shared" si="3"/>
+        <v>2.8442331412310504</v>
       </c>
       <c r="I44" s="8">
-        <f>1/(1-POWER(1-$F44*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F44*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>5.7137417013118368</v>
       </c>
       <c r="J44" s="8">
-        <f>1/(1-POWER(1-$F44*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F44*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>47.481600280957529</v>
       </c>
       <c r="K44" s="10">
-        <f>1/(1-POWER(1-$F44*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F44*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.064960983515661</v>
       </c>
       <c r="L44" s="10">
-        <f>1/(1-POWER(1-$F44*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F44*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>77.698299006688089</v>
       </c>
       <c r="M44" s="12">
-        <f>1/(1-POWER(1-$F44*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F44*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>17.640344596567786</v>
       </c>
       <c r="N44" s="12">
-        <f>1/(1-POWER(1-$F44*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F44*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>154.9199827506408</v>
       </c>
       <c r="O44" s="6">
-        <f>1/(1-POWER(1-$F44*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F44*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>51.95809691416796</v>
       </c>
       <c r="P44" s="6">
-        <f>1/(1-POWER(1-$F44*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F44*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="Q44" s="16">
+        <f>1/(1-POWER(1-$F44*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>360.84560105190172</v>
+      </c>
+      <c r="R44" s="16">
+        <f>1/(1-POWER(1-$F44*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3243.8083589698131</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C45" t="s">
-        <v>763</v>
+        <v>342</v>
       </c>
       <c r="D45" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E45" s="3">
-        <f>VLOOKUP(D45,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C45,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>2.1428571428571429E-2</v>
+        <f>VLOOKUP(D45,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C45,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>0.02</v>
       </c>
       <c r="F45" s="3">
-        <f t="shared" si="3"/>
-        <v>2.1428571428571415E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.9999999999999987E-2</v>
       </c>
       <c r="G45" s="3">
         <f>1-POWER(1-E45,Donnees!$D$4)</f>
-        <v>0.35158861821263243</v>
+        <v>0.33239202824490588</v>
       </c>
       <c r="H45" s="3">
-        <f t="shared" si="2"/>
-        <v>2.8442331412310504</v>
+        <f t="shared" si="3"/>
+        <v>3.0084957370373568</v>
       </c>
       <c r="I45" s="8">
-        <f>1/(1-POWER(1-$F45*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>5.6762841299274625</v>
+        <f>1/(1-POWER(1-$F45*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J45" s="8">
-        <f>1/(1-POWER(1-$F45*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>47.143448857901362</v>
+        <f>1/(1-POWER(1-$F45*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K45" s="10">
-        <f>1/(1-POWER(1-$F45*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.126619822082489</v>
+        <f>1/(1-POWER(1-$F45*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L45" s="10">
-        <f>1/(1-POWER(1-$F45*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>78.253846868491379</v>
+        <f>1/(1-POWER(1-$F45*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M45" s="12">
-        <f>1/(1-POWER(1-$F45*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>17.763766692007298</v>
+        <f>1/(1-POWER(1-$F45*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N45" s="12">
-        <f>1/(1-POWER(1-$F45*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>156.03109001607743</v>
+        <f>1/(1-POWER(1-$F45*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O45" s="6">
-        <f>1/(1-POWER(1-$F45*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>52.328455740305785</v>
+        <f>1/(1-POWER(1-$F45*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P45" s="6">
-        <f>1/(1-POWER(1-$F45*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>467.14184480110237</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F45*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q45" s="16">
+        <f>1/(1-POWER(1-$F45*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R45" s="16">
+        <f>1/(1-POWER(1-$F45*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>366</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>764</v>
+        <v>353</v>
+      </c>
+      <c r="C46" t="s">
+        <v>755</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E46" s="3">
-        <f>VLOOKUP(D46,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C46,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>0.02</v>
+        <f>VLOOKUP(D46,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C46,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>2.1428571428571429E-2</v>
       </c>
       <c r="F46" s="3">
-        <f t="shared" si="3"/>
-        <v>1.9999999999999987E-2</v>
+        <f t="shared" si="4"/>
+        <v>2.1428571428571415E-2</v>
       </c>
       <c r="G46" s="3">
         <f>1-POWER(1-E46,Donnees!$D$4)</f>
-        <v>0.33239202824490588</v>
+        <v>0.35158861821263243</v>
       </c>
       <c r="H46" s="3">
-        <f t="shared" si="2"/>
-        <v>3.0084957370373568</v>
+        <f t="shared" si="3"/>
+        <v>2.8442331412310504</v>
       </c>
       <c r="I46" s="8">
-        <f>1/(1-POWER(1-$F46*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F46*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>5.7137417013118368</v>
       </c>
       <c r="J46" s="8">
-        <f>1/(1-POWER(1-$F46*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F46*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>47.481600280957529</v>
       </c>
       <c r="K46" s="10">
-        <f>1/(1-POWER(1-$F46*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F46*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.064960983515661</v>
       </c>
       <c r="L46" s="10">
-        <f>1/(1-POWER(1-$F46*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F46*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>77.698299006688089</v>
       </c>
       <c r="M46" s="12">
-        <f>1/(1-POWER(1-$F46*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F46*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>17.640344596567786</v>
       </c>
       <c r="N46" s="12">
-        <f>1/(1-POWER(1-$F46*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F46*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>154.9199827506408</v>
       </c>
       <c r="O46" s="6">
-        <f>1/(1-POWER(1-$F46*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F46*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>51.95809691416796</v>
       </c>
       <c r="P46" s="6">
-        <f>1/(1-POWER(1-$F46*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F46*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="Q46" s="16">
+        <f>1/(1-POWER(1-$F46*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>360.84560105190172</v>
+      </c>
+      <c r="R46" s="16">
+        <f>1/(1-POWER(1-$F46*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3243.8083589698131</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="C47" t="s">
-        <v>378</v>
+        <v>756</v>
       </c>
       <c r="D47" t="s">
-        <v>305</v>
+        <v>52</v>
       </c>
       <c r="E47" s="3">
-        <f>VLOOKUP(D47,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C47,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>1.8749999999999999E-2</v>
+        <f>VLOOKUP(D47,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C47,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>0.02</v>
       </c>
       <c r="F47" s="3">
-        <f t="shared" si="3"/>
-        <v>1.8749999999999985E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.9999999999999987E-2</v>
       </c>
       <c r="G47" s="3">
         <f>1-POWER(1-E47,Donnees!$D$4)</f>
-        <v>0.31515325639173553</v>
+        <v>0.33239202824490588</v>
       </c>
       <c r="H47" s="3">
-        <f t="shared" si="2"/>
-        <v>3.1730593916408716</v>
+        <f t="shared" si="3"/>
+        <v>3.0084957370373568</v>
       </c>
       <c r="I47" s="8">
-        <f>1/(1-POWER(1-$F47*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.4150060276858722</v>
+        <f>1/(1-POWER(1-$F47*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J47" s="8">
-        <f>1/(1-POWER(1-$F47*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>53.809892648961679</v>
+        <f>1/(1-POWER(1-$F47*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K47" s="10">
-        <f>1/(1-POWER(1-$F47*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>10.359979540057177</v>
+        <f>1/(1-POWER(1-$F47*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L47" s="10">
-        <f>1/(1-POWER(1-$F47*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>89.364824306266769</v>
+        <f>1/(1-POWER(1-$F47*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M47" s="12">
-        <f>1/(1-POWER(1-$F47*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>20.232299777012749</v>
+        <f>1/(1-POWER(1-$F47*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N47" s="12">
-        <f>1/(1-POWER(1-$F47*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>178.25324542143156</v>
+        <f>1/(1-POWER(1-$F47*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O47" s="6">
-        <f>1/(1-POWER(1-$F47*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>59.73566257905977</v>
+        <f>1/(1-POWER(1-$F47*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P47" s="6">
-        <f>1/(1-POWER(1-$F47*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>533.80848919998323</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F47*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q47" s="16">
+        <f>1/(1-POWER(1-$F47*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R47" s="16">
+        <f>1/(1-POWER(1-$F47*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>391</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>392</v>
+        <v>377</v>
+      </c>
+      <c r="C48" t="s">
+        <v>378</v>
       </c>
       <c r="D48" t="s">
-        <v>70</v>
+        <v>305</v>
       </c>
       <c r="E48" s="3">
-        <f>VLOOKUP(D48,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C48,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>2.1428571428571429E-2</v>
+        <f>VLOOKUP(D48,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C48,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>1.8749999999999999E-2</v>
       </c>
       <c r="F48" s="3">
-        <f t="shared" si="3"/>
-        <v>2.1428571428571415E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.8749999999999985E-2</v>
       </c>
       <c r="G48" s="3">
         <f>1-POWER(1-E48,Donnees!$D$4)</f>
-        <v>0.35158861821263243</v>
+        <v>0.31515325639173553</v>
       </c>
       <c r="H48" s="3">
-        <f t="shared" si="2"/>
-        <v>2.8442331412310504</v>
+        <f t="shared" si="3"/>
+        <v>3.1730593916408716</v>
       </c>
       <c r="I48" s="8">
-        <f>1/(1-POWER(1-$F48*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>5.6762841299274625</v>
+        <f>1/(1-POWER(1-$F48*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.4578458934330172</v>
       </c>
       <c r="J48" s="8">
-        <f>1/(1-POWER(1-$F48*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>47.143448857901362</v>
+        <f>1/(1-POWER(1-$F48*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>54.196354855722817</v>
       </c>
       <c r="K48" s="10">
-        <f>1/(1-POWER(1-$F48*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.126619822082489</v>
+        <f>1/(1-POWER(1-$F48*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>10.289493630089176</v>
       </c>
       <c r="L48" s="10">
-        <f>1/(1-POWER(1-$F48*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>78.253846868491379</v>
+        <f>1/(1-POWER(1-$F48*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>88.729910402846656</v>
       </c>
       <c r="M48" s="12">
-        <f>1/(1-POWER(1-$F48*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>17.763766692007298</v>
+        <f>1/(1-POWER(1-$F48*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>20.091236650595796</v>
       </c>
       <c r="N48" s="12">
-        <f>1/(1-POWER(1-$F48*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>156.03109001607743</v>
+        <f>1/(1-POWER(1-$F48*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>176.98340751640595</v>
       </c>
       <c r="O48" s="6">
-        <f>1/(1-POWER(1-$F48*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>52.328455740305785</v>
+        <f>1/(1-POWER(1-$F48*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>59.312392255803132</v>
       </c>
       <c r="P48" s="6">
-        <f>1/(1-POWER(1-$F48*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>467.14184480110237</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F48*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>529.99896651203778</v>
+      </c>
+      <c r="Q48" s="16">
+        <f>1/(1-POWER(1-$F48*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>412.3270536965432</v>
+      </c>
+      <c r="R48" s="16">
+        <f>1/(1-POWER(1-$F48*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3707.1416890942214</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C49" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="D49" t="s">
         <v>70</v>
       </c>
       <c r="E49" s="3">
-        <f>VLOOKUP(D49,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C49,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D49,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C49,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F49" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G49" s="3">
@@ -12526,123 +12739,139 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H49" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I49" s="8">
-        <f>1/(1-POWER(1-$F49*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>5.6762841299274625</v>
+        <f>1/(1-POWER(1-$F49*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>5.7137417013118368</v>
       </c>
       <c r="J49" s="8">
-        <f>1/(1-POWER(1-$F49*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>47.143448857901362</v>
+        <f>1/(1-POWER(1-$F49*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>47.481600280957529</v>
       </c>
       <c r="K49" s="10">
-        <f>1/(1-POWER(1-$F49*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.126619822082489</v>
+        <f>1/(1-POWER(1-$F49*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.064960983515661</v>
       </c>
       <c r="L49" s="10">
-        <f>1/(1-POWER(1-$F49*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>78.253846868491379</v>
+        <f>1/(1-POWER(1-$F49*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>77.698299006688089</v>
       </c>
       <c r="M49" s="12">
-        <f>1/(1-POWER(1-$F49*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>17.763766692007298</v>
+        <f>1/(1-POWER(1-$F49*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>17.640344596567786</v>
       </c>
       <c r="N49" s="12">
-        <f>1/(1-POWER(1-$F49*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>156.03109001607743</v>
+        <f>1/(1-POWER(1-$F49*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>154.9199827506408</v>
       </c>
       <c r="O49" s="6">
-        <f>1/(1-POWER(1-$F49*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>52.328455740305785</v>
+        <f>1/(1-POWER(1-$F49*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>51.95809691416796</v>
       </c>
       <c r="P49" s="6">
-        <f>1/(1-POWER(1-$F49*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>467.14184480110237</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F49*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="Q49" s="16">
+        <f>1/(1-POWER(1-$F49*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>360.84560105190172</v>
+      </c>
+      <c r="R49" s="16">
+        <f>1/(1-POWER(1-$F49*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3243.8083589698131</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>410</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>411</v>
+        <v>400</v>
+      </c>
+      <c r="C50" t="s">
+        <v>401</v>
       </c>
       <c r="D50" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E50" s="3">
-        <f>VLOOKUP(D50,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C50,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>0.02</v>
+        <f>VLOOKUP(D50,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C50,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>2.1428571428571429E-2</v>
       </c>
       <c r="F50" s="3">
-        <f t="shared" si="3"/>
-        <v>1.9999999999999987E-2</v>
+        <f t="shared" si="4"/>
+        <v>2.1428571428571415E-2</v>
       </c>
       <c r="G50" s="3">
         <f>1-POWER(1-E50,Donnees!$D$4)</f>
-        <v>0.33239202824490588</v>
+        <v>0.35158861821263243</v>
       </c>
       <c r="H50" s="3">
-        <f t="shared" si="2"/>
-        <v>3.0084957370373568</v>
+        <f t="shared" si="3"/>
+        <v>2.8442331412310504</v>
       </c>
       <c r="I50" s="8">
-        <f>1/(1-POWER(1-$F50*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F50*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>5.7137417013118368</v>
       </c>
       <c r="J50" s="8">
-        <f>1/(1-POWER(1-$F50*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F50*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>47.481600280957529</v>
       </c>
       <c r="K50" s="10">
-        <f>1/(1-POWER(1-$F50*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F50*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.064960983515661</v>
       </c>
       <c r="L50" s="10">
-        <f>1/(1-POWER(1-$F50*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F50*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>77.698299006688089</v>
       </c>
       <c r="M50" s="12">
-        <f>1/(1-POWER(1-$F50*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F50*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>17.640344596567786</v>
       </c>
       <c r="N50" s="12">
-        <f>1/(1-POWER(1-$F50*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F50*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>154.9199827506408</v>
       </c>
       <c r="O50" s="6">
-        <f>1/(1-POWER(1-$F50*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F50*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>51.95809691416796</v>
       </c>
       <c r="P50" s="6">
-        <f>1/(1-POWER(1-$F50*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F50*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="Q50" s="16">
+        <f>1/(1-POWER(1-$F50*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>360.84560105190172</v>
+      </c>
+      <c r="R50" s="16">
+        <f>1/(1-POWER(1-$F50*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3243.8083589698131</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C51" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="D51" t="s">
         <v>52</v>
       </c>
       <c r="E51" s="3">
-        <f>VLOOKUP(D51,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C51,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D51,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C51,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>0.02</v>
       </c>
       <c r="F51" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G51" s="3">
@@ -12650,61 +12879,69 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H51" s="3">
-        <f t="shared" ref="H51:H68" si="4">1/G51</f>
+        <f t="shared" si="3"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I51" s="8">
-        <f>1/(1-POWER(1-$F51*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F51*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J51" s="8">
-        <f>1/(1-POWER(1-$F51*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F51*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K51" s="10">
-        <f>1/(1-POWER(1-$F51*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F51*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L51" s="10">
-        <f>1/(1-POWER(1-$F51*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F51*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M51" s="12">
-        <f>1/(1-POWER(1-$F51*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F51*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N51" s="12">
-        <f>1/(1-POWER(1-$F51*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F51*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O51" s="6">
-        <f>1/(1-POWER(1-$F51*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F51*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P51" s="6">
-        <f>1/(1-POWER(1-$F51*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F51*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q51" s="16">
+        <f>1/(1-POWER(1-$F51*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R51" s="16">
+        <f>1/(1-POWER(1-$F51*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>430</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>770</v>
+        <v>420</v>
+      </c>
+      <c r="C52" t="s">
+        <v>421</v>
       </c>
       <c r="D52" t="s">
         <v>52</v>
       </c>
       <c r="E52" s="3">
-        <f>VLOOKUP(D52,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C52,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D52,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C52,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>0.02</v>
       </c>
       <c r="F52" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G52" s="3">
@@ -12712,61 +12949,69 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H52" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="H52:H69" si="5">1/G52</f>
         <v>3.0084957370373568</v>
       </c>
       <c r="I52" s="8">
-        <f>1/(1-POWER(1-$F52*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F52*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J52" s="8">
-        <f>1/(1-POWER(1-$F52*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F52*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K52" s="10">
-        <f>1/(1-POWER(1-$F52*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F52*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L52" s="10">
-        <f>1/(1-POWER(1-$F52*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F52*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M52" s="12">
-        <f>1/(1-POWER(1-$F52*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F52*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N52" s="12">
-        <f>1/(1-POWER(1-$F52*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F52*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O52" s="6">
-        <f>1/(1-POWER(1-$F52*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F52*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P52" s="6">
-        <f>1/(1-POWER(1-$F52*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F52*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q52" s="16">
+        <f>1/(1-POWER(1-$F52*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R52" s="16">
+        <f>1/(1-POWER(1-$F52*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>47</v>
       </c>
       <c r="B53" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C53" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
       <c r="D53" t="s">
         <v>52</v>
       </c>
       <c r="E53" s="3">
-        <f>VLOOKUP(D53,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C53,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D53,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C53,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>0.02</v>
       </c>
       <c r="F53" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G53" s="3">
@@ -12774,247 +13019,279 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H53" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I53" s="8">
-        <f>1/(1-POWER(1-$F53*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F53*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J53" s="8">
-        <f>1/(1-POWER(1-$F53*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F53*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K53" s="10">
-        <f>1/(1-POWER(1-$F53*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F53*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L53" s="10">
-        <f>1/(1-POWER(1-$F53*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F53*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M53" s="12">
-        <f>1/(1-POWER(1-$F53*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F53*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N53" s="12">
-        <f>1/(1-POWER(1-$F53*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F53*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O53" s="6">
-        <f>1/(1-POWER(1-$F53*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F53*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P53" s="6">
-        <f>1/(1-POWER(1-$F53*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F53*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q53" s="16">
+        <f>1/(1-POWER(1-$F53*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R53" s="16">
+        <f>1/(1-POWER(1-$F53*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>47</v>
       </c>
       <c r="B54" t="s">
-        <v>453</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>454</v>
+        <v>442</v>
+      </c>
+      <c r="C54" t="s">
+        <v>764</v>
       </c>
       <c r="D54" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E54" s="3">
-        <f>VLOOKUP(D54,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C54,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>2.1428571428571429E-2</v>
+        <f>VLOOKUP(D54,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C54,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>0.02</v>
       </c>
       <c r="F54" s="3">
-        <f t="shared" si="3"/>
-        <v>2.1428571428571415E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.9999999999999987E-2</v>
       </c>
       <c r="G54" s="3">
         <f>1-POWER(1-E54,Donnees!$D$4)</f>
-        <v>0.35158861821263243</v>
+        <v>0.33239202824490588</v>
       </c>
       <c r="H54" s="3">
-        <f t="shared" si="4"/>
-        <v>2.8442331412310504</v>
+        <f t="shared" si="5"/>
+        <v>3.0084957370373568</v>
       </c>
       <c r="I54" s="8">
-        <f>1/(1-POWER(1-$F54*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>5.6762841299274625</v>
+        <f>1/(1-POWER(1-$F54*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J54" s="8">
-        <f>1/(1-POWER(1-$F54*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>47.143448857901362</v>
+        <f>1/(1-POWER(1-$F54*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K54" s="10">
-        <f>1/(1-POWER(1-$F54*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.126619822082489</v>
+        <f>1/(1-POWER(1-$F54*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L54" s="10">
-        <f>1/(1-POWER(1-$F54*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>78.253846868491379</v>
+        <f>1/(1-POWER(1-$F54*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M54" s="12">
-        <f>1/(1-POWER(1-$F54*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>17.763766692007298</v>
+        <f>1/(1-POWER(1-$F54*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N54" s="12">
-        <f>1/(1-POWER(1-$F54*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>156.03109001607743</v>
+        <f>1/(1-POWER(1-$F54*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O54" s="6">
-        <f>1/(1-POWER(1-$F54*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>52.328455740305785</v>
+        <f>1/(1-POWER(1-$F54*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P54" s="6">
-        <f>1/(1-POWER(1-$F54*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>467.14184480110237</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F54*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q54" s="16">
+        <f>1/(1-POWER(1-$F54*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R54" s="16">
+        <f>1/(1-POWER(1-$F54*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>47</v>
       </c>
       <c r="B55" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="C55" t="s">
-        <v>775</v>
+        <v>454</v>
       </c>
       <c r="D55" t="s">
-        <v>305</v>
+        <v>70</v>
       </c>
       <c r="E55" s="3">
-        <f>VLOOKUP(D55,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C55,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>1.8749999999999999E-2</v>
+        <f>VLOOKUP(D55,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C55,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>2.1428571428571429E-2</v>
       </c>
       <c r="F55" s="3">
-        <f t="shared" si="3"/>
-        <v>1.8749999999999985E-2</v>
+        <f t="shared" si="4"/>
+        <v>2.1428571428571415E-2</v>
       </c>
       <c r="G55" s="3">
         <f>1-POWER(1-E55,Donnees!$D$4)</f>
-        <v>0.31515325639173553</v>
+        <v>0.35158861821263243</v>
       </c>
       <c r="H55" s="3">
-        <f t="shared" si="4"/>
-        <v>3.1730593916408716</v>
+        <f t="shared" si="5"/>
+        <v>2.8442331412310504</v>
       </c>
       <c r="I55" s="8">
-        <f>1/(1-POWER(1-$F55*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.4150060276858722</v>
+        <f>1/(1-POWER(1-$F55*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>5.7137417013118368</v>
       </c>
       <c r="J55" s="8">
-        <f>1/(1-POWER(1-$F55*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>53.809892648961679</v>
+        <f>1/(1-POWER(1-$F55*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>47.481600280957529</v>
       </c>
       <c r="K55" s="10">
-        <f>1/(1-POWER(1-$F55*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>10.359979540057177</v>
+        <f>1/(1-POWER(1-$F55*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.064960983515661</v>
       </c>
       <c r="L55" s="10">
-        <f>1/(1-POWER(1-$F55*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>89.364824306266769</v>
+        <f>1/(1-POWER(1-$F55*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>77.698299006688089</v>
       </c>
       <c r="M55" s="12">
-        <f>1/(1-POWER(1-$F55*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>20.232299777012749</v>
+        <f>1/(1-POWER(1-$F55*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>17.640344596567786</v>
       </c>
       <c r="N55" s="12">
-        <f>1/(1-POWER(1-$F55*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>178.25324542143156</v>
+        <f>1/(1-POWER(1-$F55*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>154.9199827506408</v>
       </c>
       <c r="O55" s="6">
-        <f>1/(1-POWER(1-$F55*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>59.73566257905977</v>
+        <f>1/(1-POWER(1-$F55*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>51.95809691416796</v>
       </c>
       <c r="P55" s="6">
-        <f>1/(1-POWER(1-$F55*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>533.80848919998323</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F55*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="Q55" s="16">
+        <f>1/(1-POWER(1-$F55*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>360.84560105190172</v>
+      </c>
+      <c r="R55" s="16">
+        <f>1/(1-POWER(1-$F55*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3243.8083589698131</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>47</v>
       </c>
       <c r="B56" t="s">
-        <v>475</v>
-      </c>
-      <c r="C56" s="16" t="s">
-        <v>476</v>
+        <v>464</v>
+      </c>
+      <c r="C56" t="s">
+        <v>767</v>
       </c>
       <c r="D56" t="s">
-        <v>70</v>
+        <v>305</v>
       </c>
       <c r="E56" s="3">
-        <f>VLOOKUP(D56,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C56,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>2.1428571428571429E-2</v>
+        <f>VLOOKUP(D56,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C56,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>1.8749999999999999E-2</v>
       </c>
       <c r="F56" s="3">
-        <f t="shared" si="3"/>
-        <v>2.1428571428571415E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.8749999999999985E-2</v>
       </c>
       <c r="G56" s="3">
         <f>1-POWER(1-E56,Donnees!$D$4)</f>
-        <v>0.35158861821263243</v>
+        <v>0.31515325639173553</v>
       </c>
       <c r="H56" s="3">
-        <f t="shared" si="4"/>
-        <v>2.8442331412310504</v>
+        <f t="shared" si="5"/>
+        <v>3.1730593916408716</v>
       </c>
       <c r="I56" s="8">
-        <f>1/(1-POWER(1-$F56*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>5.6762841299274625</v>
+        <f>1/(1-POWER(1-$F56*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.4578458934330172</v>
       </c>
       <c r="J56" s="8">
-        <f>1/(1-POWER(1-$F56*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>47.143448857901362</v>
+        <f>1/(1-POWER(1-$F56*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>54.196354855722817</v>
       </c>
       <c r="K56" s="10">
-        <f>1/(1-POWER(1-$F56*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.126619822082489</v>
+        <f>1/(1-POWER(1-$F56*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>10.289493630089176</v>
       </c>
       <c r="L56" s="10">
-        <f>1/(1-POWER(1-$F56*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>78.253846868491379</v>
+        <f>1/(1-POWER(1-$F56*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>88.729910402846656</v>
       </c>
       <c r="M56" s="12">
-        <f>1/(1-POWER(1-$F56*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>17.763766692007298</v>
+        <f>1/(1-POWER(1-$F56*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>20.091236650595796</v>
       </c>
       <c r="N56" s="12">
-        <f>1/(1-POWER(1-$F56*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>156.03109001607743</v>
+        <f>1/(1-POWER(1-$F56*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>176.98340751640595</v>
       </c>
       <c r="O56" s="6">
-        <f>1/(1-POWER(1-$F56*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>52.328455740305785</v>
+        <f>1/(1-POWER(1-$F56*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>59.312392255803132</v>
       </c>
       <c r="P56" s="6">
-        <f>1/(1-POWER(1-$F56*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>467.14184480110237</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F56*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>529.99896651203778</v>
+      </c>
+      <c r="Q56" s="16">
+        <f>1/(1-POWER(1-$F56*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>412.3270536965432</v>
+      </c>
+      <c r="R56" s="16">
+        <f>1/(1-POWER(1-$F56*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3707.1416890942214</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>47</v>
       </c>
       <c r="B57" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="C57" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="D57" t="s">
         <v>70</v>
       </c>
       <c r="E57" s="3">
-        <f>VLOOKUP(D57,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C57,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D57,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C57,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F57" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G57" s="3">
@@ -13022,123 +13299,139 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H57" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I57" s="8">
-        <f>1/(1-POWER(1-$F57*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>5.6762841299274625</v>
+        <f>1/(1-POWER(1-$F57*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>5.7137417013118368</v>
       </c>
       <c r="J57" s="8">
-        <f>1/(1-POWER(1-$F57*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>47.143448857901362</v>
+        <f>1/(1-POWER(1-$F57*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>47.481600280957529</v>
       </c>
       <c r="K57" s="10">
-        <f>1/(1-POWER(1-$F57*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.126619822082489</v>
+        <f>1/(1-POWER(1-$F57*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.064960983515661</v>
       </c>
       <c r="L57" s="10">
-        <f>1/(1-POWER(1-$F57*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>78.253846868491379</v>
+        <f>1/(1-POWER(1-$F57*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>77.698299006688089</v>
       </c>
       <c r="M57" s="12">
-        <f>1/(1-POWER(1-$F57*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>17.763766692007298</v>
+        <f>1/(1-POWER(1-$F57*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>17.640344596567786</v>
       </c>
       <c r="N57" s="12">
-        <f>1/(1-POWER(1-$F57*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>156.03109001607743</v>
+        <f>1/(1-POWER(1-$F57*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>154.9199827506408</v>
       </c>
       <c r="O57" s="6">
-        <f>1/(1-POWER(1-$F57*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>52.328455740305785</v>
+        <f>1/(1-POWER(1-$F57*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>51.95809691416796</v>
       </c>
       <c r="P57" s="6">
-        <f>1/(1-POWER(1-$F57*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>467.14184480110237</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F57*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="Q57" s="16">
+        <f>1/(1-POWER(1-$F57*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>360.84560105190172</v>
+      </c>
+      <c r="R57" s="16">
+        <f>1/(1-POWER(1-$F57*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3243.8083589698131</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>47</v>
       </c>
       <c r="B58" t="s">
-        <v>499</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>500</v>
+        <v>487</v>
+      </c>
+      <c r="C58" t="s">
+        <v>488</v>
       </c>
       <c r="D58" t="s">
-        <v>305</v>
+        <v>70</v>
       </c>
       <c r="E58" s="3">
-        <f>VLOOKUP(D58,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C58,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>1.8749999999999999E-2</v>
+        <f>VLOOKUP(D58,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C58,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>2.1428571428571429E-2</v>
       </c>
       <c r="F58" s="3">
-        <f t="shared" si="3"/>
-        <v>1.8749999999999985E-2</v>
+        <f t="shared" si="4"/>
+        <v>2.1428571428571415E-2</v>
       </c>
       <c r="G58" s="3">
         <f>1-POWER(1-E58,Donnees!$D$4)</f>
-        <v>0.31515325639173553</v>
+        <v>0.35158861821263243</v>
       </c>
       <c r="H58" s="3">
-        <f t="shared" si="4"/>
-        <v>3.1730593916408716</v>
+        <f t="shared" si="5"/>
+        <v>2.8442331412310504</v>
       </c>
       <c r="I58" s="8">
-        <f>1/(1-POWER(1-$F58*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.4150060276858722</v>
+        <f>1/(1-POWER(1-$F58*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>5.7137417013118368</v>
       </c>
       <c r="J58" s="8">
-        <f>1/(1-POWER(1-$F58*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>53.809892648961679</v>
+        <f>1/(1-POWER(1-$F58*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>47.481600280957529</v>
       </c>
       <c r="K58" s="10">
-        <f>1/(1-POWER(1-$F58*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>10.359979540057177</v>
+        <f>1/(1-POWER(1-$F58*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.064960983515661</v>
       </c>
       <c r="L58" s="10">
-        <f>1/(1-POWER(1-$F58*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>89.364824306266769</v>
+        <f>1/(1-POWER(1-$F58*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>77.698299006688089</v>
       </c>
       <c r="M58" s="12">
-        <f>1/(1-POWER(1-$F58*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>20.232299777012749</v>
+        <f>1/(1-POWER(1-$F58*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>17.640344596567786</v>
       </c>
       <c r="N58" s="12">
-        <f>1/(1-POWER(1-$F58*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>178.25324542143156</v>
+        <f>1/(1-POWER(1-$F58*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>154.9199827506408</v>
       </c>
       <c r="O58" s="6">
-        <f>1/(1-POWER(1-$F58*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>59.73566257905977</v>
+        <f>1/(1-POWER(1-$F58*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>51.95809691416796</v>
       </c>
       <c r="P58" s="6">
-        <f>1/(1-POWER(1-$F58*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>533.80848919998323</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F58*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>463.80851274980165</v>
+      </c>
+      <c r="Q58" s="16">
+        <f>1/(1-POWER(1-$F58*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>360.84560105190172</v>
+      </c>
+      <c r="R58" s="16">
+        <f>1/(1-POWER(1-$F58*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3243.8083589698131</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>47</v>
       </c>
       <c r="B59" t="s">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="C59" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="D59" t="s">
         <v>305</v>
       </c>
       <c r="E59" s="3">
-        <f>VLOOKUP(D59,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C59,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D59,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C59,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>1.8749999999999999E-2</v>
       </c>
       <c r="F59" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.8749999999999985E-2</v>
       </c>
       <c r="G59" s="3">
@@ -13146,61 +13439,69 @@
         <v>0.31515325639173553</v>
       </c>
       <c r="H59" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.1730593916408716</v>
       </c>
       <c r="I59" s="8">
-        <f>1/(1-POWER(1-$F59*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.4150060276858722</v>
+        <f>1/(1-POWER(1-$F59*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.4578458934330172</v>
       </c>
       <c r="J59" s="8">
-        <f>1/(1-POWER(1-$F59*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>53.809892648961679</v>
+        <f>1/(1-POWER(1-$F59*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>54.196354855722817</v>
       </c>
       <c r="K59" s="10">
-        <f>1/(1-POWER(1-$F59*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>10.359979540057177</v>
+        <f>1/(1-POWER(1-$F59*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>10.289493630089176</v>
       </c>
       <c r="L59" s="10">
-        <f>1/(1-POWER(1-$F59*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>89.364824306266769</v>
+        <f>1/(1-POWER(1-$F59*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>88.729910402846656</v>
       </c>
       <c r="M59" s="12">
-        <f>1/(1-POWER(1-$F59*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>20.232299777012749</v>
+        <f>1/(1-POWER(1-$F59*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>20.091236650595796</v>
       </c>
       <c r="N59" s="12">
-        <f>1/(1-POWER(1-$F59*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>178.25324542143156</v>
+        <f>1/(1-POWER(1-$F59*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>176.98340751640595</v>
       </c>
       <c r="O59" s="6">
-        <f>1/(1-POWER(1-$F59*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>59.73566257905977</v>
+        <f>1/(1-POWER(1-$F59*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>59.312392255803132</v>
       </c>
       <c r="P59" s="6">
-        <f>1/(1-POWER(1-$F59*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>533.80848919998323</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F59*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>529.99896651203778</v>
+      </c>
+      <c r="Q59" s="16">
+        <f>1/(1-POWER(1-$F59*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>412.3270536965432</v>
+      </c>
+      <c r="R59" s="16">
+        <f>1/(1-POWER(1-$F59*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3707.1416890942214</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>47</v>
       </c>
       <c r="B60" t="s">
-        <v>527</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>528</v>
+        <v>513</v>
+      </c>
+      <c r="C60" t="s">
+        <v>514</v>
       </c>
       <c r="D60" t="s">
         <v>305</v>
       </c>
       <c r="E60" s="3">
-        <f>VLOOKUP(D60,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C60,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D60,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C60,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>1.8749999999999999E-2</v>
       </c>
       <c r="F60" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.8749999999999985E-2</v>
       </c>
       <c r="G60" s="3">
@@ -13208,247 +13509,279 @@
         <v>0.31515325639173553</v>
       </c>
       <c r="H60" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.1730593916408716</v>
       </c>
       <c r="I60" s="8">
-        <f>1/(1-POWER(1-$F60*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.4150060276858722</v>
+        <f>1/(1-POWER(1-$F60*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.4578458934330172</v>
       </c>
       <c r="J60" s="8">
-        <f>1/(1-POWER(1-$F60*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>53.809892648961679</v>
+        <f>1/(1-POWER(1-$F60*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>54.196354855722817</v>
       </c>
       <c r="K60" s="10">
-        <f>1/(1-POWER(1-$F60*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>10.359979540057177</v>
+        <f>1/(1-POWER(1-$F60*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>10.289493630089176</v>
       </c>
       <c r="L60" s="10">
-        <f>1/(1-POWER(1-$F60*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>89.364824306266769</v>
+        <f>1/(1-POWER(1-$F60*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>88.729910402846656</v>
       </c>
       <c r="M60" s="12">
-        <f>1/(1-POWER(1-$F60*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>20.232299777012749</v>
+        <f>1/(1-POWER(1-$F60*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>20.091236650595796</v>
       </c>
       <c r="N60" s="12">
-        <f>1/(1-POWER(1-$F60*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>178.25324542143156</v>
+        <f>1/(1-POWER(1-$F60*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>176.98340751640595</v>
       </c>
       <c r="O60" s="6">
-        <f>1/(1-POWER(1-$F60*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>59.73566257905977</v>
+        <f>1/(1-POWER(1-$F60*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>59.312392255803132</v>
       </c>
       <c r="P60" s="6">
-        <f>1/(1-POWER(1-$F60*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>533.80848919998323</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F60*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>529.99896651203778</v>
+      </c>
+      <c r="Q60" s="16">
+        <f>1/(1-POWER(1-$F60*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>412.3270536965432</v>
+      </c>
+      <c r="R60" s="16">
+        <f>1/(1-POWER(1-$F60*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3707.1416890942214</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>47</v>
       </c>
       <c r="B61" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="C61" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="D61" t="s">
-        <v>52</v>
+        <v>305</v>
       </c>
       <c r="E61" s="3">
-        <f>VLOOKUP(D61,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C61,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>0.02</v>
+        <f>VLOOKUP(D61,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C61,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>1.8749999999999999E-2</v>
       </c>
       <c r="F61" s="3">
-        <f t="shared" si="3"/>
-        <v>1.9999999999999987E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.8749999999999985E-2</v>
       </c>
       <c r="G61" s="3">
         <f>1-POWER(1-E61,Donnees!$D$4)</f>
-        <v>0.33239202824490588</v>
+        <v>0.31515325639173553</v>
       </c>
       <c r="H61" s="3">
-        <f t="shared" si="4"/>
-        <v>3.0084957370373568</v>
+        <f t="shared" si="5"/>
+        <v>3.1730593916408716</v>
       </c>
       <c r="I61" s="8">
-        <f>1/(1-POWER(1-$F61*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F61*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.4578458934330172</v>
       </c>
       <c r="J61" s="8">
-        <f>1/(1-POWER(1-$F61*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F61*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>54.196354855722817</v>
       </c>
       <c r="K61" s="10">
-        <f>1/(1-POWER(1-$F61*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F61*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>10.289493630089176</v>
       </c>
       <c r="L61" s="10">
-        <f>1/(1-POWER(1-$F61*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F61*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>88.729910402846656</v>
       </c>
       <c r="M61" s="12">
-        <f>1/(1-POWER(1-$F61*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F61*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>20.091236650595796</v>
       </c>
       <c r="N61" s="12">
-        <f>1/(1-POWER(1-$F61*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F61*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>176.98340751640595</v>
       </c>
       <c r="O61" s="6">
-        <f>1/(1-POWER(1-$F61*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F61*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>59.312392255803132</v>
       </c>
       <c r="P61" s="6">
-        <f>1/(1-POWER(1-$F61*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F61*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>529.99896651203778</v>
+      </c>
+      <c r="Q61" s="16">
+        <f>1/(1-POWER(1-$F61*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>412.3270536965432</v>
+      </c>
+      <c r="R61" s="16">
+        <f>1/(1-POWER(1-$F61*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3707.1416890942214</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>47</v>
       </c>
       <c r="B62" t="s">
-        <v>549</v>
-      </c>
-      <c r="C62" s="16" t="s">
-        <v>779</v>
+        <v>539</v>
+      </c>
+      <c r="C62" t="s">
+        <v>540</v>
       </c>
       <c r="D62" t="s">
-        <v>305</v>
+        <v>52</v>
       </c>
       <c r="E62" s="3">
-        <f>VLOOKUP(D62,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C62,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>1.8749999999999999E-2</v>
+        <f>VLOOKUP(D62,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C62,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>0.02</v>
       </c>
       <c r="F62" s="3">
-        <f t="shared" si="3"/>
-        <v>1.8749999999999985E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.9999999999999987E-2</v>
       </c>
       <c r="G62" s="3">
         <f>1-POWER(1-E62,Donnees!$D$4)</f>
-        <v>0.31515325639173553</v>
+        <v>0.33239202824490588</v>
       </c>
       <c r="H62" s="3">
-        <f t="shared" si="4"/>
-        <v>3.1730593916408716</v>
+        <f t="shared" si="5"/>
+        <v>3.0084957370373568</v>
       </c>
       <c r="I62" s="8">
-        <f>1/(1-POWER(1-$F62*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.4150060276858722</v>
+        <f>1/(1-POWER(1-$F62*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J62" s="8">
-        <f>1/(1-POWER(1-$F62*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>53.809892648961679</v>
+        <f>1/(1-POWER(1-$F62*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K62" s="10">
-        <f>1/(1-POWER(1-$F62*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>10.359979540057177</v>
+        <f>1/(1-POWER(1-$F62*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L62" s="10">
-        <f>1/(1-POWER(1-$F62*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>89.364824306266769</v>
+        <f>1/(1-POWER(1-$F62*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M62" s="12">
-        <f>1/(1-POWER(1-$F62*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>20.232299777012749</v>
+        <f>1/(1-POWER(1-$F62*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N62" s="12">
-        <f>1/(1-POWER(1-$F62*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>178.25324542143156</v>
+        <f>1/(1-POWER(1-$F62*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O62" s="6">
-        <f>1/(1-POWER(1-$F62*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>59.73566257905977</v>
+        <f>1/(1-POWER(1-$F62*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P62" s="6">
-        <f>1/(1-POWER(1-$F62*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>533.80848919998323</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F62*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q62" s="16">
+        <f>1/(1-POWER(1-$F62*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R62" s="16">
+        <f>1/(1-POWER(1-$F62*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>47</v>
       </c>
       <c r="B63" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="C63" t="s">
-        <v>146</v>
+        <v>771</v>
       </c>
       <c r="D63" t="s">
-        <v>52</v>
+        <v>305</v>
       </c>
       <c r="E63" s="3">
-        <f>VLOOKUP(D63,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C63,Table1[name],Table1[cardRarityMultiplier])</f>
-        <v>0.02</v>
+        <f>VLOOKUP(D63,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C63,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>1.8749999999999999E-2</v>
       </c>
       <c r="F63" s="3">
-        <f t="shared" si="3"/>
-        <v>1.9999999999999987E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.8749999999999985E-2</v>
       </c>
       <c r="G63" s="3">
         <f>1-POWER(1-E63,Donnees!$D$4)</f>
-        <v>0.33239202824490588</v>
+        <v>0.31515325639173553</v>
       </c>
       <c r="H63" s="3">
-        <f t="shared" si="4"/>
-        <v>3.0084957370373568</v>
+        <f t="shared" si="5"/>
+        <v>3.1730593916408716</v>
       </c>
       <c r="I63" s="8">
-        <f>1/(1-POWER(1-$F63*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F63*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.4578458934330172</v>
       </c>
       <c r="J63" s="8">
-        <f>1/(1-POWER(1-$F63*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F63*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>54.196354855722817</v>
       </c>
       <c r="K63" s="10">
-        <f>1/(1-POWER(1-$F63*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F63*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>10.289493630089176</v>
       </c>
       <c r="L63" s="10">
-        <f>1/(1-POWER(1-$F63*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F63*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>88.729910402846656</v>
       </c>
       <c r="M63" s="12">
-        <f>1/(1-POWER(1-$F63*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F63*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>20.091236650595796</v>
       </c>
       <c r="N63" s="12">
-        <f>1/(1-POWER(1-$F63*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F63*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>176.98340751640595</v>
       </c>
       <c r="O63" s="6">
-        <f>1/(1-POWER(1-$F63*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F63*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>59.312392255803132</v>
       </c>
       <c r="P63" s="6">
-        <f>1/(1-POWER(1-$F63*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F63*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>529.99896651203778</v>
+      </c>
+      <c r="Q63" s="16">
+        <f>1/(1-POWER(1-$F63*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>412.3270536965432</v>
+      </c>
+      <c r="R63" s="16">
+        <f>1/(1-POWER(1-$F63*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3707.1416890942214</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>47</v>
       </c>
       <c r="B64" t="s">
-        <v>568</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>781</v>
+        <v>559</v>
+      </c>
+      <c r="C64" t="s">
+        <v>146</v>
       </c>
       <c r="D64" t="s">
         <v>52</v>
       </c>
       <c r="E64" s="3">
-        <f>VLOOKUP(D64,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C64,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D64,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C64,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>0.02</v>
       </c>
       <c r="F64" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G64" s="3">
@@ -13456,61 +13789,69 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H64" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I64" s="8">
-        <f>1/(1-POWER(1-$F64*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F64*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J64" s="8">
-        <f>1/(1-POWER(1-$F64*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F64*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K64" s="10">
-        <f>1/(1-POWER(1-$F64*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F64*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L64" s="10">
-        <f>1/(1-POWER(1-$F64*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F64*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M64" s="12">
-        <f>1/(1-POWER(1-$F64*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F64*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N64" s="12">
-        <f>1/(1-POWER(1-$F64*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F64*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O64" s="6">
-        <f>1/(1-POWER(1-$F64*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F64*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P64" s="6">
-        <f>1/(1-POWER(1-$F64*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F64*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q64" s="16">
+        <f>1/(1-POWER(1-$F64*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R64" s="16">
+        <f>1/(1-POWER(1-$F64*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>47</v>
       </c>
       <c r="B65" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="C65" t="s">
-        <v>783</v>
+        <v>773</v>
       </c>
       <c r="D65" t="s">
         <v>52</v>
       </c>
       <c r="E65" s="3">
-        <f>VLOOKUP(D65,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C65,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D65,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C65,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>0.02</v>
       </c>
       <c r="F65" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G65" s="3">
@@ -13518,61 +13859,69 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H65" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I65" s="8">
-        <f>1/(1-POWER(1-$F65*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F65*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J65" s="8">
-        <f>1/(1-POWER(1-$F65*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F65*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K65" s="10">
-        <f>1/(1-POWER(1-$F65*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F65*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L65" s="10">
-        <f>1/(1-POWER(1-$F65*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F65*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M65" s="12">
-        <f>1/(1-POWER(1-$F65*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F65*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N65" s="12">
-        <f>1/(1-POWER(1-$F65*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F65*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O65" s="6">
-        <f>1/(1-POWER(1-$F65*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F65*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P65" s="6">
-        <f>1/(1-POWER(1-$F65*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F65*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q65" s="16">
+        <f>1/(1-POWER(1-$F65*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R65" s="16">
+        <f>1/(1-POWER(1-$F65*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>47</v>
       </c>
       <c r="B66" t="s">
-        <v>580</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>784</v>
+        <v>574</v>
+      </c>
+      <c r="C66" t="s">
+        <v>775</v>
       </c>
       <c r="D66" t="s">
         <v>52</v>
       </c>
       <c r="E66" s="3">
-        <f>VLOOKUP(D66,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C66,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D66,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C66,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>0.02</v>
       </c>
       <c r="F66" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G66" s="3">
@@ -13580,61 +13929,69 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H66" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I66" s="8">
-        <f>1/(1-POWER(1-$F66*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F66*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J66" s="8">
-        <f>1/(1-POWER(1-$F66*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F66*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K66" s="10">
-        <f>1/(1-POWER(1-$F66*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F66*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L66" s="10">
-        <f>1/(1-POWER(1-$F66*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F66*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M66" s="12">
-        <f>1/(1-POWER(1-$F66*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F66*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N66" s="12">
-        <f>1/(1-POWER(1-$F66*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F66*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O66" s="6">
-        <f>1/(1-POWER(1-$F66*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F66*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P66" s="6">
-        <f>1/(1-POWER(1-$F66*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F66*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q66" s="16">
+        <f>1/(1-POWER(1-$F66*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R66" s="16">
+        <f>1/(1-POWER(1-$F66*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>47</v>
       </c>
       <c r="B67" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="C67" t="s">
-        <v>593</v>
+        <v>776</v>
       </c>
       <c r="D67" t="s">
         <v>52</v>
       </c>
       <c r="E67" s="3">
-        <f>VLOOKUP(D67,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C67,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D67,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C67,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>0.02</v>
       </c>
       <c r="F67" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G67" s="3">
@@ -13642,61 +13999,69 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H67" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I67" s="8">
-        <f>1/(1-POWER(1-$F67*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
+        <f>1/(1-POWER(1-$F67*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
       </c>
       <c r="J67" s="8">
-        <f>1/(1-POWER(1-$F67*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
+        <f>1/(1-POWER(1-$F67*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
       </c>
       <c r="K67" s="10">
-        <f>1/(1-POWER(1-$F67*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
+        <f>1/(1-POWER(1-$F67*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
       </c>
       <c r="L67" s="10">
-        <f>1/(1-POWER(1-$F67*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
+        <f>1/(1-POWER(1-$F67*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
       </c>
       <c r="M67" s="12">
-        <f>1/(1-POWER(1-$F67*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
+        <f>1/(1-POWER(1-$F67*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
       </c>
       <c r="N67" s="12">
-        <f>1/(1-POWER(1-$F67*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
+        <f>1/(1-POWER(1-$F67*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
       </c>
       <c r="O67" s="6">
-        <f>1/(1-POWER(1-$F67*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
+        <f>1/(1-POWER(1-$F67*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
       </c>
       <c r="P67" s="6">
-        <f>1/(1-POWER(1-$F67*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1/(1-POWER(1-$F67*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q67" s="16">
+        <f>1/(1-POWER(1-$F67*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R67" s="16">
+        <f>1/(1-POWER(1-$F67*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>47</v>
       </c>
       <c r="B68" t="s">
-        <v>603</v>
-      </c>
-      <c r="C68" s="16" t="s">
-        <v>503</v>
+        <v>592</v>
+      </c>
+      <c r="C68" t="s">
+        <v>593</v>
       </c>
       <c r="D68" t="s">
         <v>52</v>
       </c>
       <c r="E68" s="3">
-        <f>VLOOKUP(D68,$A$12:$F$15,5,FALSE)*_xlfn.XLOOKUP(Resultats!C68,Table1[name],Table1[cardRarityMultiplier])</f>
+        <f>VLOOKUP(D68,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C68,Table1[name],Table1[cardRarityMultiplier])</f>
         <v>0.02</v>
       </c>
       <c r="F68" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G68" s="3">
@@ -13704,130 +14069,205 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H68" s="3">
+        <f t="shared" si="5"/>
+        <v>3.0084957370373568</v>
+      </c>
+      <c r="I68" s="8">
+        <f>1/(1-POWER(1-$F68*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
+      </c>
+      <c r="J68" s="8">
+        <f>1/(1-POWER(1-$F68*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
+      </c>
+      <c r="K68" s="10">
+        <f>1/(1-POWER(1-$F68*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
+      </c>
+      <c r="L68" s="10">
+        <f>1/(1-POWER(1-$F68*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
+      </c>
+      <c r="M68" s="12">
+        <f>1/(1-POWER(1-$F68*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
+      </c>
+      <c r="N68" s="12">
+        <f>1/(1-POWER(1-$F68*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
+      </c>
+      <c r="O68" s="6">
+        <f>1/(1-POWER(1-$F68*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
+      </c>
+      <c r="P68" s="6">
+        <f>1/(1-POWER(1-$F68*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q68" s="16">
+        <f>1/(1-POWER(1-$F68*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R68" s="16">
+        <f>1/(1-POWER(1-$F68*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>47</v>
+      </c>
+      <c r="B69" t="s">
+        <v>603</v>
+      </c>
+      <c r="C69" t="s">
+        <v>503</v>
+      </c>
+      <c r="D69" t="s">
+        <v>52</v>
+      </c>
+      <c r="E69" s="3">
+        <f>VLOOKUP(D69,$A$13:$F$16,5,FALSE)*_xlfn.XLOOKUP(Resultats!C69,Table1[name],Table1[cardRarityMultiplier])</f>
+        <v>0.02</v>
+      </c>
+      <c r="F69" s="3">
         <f t="shared" si="4"/>
+        <v>1.9999999999999987E-2</v>
+      </c>
+      <c r="G69" s="3">
+        <f>1-POWER(1-E69,Donnees!$D$4)</f>
+        <v>0.33239202824490588</v>
+      </c>
+      <c r="H69" s="3">
+        <f t="shared" si="5"/>
         <v>3.0084957370373568</v>
       </c>
-      <c r="I68" s="8">
-        <f>1/(1-POWER(1-$F68*$F$3*$F$7,Donnees!$D$4))</f>
-        <v>6.0455775894678005</v>
-      </c>
-      <c r="J68" s="8">
-        <f>1/(1-POWER(1-$F68*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>50.476663320677318</v>
-      </c>
-      <c r="K68" s="10">
-        <f>1/(1-POWER(1-$F68*$F$4*$F$7,Donnees!$D$4))</f>
-        <v>9.7432593227673596</v>
-      </c>
-      <c r="L68" s="10">
-        <f>1/(1-POWER(1-$F68*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>83.809331130297309</v>
-      </c>
-      <c r="M68" s="12">
-        <f>1/(1-POWER(1-$F68*$F$5*$F$7,Donnees!$D$4))</f>
-        <v>18.998013119688618</v>
-      </c>
-      <c r="N68" s="12">
-        <f>1/(1-POWER(1-$F68*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>167.14216549121571</v>
-      </c>
-      <c r="O68" s="6">
-        <f>1/(1-POWER(1-$F68*$F$6*$F$7,Donnees!$D$4))</f>
-        <v>56.032052471159972</v>
-      </c>
-      <c r="P68" s="6">
-        <f>1/(1-POWER(1-$F68*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>500.47516625842803</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C69" s="17" t="s">
-        <v>503</v>
-      </c>
-      <c r="E69" s="4">
-        <f>SUM(E19:E68)</f>
+      <c r="I69" s="8">
+        <f>1/(1-POWER(1-$F69*$F$3*$F$8,Donnees!$D$4))</f>
+        <v>6.0857267969823825</v>
+      </c>
+      <c r="J69" s="8">
+        <f>1/(1-POWER(1-$F69*$F$3*$F$9,Donnees!$D$4))</f>
+        <v>50.838970189131004</v>
+      </c>
+      <c r="K69" s="10">
+        <f>1/(1-POWER(1-$F69*$F$4*$F$8,Donnees!$D$4))</f>
+        <v>9.6771866564579643</v>
+      </c>
+      <c r="L69" s="10">
+        <f>1/(1-POWER(1-$F69*$F$4*$F$9,Donnees!$D$4))</f>
+        <v>83.214100215587194</v>
+      </c>
+      <c r="M69" s="12">
+        <f>1/(1-POWER(1-$F69*$F$5*$F$8,Donnees!$D$4))</f>
+        <v>18.865770363543039</v>
+      </c>
+      <c r="N69" s="12">
+        <f>1/(1-POWER(1-$F69*$F$5*$F$9,Donnees!$D$4))</f>
+        <v>165.95169288991335</v>
+      </c>
+      <c r="O69" s="6">
+        <f>1/(1-POWER(1-$F69*$F$6*$F$8,Donnees!$D$4))</f>
+        <v>55.635237848282955</v>
+      </c>
+      <c r="P69" s="6">
+        <f>1/(1-POWER(1-$F69*$F$6*$F$9,Donnees!$D$4))</f>
+        <v>496.90373888289122</v>
+      </c>
+      <c r="Q69" s="16">
+        <f>1/(1-POWER(1-$F69*$F$7*$F$8,Donnees!$D$4))</f>
+        <v>386.58632641271407</v>
+      </c>
+      <c r="R69" s="16">
+        <f>1/(1-POWER(1-$F69*$F$7*$F$9,Donnees!$D$4))</f>
+        <v>3475.4750239175241</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="E70" s="4">
+        <f>SUM(E20:E69)</f>
         <v>1.0000000000000007</v>
       </c>
-      <c r="F69" s="4">
-        <f>SUM(F19:F68)</f>
+      <c r="F70" s="4">
+        <f>SUM(F20:F69)</f>
         <v>0.99999999999999956</v>
       </c>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G70" s="15"/>
-      <c r="H70" s="13">
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G71" s="15"/>
+      <c r="H71" s="13">
         <v>30</v>
       </c>
-      <c r="I70" s="14" cm="1">
-        <f t="array" ref="I70">SUM((1-_xlfn._xlws.FILTER(1/I$19:I$68,(1/I$19:I$68)&lt;&gt;""))^($H70))</f>
-        <v>0.23432110033910222</v>
-      </c>
-      <c r="J70" s="14" cm="1">
-        <f t="array" ref="J70">SUM((1-_xlfn._xlws.FILTER(1/J$19:J$68,(1/J$19:J$68)&lt;&gt;""))^($H70))</f>
-        <v>27.450941449985105</v>
-      </c>
-      <c r="K70" s="14" cm="1">
-        <f t="array" ref="K70">SUM((1-_xlfn._xlws.FILTER(1/K$19:K$68,(1/K$19:K$68)&lt;&gt;""))^($H70))</f>
-        <v>1.9822724643440246</v>
-      </c>
-      <c r="L70" s="14" cm="1">
-        <f t="array" ref="L70">SUM((1-_xlfn._xlws.FILTER(1/L$19:L$68,(1/L$19:L$68)&lt;&gt;""))^($H70))</f>
-        <v>34.888511641558161</v>
-      </c>
-      <c r="M70" s="14" cm="1">
-        <f t="array" ref="M70">SUM((1-_xlfn._xlws.FILTER(1/M$19:M$68,(1/M$19:M$68)&lt;&gt;""))^($H70))</f>
-        <v>9.9233317112353596</v>
-      </c>
-      <c r="N70" s="14" cm="1">
-        <f t="array" ref="N70">SUM((1-_xlfn._xlws.FILTER(1/N$19:N$68,(1/N$19:N$68)&lt;&gt;""))^($H70))</f>
-        <v>41.764905773737368</v>
-      </c>
-      <c r="O70" s="14" cm="1">
-        <f t="array" ref="O70">SUM((1-_xlfn._xlws.FILTER(1/O$19:O$68,(1/O$19:O$68)&lt;&gt;""))^($H70))</f>
-        <v>29.146301200516572</v>
-      </c>
-      <c r="P70" s="14" cm="1">
-        <f t="array" ref="P70">SUM((1-_xlfn._xlws.FILTER(1/P$19:P$68,(1/P$19:P$68)&lt;&gt;""))^($H70))</f>
-        <v>47.088400628583898</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H71" s="13">
+      <c r="I71" s="14" cm="1">
+        <f t="array" ref="I71">SUM((1-_xlfn._xlws.FILTER(1/I$20:I$69,(1/I$20:I$69)&lt;&gt;""))^($H71))</f>
+        <v>0.2434613276379263</v>
+      </c>
+      <c r="J71" s="14" cm="1">
+        <f t="array" ref="J71">SUM((1-_xlfn._xlws.FILTER(1/J$20:J$69,(1/J$20:J$69)&lt;&gt;""))^($H71))</f>
+        <v>27.569539872237119</v>
+      </c>
+      <c r="K71" s="14" cm="1">
+        <f t="array" ref="K71">SUM((1-_xlfn._xlws.FILTER(1/K$20:K$69,(1/K$20:K$69)&lt;&gt;""))^($H71))</f>
+        <v>1.9369651090038544</v>
+      </c>
+      <c r="L71" s="14" cm="1">
+        <f t="array" ref="L71">SUM((1-_xlfn._xlws.FILTER(1/L$20:L$69,(1/L$20:L$69)&lt;&gt;""))^($H71))</f>
+        <v>34.798337938919637</v>
+      </c>
+      <c r="M71" s="14" cm="1">
+        <f t="array" ref="M71">SUM((1-_xlfn._xlws.FILTER(1/M$20:M$69,(1/M$20:M$69)&lt;&gt;""))^($H71))</f>
+        <v>9.8087689322632077</v>
+      </c>
+      <c r="N71" s="14" cm="1">
+        <f t="array" ref="N71">SUM((1-_xlfn._xlws.FILTER(1/N$20:N$69,(1/N$20:N$69)&lt;&gt;""))^($H71))</f>
+        <v>41.710876920863612</v>
+      </c>
+      <c r="O71" s="14" cm="1">
+        <f t="array" ref="O71">SUM((1-_xlfn._xlws.FILTER(1/O$20:O$69,(1/O$20:O$69)&lt;&gt;""))^($H71))</f>
+        <v>29.03341989239447</v>
+      </c>
+      <c r="P71" s="14" cm="1">
+        <f t="array" ref="P71">SUM((1-_xlfn._xlws.FILTER(1/P$20:P$69,(1/P$20:P$69)&lt;&gt;""))^($H71))</f>
+        <v>47.068081600348016</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H72" s="13">
         <v>365</v>
       </c>
-      <c r="I71" s="14" cm="1">
-        <f t="array" ref="I71">SUM((1-_xlfn._xlws.FILTER(1/I$19:I$68,(1/I$19:I$68)&lt;&gt;""))^($H71))</f>
-        <v>4.0842199533540051E-24</v>
-      </c>
-      <c r="J71" s="14" cm="1">
-        <f t="array" ref="J71">SUM((1-_xlfn._xlws.FILTER(1/J$19:J$68,(1/J$19:J$68)&lt;&gt;""))^($H71))</f>
-        <v>3.7743888845230694E-2</v>
-      </c>
-      <c r="K71" s="14" cm="1">
-        <f t="array" ref="K71">SUM((1-_xlfn._xlws.FILTER(1/K$19:K$68,(1/K$19:K$68)&lt;&gt;""))^($H71))</f>
-        <v>1.5903633723943963E-14</v>
-      </c>
-      <c r="L71" s="14" cm="1">
-        <f t="array" ref="L71">SUM((1-_xlfn._xlws.FILTER(1/L$19:L$68,(1/L$19:L$68)&lt;&gt;""))^($H71))</f>
-        <v>0.65028135657011221</v>
-      </c>
-      <c r="M71" s="14" cm="1">
-        <f t="array" ref="M71">SUM((1-_xlfn._xlws.FILTER(1/M$19:M$68,(1/M$19:M$68)&lt;&gt;""))^($H71))</f>
-        <v>3.6665848268600179E-7</v>
-      </c>
-      <c r="N71" s="14" cm="1">
-        <f t="array" ref="N71">SUM((1-_xlfn._xlws.FILTER(1/N$19:N$68,(1/N$19:N$68)&lt;&gt;""))^($H71))</f>
-        <v>5.6463515485136497</v>
-      </c>
-      <c r="O71" s="14" cm="1">
-        <f t="array" ref="O71">SUM((1-_xlfn._xlws.FILTER(1/O$19:O$68,(1/O$19:O$68)&lt;&gt;""))^($H71))</f>
-        <v>7.6583913475761017E-2</v>
-      </c>
-      <c r="P71" s="14" cm="1">
-        <f t="array" ref="P71">SUM((1-_xlfn._xlws.FILTER(1/P$19:P$68,(1/P$19:P$68)&lt;&gt;""))^($H71))</f>
-        <v>24.118807206138069</v>
+      <c r="I72" s="14" cm="1">
+        <f t="array" ref="I72">SUM((1-_xlfn._xlws.FILTER(1/I$20:I$69,(1/I$20:I$69)&lt;&gt;""))^($H72))</f>
+        <v>6.0746850639769249E-24</v>
+      </c>
+      <c r="J72" s="14" cm="1">
+        <f t="array" ref="J72">SUM((1-_xlfn._xlws.FILTER(1/J$20:J$69,(1/J$20:J$69)&lt;&gt;""))^($H72))</f>
+        <v>3.9711157108312689E-2</v>
+      </c>
+      <c r="K72" s="14" cm="1">
+        <f t="array" ref="K72">SUM((1-_xlfn._xlws.FILTER(1/K$20:K$69,(1/K$20:K$69)&lt;&gt;""))^($H72))</f>
+        <v>1.2521163371041199E-14</v>
+      </c>
+      <c r="L72" s="14" cm="1">
+        <f t="array" ref="L72">SUM((1-_xlfn._xlws.FILTER(1/L$20:L$69,(1/L$20:L$69)&lt;&gt;""))^($H72))</f>
+        <v>0.63046827505992153</v>
+      </c>
+      <c r="M72" s="14" cm="1">
+        <f t="array" ref="M72">SUM((1-_xlfn._xlws.FILTER(1/M$20:M$69,(1/M$20:M$69)&lt;&gt;""))^($H72))</f>
+        <v>3.2307203383089968E-7</v>
+      </c>
+      <c r="N72" s="14" cm="1">
+        <f t="array" ref="N72">SUM((1-_xlfn._xlws.FILTER(1/N$20:N$69,(1/N$20:N$69)&lt;&gt;""))^($H72))</f>
+        <v>5.5588260647850234</v>
+      </c>
+      <c r="O72" s="14" cm="1">
+        <f t="array" ref="O72">SUM((1-_xlfn._xlws.FILTER(1/O$20:O$69,(1/O$20:O$69)&lt;&gt;""))^($H72))</f>
+        <v>7.3148239691921149E-2</v>
+      </c>
+      <c r="P72" s="14" cm="1">
+        <f t="array" ref="P72">SUM((1-_xlfn._xlws.FILTER(1/P$20:P$69,(1/P$20:P$69)&lt;&gt;""))^($H72))</f>
+        <v>23.992810344773858</v>
       </c>
     </row>
   </sheetData>

--- a/catalogue_astronomie.xlsx
+++ b/catalogue_astronomie.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Derfence\Documents\Gatcha\client-android-standalone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5625448-81B1-4631-A571-07EEC1ED1E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8143B11E-62EE-46C9-AAA3-7D6E492D7768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogue" sheetId="1" r:id="rId1"/>
@@ -10305,16 +10305,16 @@
         <v>9.8571428571428577</v>
       </c>
       <c r="F3">
-        <f>E3/SUMPRODUCT($E$3:$E$6)</f>
-        <v>0.49640287769784175</v>
+        <f>E3/SUMPRODUCT($E$3:$E$7)</f>
+        <v>0.49285714285714288</v>
       </c>
       <c r="G3">
         <f>1/(F3*Donnees!$B$3)</f>
-        <v>0.40289855072463765</v>
+        <v>0.40579710144927533</v>
       </c>
       <c r="H3">
         <f>1/(1/G3*24/Donnees!$B$4)</f>
-        <v>0.10072463768115941</v>
+        <v>0.10144927536231883</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -10335,16 +10335,16 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F4:F6" si="0">E4/SUMPRODUCT($E$3:$E$6)</f>
-        <v>0.30215827338129497</v>
+        <f t="shared" ref="F4:F7" si="0">E4/SUMPRODUCT($E$3:$E$7)</f>
+        <v>0.3</v>
       </c>
       <c r="G4">
         <f>1/(F4*Donnees!$B$3)</f>
-        <v>0.66190476190476188</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H4">
         <f>1/(1/G4*24/Donnees!$B$4)</f>
-        <v>0.16547619047619047</v>
+        <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -10366,15 +10366,15 @@
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>0.15107913669064749</v>
+        <v>0.15</v>
       </c>
       <c r="G5">
         <f>1/(F5*Donnees!$B$3)</f>
-        <v>1.3238095238095238</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="H5">
         <f>1/(1/G5*24/Donnees!$B$4)</f>
-        <v>0.33095238095238094</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -10396,15 +10396,15 @@
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>5.0359712230215826E-2</v>
+        <v>0.05</v>
       </c>
       <c r="G6">
         <f>1/(F6*Donnees!$B$3)</f>
-        <v>3.9714285714285715</v>
+        <v>4</v>
       </c>
       <c r="H6">
         <f>1/(1/G6*24/Donnees!$B$4)</f>
-        <v>0.99285714285714288</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -10425,16 +10425,16 @@
         <v>0.14285714285714285</v>
       </c>
       <c r="F7">
-        <f t="shared" ref="F7" si="1">E7/SUMPRODUCT($E$3:$E$6)</f>
-        <v>7.1942446043165463E-3</v>
+        <f t="shared" si="0"/>
+        <v>7.1428571428571426E-3</v>
       </c>
       <c r="G7">
         <f>1/(F7*Donnees!$B$3)</f>
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="H7">
         <f>1/(1/G7*24/Donnees!$B$4)</f>
-        <v>6.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -10564,7 +10564,7 @@
         <v>0.3</v>
       </c>
       <c r="E14">
-        <f t="shared" ref="E14:E16" si="2">D14/B14</f>
+        <f t="shared" ref="E14:E16" si="1">D14/B14</f>
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F14">
@@ -10589,7 +10589,7 @@
         <v>0.15</v>
       </c>
       <c r="E15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.8749999999999999E-2</v>
       </c>
       <c r="F15">
@@ -10614,7 +10614,7 @@
         <v>0.05</v>
       </c>
       <c r="E16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.6666666666666666E-2</v>
       </c>
       <c r="F16">
@@ -10709,48 +10709,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" ref="H20:H51" si="3">1/G20</f>
+        <f t="shared" ref="H20:H51" si="2">1/G20</f>
         <v>3.0084957370373568</v>
       </c>
       <c r="I20" s="8">
         <f>1/(1-POWER(1-$F20*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J20" s="8">
         <f>1/(1-POWER(1-$F20*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K20" s="10">
         <f>1/(1-POWER(1-$F20*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L20" s="10">
         <f>1/(1-POWER(1-$F20*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M20" s="12">
         <f>1/(1-POWER(1-$F20*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N20" s="12">
         <f>1/(1-POWER(1-$F20*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O20" s="6">
         <f>1/(1-POWER(1-$F20*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P20" s="6">
         <f>1/(1-POWER(1-$F20*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q20" s="16">
         <f>1/(1-POWER(1-$F20*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R20" s="16">
         <f>1/(1-POWER(1-$F20*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -10771,7 +10771,7 @@
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F21" s="3">
-        <f t="shared" ref="F21:F69" si="4">E21/$E$70</f>
+        <f t="shared" ref="F21:F69" si="3">E21/$E$70</f>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G21" s="3">
@@ -10779,48 +10779,48 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H21" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I21" s="8">
         <f>1/(1-POWER(1-$F21*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>5.7137417013118368</v>
+        <v>5.7512009380835991</v>
       </c>
       <c r="J21" s="8">
         <f>1/(1-POWER(1-$F21*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>47.481600280957529</v>
+        <v>47.819751887369826</v>
       </c>
       <c r="K21" s="10">
         <f>1/(1-POWER(1-$F21*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.064960983515661</v>
+        <v>9.126619822082489</v>
       </c>
       <c r="L21" s="10">
         <f>1/(1-POWER(1-$F21*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>77.698299006688089</v>
+        <v>78.253846868491379</v>
       </c>
       <c r="M21" s="12">
         <f>1/(1-POWER(1-$F21*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>17.640344596567786</v>
+        <v>17.763766692007298</v>
       </c>
       <c r="N21" s="12">
         <f>1/(1-POWER(1-$F21*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>154.9199827506408</v>
+        <v>156.03109001607743</v>
       </c>
       <c r="O21" s="6">
         <f>1/(1-POWER(1-$F21*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>51.95809691416796</v>
+        <v>52.328455740305785</v>
       </c>
       <c r="P21" s="6">
         <f>1/(1-POWER(1-$F21*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="Q21" s="16">
         <f>1/(1-POWER(1-$F21*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>360.84560105190172</v>
+        <v>363.43819199656815</v>
       </c>
       <c r="R21" s="16">
         <f>1/(1-POWER(1-$F21*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3243.8083589698131</v>
+        <v>3267.1416921215396</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -10841,7 +10841,7 @@
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F22" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G22" s="3">
@@ -10849,48 +10849,48 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H22" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I22" s="8">
         <f>1/(1-POWER(1-$F22*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>5.7137417013118368</v>
+        <v>5.7512009380835991</v>
       </c>
       <c r="J22" s="8">
         <f>1/(1-POWER(1-$F22*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>47.481600280957529</v>
+        <v>47.819751887369826</v>
       </c>
       <c r="K22" s="10">
         <f>1/(1-POWER(1-$F22*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.064960983515661</v>
+        <v>9.126619822082489</v>
       </c>
       <c r="L22" s="10">
         <f>1/(1-POWER(1-$F22*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>77.698299006688089</v>
+        <v>78.253846868491379</v>
       </c>
       <c r="M22" s="12">
         <f>1/(1-POWER(1-$F22*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>17.640344596567786</v>
+        <v>17.763766692007298</v>
       </c>
       <c r="N22" s="12">
         <f>1/(1-POWER(1-$F22*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>154.9199827506408</v>
+        <v>156.03109001607743</v>
       </c>
       <c r="O22" s="6">
         <f>1/(1-POWER(1-$F22*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>51.95809691416796</v>
+        <v>52.328455740305785</v>
       </c>
       <c r="P22" s="6">
         <f>1/(1-POWER(1-$F22*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="Q22" s="16">
         <f>1/(1-POWER(1-$F22*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>360.84560105190172</v>
+        <v>363.43819199656815</v>
       </c>
       <c r="R22" s="16">
         <f>1/(1-POWER(1-$F22*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3243.8083589698131</v>
+        <v>3267.1416921215396</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -10911,7 +10911,7 @@
         <v>0.02</v>
       </c>
       <c r="F23" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G23" s="3">
@@ -10919,48 +10919,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H23" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I23" s="8">
         <f>1/(1-POWER(1-$F23*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J23" s="8">
         <f>1/(1-POWER(1-$F23*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K23" s="10">
         <f>1/(1-POWER(1-$F23*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L23" s="10">
         <f>1/(1-POWER(1-$F23*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M23" s="12">
         <f>1/(1-POWER(1-$F23*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N23" s="12">
         <f>1/(1-POWER(1-$F23*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O23" s="6">
         <f>1/(1-POWER(1-$F23*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P23" s="6">
         <f>1/(1-POWER(1-$F23*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q23" s="16">
         <f>1/(1-POWER(1-$F23*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R23" s="16">
         <f>1/(1-POWER(1-$F23*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -10981,7 +10981,7 @@
         <v>0.02</v>
       </c>
       <c r="F24" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G24" s="3">
@@ -10989,48 +10989,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I24" s="8">
         <f>1/(1-POWER(1-$F24*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J24" s="8">
         <f>1/(1-POWER(1-$F24*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K24" s="10">
         <f>1/(1-POWER(1-$F24*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L24" s="10">
         <f>1/(1-POWER(1-$F24*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M24" s="12">
         <f>1/(1-POWER(1-$F24*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N24" s="12">
         <f>1/(1-POWER(1-$F24*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O24" s="6">
         <f>1/(1-POWER(1-$F24*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P24" s="6">
         <f>1/(1-POWER(1-$F24*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q24" s="16">
         <f>1/(1-POWER(1-$F24*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R24" s="16">
         <f>1/(1-POWER(1-$F24*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -11051,7 +11051,7 @@
         <v>0.02</v>
       </c>
       <c r="F25" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G25" s="3">
@@ -11059,48 +11059,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H25" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I25" s="8">
         <f>1/(1-POWER(1-$F25*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J25" s="8">
         <f>1/(1-POWER(1-$F25*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K25" s="10">
         <f>1/(1-POWER(1-$F25*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L25" s="10">
         <f>1/(1-POWER(1-$F25*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M25" s="12">
         <f>1/(1-POWER(1-$F25*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N25" s="12">
         <f>1/(1-POWER(1-$F25*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O25" s="6">
         <f>1/(1-POWER(1-$F25*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P25" s="6">
         <f>1/(1-POWER(1-$F25*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q25" s="16">
         <f>1/(1-POWER(1-$F25*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R25" s="16">
         <f>1/(1-POWER(1-$F25*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -11121,7 +11121,7 @@
         <v>1.6666666666666666E-2</v>
       </c>
       <c r="F26" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.6666666666666656E-2</v>
       </c>
       <c r="G26" s="3">
@@ -11129,48 +11129,48 @@
         <v>0.28547862520944578</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.5028892242504481</v>
       </c>
       <c r="I26" s="8">
         <f>1/(1-POWER(1-$F26*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>7.2023965734528721</v>
+        <v>7.2506167684594436</v>
       </c>
       <c r="J26" s="8">
         <f>1/(1-POWER(1-$F26*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>60.911158621330586</v>
+        <v>61.345931397417964</v>
       </c>
       <c r="K26" s="10">
         <f>1/(1-POWER(1-$F26*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>11.514297189973696</v>
+        <v>11.593608225426648</v>
       </c>
       <c r="L26" s="10">
         <f>1/(1-POWER(1-$F26*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>99.761551725391485</v>
+        <v>100.47583145650593</v>
       </c>
       <c r="M26" s="12">
         <f>1/(1-POWER(1-$F26*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>22.542263745146919</v>
+        <v>22.700966934764622</v>
       </c>
       <c r="N26" s="12">
         <f>1/(1-POWER(1-$F26*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>199.04684723903111</v>
+        <v>200.47541567679099</v>
       </c>
       <c r="O26" s="6">
         <f>1/(1-POWER(1-$F26*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>66.666732505570209</v>
+        <v>67.142914004784032</v>
       </c>
       <c r="P26" s="6">
         <f>1/(1-POWER(1-$F26*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>596.1894252587216</v>
+        <v>600.4751385476535</v>
       </c>
       <c r="Q26" s="16">
         <f>1/(1-POWER(1-$F26*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="R26" s="16">
         <f>1/(1-POWER(1-$F26*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>4170.4750199394775</v>
+        <v>4200.4750198192387</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -11191,7 +11191,7 @@
         <v>0.02</v>
       </c>
       <c r="F27" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G27" s="3">
@@ -11199,48 +11199,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H27" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I27" s="8">
         <f>1/(1-POWER(1-$F27*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J27" s="8">
         <f>1/(1-POWER(1-$F27*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K27" s="10">
         <f>1/(1-POWER(1-$F27*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L27" s="10">
         <f>1/(1-POWER(1-$F27*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M27" s="12">
         <f>1/(1-POWER(1-$F27*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N27" s="12">
         <f>1/(1-POWER(1-$F27*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O27" s="6">
         <f>1/(1-POWER(1-$F27*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P27" s="6">
         <f>1/(1-POWER(1-$F27*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q27" s="16">
         <f>1/(1-POWER(1-$F27*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R27" s="16">
         <f>1/(1-POWER(1-$F27*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -11261,7 +11261,7 @@
         <v>0.02</v>
       </c>
       <c r="F28" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G28" s="3">
@@ -11269,48 +11269,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H28" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I28" s="8">
         <f>1/(1-POWER(1-$F28*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J28" s="8">
         <f>1/(1-POWER(1-$F28*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K28" s="10">
         <f>1/(1-POWER(1-$F28*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L28" s="10">
         <f>1/(1-POWER(1-$F28*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M28" s="12">
         <f>1/(1-POWER(1-$F28*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N28" s="12">
         <f>1/(1-POWER(1-$F28*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O28" s="6">
         <f>1/(1-POWER(1-$F28*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P28" s="6">
         <f>1/(1-POWER(1-$F28*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q28" s="16">
         <f>1/(1-POWER(1-$F28*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R28" s="16">
         <f>1/(1-POWER(1-$F28*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -11331,7 +11331,7 @@
         <v>0.02</v>
       </c>
       <c r="F29" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G29" s="3">
@@ -11339,48 +11339,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H29" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I29" s="8">
         <f>1/(1-POWER(1-$F29*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J29" s="8">
         <f>1/(1-POWER(1-$F29*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K29" s="10">
         <f>1/(1-POWER(1-$F29*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L29" s="10">
         <f>1/(1-POWER(1-$F29*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M29" s="12">
         <f>1/(1-POWER(1-$F29*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N29" s="12">
         <f>1/(1-POWER(1-$F29*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O29" s="6">
         <f>1/(1-POWER(1-$F29*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P29" s="6">
         <f>1/(1-POWER(1-$F29*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q29" s="16">
         <f>1/(1-POWER(1-$F29*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R29" s="16">
         <f>1/(1-POWER(1-$F29*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -11401,7 +11401,7 @@
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F30" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G30" s="3">
@@ -11409,48 +11409,48 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H30" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I30" s="8">
         <f>1/(1-POWER(1-$F30*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>5.7137417013118368</v>
+        <v>5.7512009380835991</v>
       </c>
       <c r="J30" s="8">
         <f>1/(1-POWER(1-$F30*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>47.481600280957529</v>
+        <v>47.819751887369826</v>
       </c>
       <c r="K30" s="10">
         <f>1/(1-POWER(1-$F30*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.064960983515661</v>
+        <v>9.126619822082489</v>
       </c>
       <c r="L30" s="10">
         <f>1/(1-POWER(1-$F30*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>77.698299006688089</v>
+        <v>78.253846868491379</v>
       </c>
       <c r="M30" s="12">
         <f>1/(1-POWER(1-$F30*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>17.640344596567786</v>
+        <v>17.763766692007298</v>
       </c>
       <c r="N30" s="12">
         <f>1/(1-POWER(1-$F30*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>154.9199827506408</v>
+        <v>156.03109001607743</v>
       </c>
       <c r="O30" s="6">
         <f>1/(1-POWER(1-$F30*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>51.95809691416796</v>
+        <v>52.328455740305785</v>
       </c>
       <c r="P30" s="6">
         <f>1/(1-POWER(1-$F30*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="Q30" s="16">
         <f>1/(1-POWER(1-$F30*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>360.84560105190172</v>
+        <v>363.43819199656815</v>
       </c>
       <c r="R30" s="16">
         <f>1/(1-POWER(1-$F30*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3243.8083589698131</v>
+        <v>3267.1416921215396</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -11471,7 +11471,7 @@
         <v>1.6666666666666666E-2</v>
       </c>
       <c r="F31" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.6666666666666656E-2</v>
       </c>
       <c r="G31" s="3">
@@ -11479,48 +11479,48 @@
         <v>0.28547862520944578</v>
       </c>
       <c r="H31" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.5028892242504481</v>
       </c>
       <c r="I31" s="8">
         <f>1/(1-POWER(1-$F31*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>7.2023965734528721</v>
+        <v>7.2506167684594436</v>
       </c>
       <c r="J31" s="8">
         <f>1/(1-POWER(1-$F31*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>60.911158621330586</v>
+        <v>61.345931397417964</v>
       </c>
       <c r="K31" s="10">
         <f>1/(1-POWER(1-$F31*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>11.514297189973696</v>
+        <v>11.593608225426648</v>
       </c>
       <c r="L31" s="10">
         <f>1/(1-POWER(1-$F31*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>99.761551725391485</v>
+        <v>100.47583145650593</v>
       </c>
       <c r="M31" s="12">
         <f>1/(1-POWER(1-$F31*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>22.542263745146919</v>
+        <v>22.700966934764622</v>
       </c>
       <c r="N31" s="12">
         <f>1/(1-POWER(1-$F31*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>199.04684723903111</v>
+        <v>200.47541567679099</v>
       </c>
       <c r="O31" s="6">
         <f>1/(1-POWER(1-$F31*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>66.666732505570209</v>
+        <v>67.142914004784032</v>
       </c>
       <c r="P31" s="6">
         <f>1/(1-POWER(1-$F31*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>596.1894252587216</v>
+        <v>600.4751385476535</v>
       </c>
       <c r="Q31" s="16">
         <f>1/(1-POWER(1-$F31*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="R31" s="16">
         <f>1/(1-POWER(1-$F31*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>4170.4750199394775</v>
+        <v>4200.4750198192387</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -11541,7 +11541,7 @@
         <v>0.02</v>
       </c>
       <c r="F32" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G32" s="3">
@@ -11549,48 +11549,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H32" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I32" s="8">
         <f>1/(1-POWER(1-$F32*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J32" s="8">
         <f>1/(1-POWER(1-$F32*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K32" s="10">
         <f>1/(1-POWER(1-$F32*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L32" s="10">
         <f>1/(1-POWER(1-$F32*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M32" s="12">
         <f>1/(1-POWER(1-$F32*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N32" s="12">
         <f>1/(1-POWER(1-$F32*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O32" s="6">
         <f>1/(1-POWER(1-$F32*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P32" s="6">
         <f>1/(1-POWER(1-$F32*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q32" s="16">
         <f>1/(1-POWER(1-$F32*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R32" s="16">
         <f>1/(1-POWER(1-$F32*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -11611,7 +11611,7 @@
         <v>0.02</v>
       </c>
       <c r="F33" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G33" s="3">
@@ -11619,48 +11619,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H33" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I33" s="8">
         <f>1/(1-POWER(1-$F33*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J33" s="8">
         <f>1/(1-POWER(1-$F33*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K33" s="10">
         <f>1/(1-POWER(1-$F33*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L33" s="10">
         <f>1/(1-POWER(1-$F33*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M33" s="12">
         <f>1/(1-POWER(1-$F33*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N33" s="12">
         <f>1/(1-POWER(1-$F33*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O33" s="6">
         <f>1/(1-POWER(1-$F33*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P33" s="6">
         <f>1/(1-POWER(1-$F33*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q33" s="16">
         <f>1/(1-POWER(1-$F33*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R33" s="16">
         <f>1/(1-POWER(1-$F33*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -11681,7 +11681,7 @@
         <v>0.02</v>
       </c>
       <c r="F34" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G34" s="3">
@@ -11689,48 +11689,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H34" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I34" s="8">
         <f>1/(1-POWER(1-$F34*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J34" s="8">
         <f>1/(1-POWER(1-$F34*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K34" s="10">
         <f>1/(1-POWER(1-$F34*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L34" s="10">
         <f>1/(1-POWER(1-$F34*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M34" s="12">
         <f>1/(1-POWER(1-$F34*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N34" s="12">
         <f>1/(1-POWER(1-$F34*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O34" s="6">
         <f>1/(1-POWER(1-$F34*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P34" s="6">
         <f>1/(1-POWER(1-$F34*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q34" s="16">
         <f>1/(1-POWER(1-$F34*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R34" s="16">
         <f>1/(1-POWER(1-$F34*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -11751,7 +11751,7 @@
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F35" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G35" s="3">
@@ -11759,48 +11759,48 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H35" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I35" s="8">
         <f>1/(1-POWER(1-$F35*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>5.7137417013118368</v>
+        <v>5.7512009380835991</v>
       </c>
       <c r="J35" s="8">
         <f>1/(1-POWER(1-$F35*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>47.481600280957529</v>
+        <v>47.819751887369826</v>
       </c>
       <c r="K35" s="10">
         <f>1/(1-POWER(1-$F35*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.064960983515661</v>
+        <v>9.126619822082489</v>
       </c>
       <c r="L35" s="10">
         <f>1/(1-POWER(1-$F35*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>77.698299006688089</v>
+        <v>78.253846868491379</v>
       </c>
       <c r="M35" s="12">
         <f>1/(1-POWER(1-$F35*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>17.640344596567786</v>
+        <v>17.763766692007298</v>
       </c>
       <c r="N35" s="12">
         <f>1/(1-POWER(1-$F35*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>154.9199827506408</v>
+        <v>156.03109001607743</v>
       </c>
       <c r="O35" s="6">
         <f>1/(1-POWER(1-$F35*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>51.95809691416796</v>
+        <v>52.328455740305785</v>
       </c>
       <c r="P35" s="6">
         <f>1/(1-POWER(1-$F35*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="Q35" s="16">
         <f>1/(1-POWER(1-$F35*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>360.84560105190172</v>
+        <v>363.43819199656815</v>
       </c>
       <c r="R35" s="16">
         <f>1/(1-POWER(1-$F35*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3243.8083589698131</v>
+        <v>3267.1416921215396</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -11821,7 +11821,7 @@
         <v>1.6666666666666666E-2</v>
       </c>
       <c r="F36" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.6666666666666656E-2</v>
       </c>
       <c r="G36" s="3">
@@ -11829,48 +11829,48 @@
         <v>0.28547862520944578</v>
       </c>
       <c r="H36" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.5028892242504481</v>
       </c>
       <c r="I36" s="8">
         <f>1/(1-POWER(1-$F36*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>7.2023965734528721</v>
+        <v>7.2506167684594436</v>
       </c>
       <c r="J36" s="8">
         <f>1/(1-POWER(1-$F36*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>60.911158621330586</v>
+        <v>61.345931397417964</v>
       </c>
       <c r="K36" s="10">
         <f>1/(1-POWER(1-$F36*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>11.514297189973696</v>
+        <v>11.593608225426648</v>
       </c>
       <c r="L36" s="10">
         <f>1/(1-POWER(1-$F36*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>99.761551725391485</v>
+        <v>100.47583145650593</v>
       </c>
       <c r="M36" s="12">
         <f>1/(1-POWER(1-$F36*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>22.542263745146919</v>
+        <v>22.700966934764622</v>
       </c>
       <c r="N36" s="12">
         <f>1/(1-POWER(1-$F36*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>199.04684723903111</v>
+        <v>200.47541567679099</v>
       </c>
       <c r="O36" s="6">
         <f>1/(1-POWER(1-$F36*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>66.666732505570209</v>
+        <v>67.142914004784032</v>
       </c>
       <c r="P36" s="6">
         <f>1/(1-POWER(1-$F36*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>596.1894252587216</v>
+        <v>600.4751385476535</v>
       </c>
       <c r="Q36" s="16">
         <f>1/(1-POWER(1-$F36*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="R36" s="16">
         <f>1/(1-POWER(1-$F36*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>4170.4750199394775</v>
+        <v>4200.4750198192387</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
@@ -11891,7 +11891,7 @@
         <v>0.02</v>
       </c>
       <c r="F37" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G37" s="3">
@@ -11899,48 +11899,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H37" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I37" s="8">
         <f>1/(1-POWER(1-$F37*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J37" s="8">
         <f>1/(1-POWER(1-$F37*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K37" s="10">
         <f>1/(1-POWER(1-$F37*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L37" s="10">
         <f>1/(1-POWER(1-$F37*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M37" s="12">
         <f>1/(1-POWER(1-$F37*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N37" s="12">
         <f>1/(1-POWER(1-$F37*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O37" s="6">
         <f>1/(1-POWER(1-$F37*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P37" s="6">
         <f>1/(1-POWER(1-$F37*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q37" s="16">
         <f>1/(1-POWER(1-$F37*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R37" s="16">
         <f>1/(1-POWER(1-$F37*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
@@ -11961,7 +11961,7 @@
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F38" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G38" s="3">
@@ -11969,48 +11969,48 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H38" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I38" s="8">
         <f>1/(1-POWER(1-$F38*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>5.7137417013118368</v>
+        <v>5.7512009380835991</v>
       </c>
       <c r="J38" s="8">
         <f>1/(1-POWER(1-$F38*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>47.481600280957529</v>
+        <v>47.819751887369826</v>
       </c>
       <c r="K38" s="10">
         <f>1/(1-POWER(1-$F38*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.064960983515661</v>
+        <v>9.126619822082489</v>
       </c>
       <c r="L38" s="10">
         <f>1/(1-POWER(1-$F38*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>77.698299006688089</v>
+        <v>78.253846868491379</v>
       </c>
       <c r="M38" s="12">
         <f>1/(1-POWER(1-$F38*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>17.640344596567786</v>
+        <v>17.763766692007298</v>
       </c>
       <c r="N38" s="12">
         <f>1/(1-POWER(1-$F38*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>154.9199827506408</v>
+        <v>156.03109001607743</v>
       </c>
       <c r="O38" s="6">
         <f>1/(1-POWER(1-$F38*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>51.95809691416796</v>
+        <v>52.328455740305785</v>
       </c>
       <c r="P38" s="6">
         <f>1/(1-POWER(1-$F38*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="Q38" s="16">
         <f>1/(1-POWER(1-$F38*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>360.84560105190172</v>
+        <v>363.43819199656815</v>
       </c>
       <c r="R38" s="16">
         <f>1/(1-POWER(1-$F38*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3243.8083589698131</v>
+        <v>3267.1416921215396</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
@@ -12031,7 +12031,7 @@
         <v>0.02</v>
       </c>
       <c r="F39" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G39" s="3">
@@ -12039,48 +12039,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H39" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I39" s="8">
         <f>1/(1-POWER(1-$F39*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J39" s="8">
         <f>1/(1-POWER(1-$F39*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K39" s="10">
         <f>1/(1-POWER(1-$F39*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L39" s="10">
         <f>1/(1-POWER(1-$F39*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M39" s="12">
         <f>1/(1-POWER(1-$F39*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N39" s="12">
         <f>1/(1-POWER(1-$F39*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O39" s="6">
         <f>1/(1-POWER(1-$F39*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P39" s="6">
         <f>1/(1-POWER(1-$F39*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q39" s="16">
         <f>1/(1-POWER(1-$F39*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R39" s="16">
         <f>1/(1-POWER(1-$F39*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
@@ -12101,7 +12101,7 @@
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F40" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G40" s="3">
@@ -12109,48 +12109,48 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H40" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I40" s="8">
         <f>1/(1-POWER(1-$F40*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>5.7137417013118368</v>
+        <v>5.7512009380835991</v>
       </c>
       <c r="J40" s="8">
         <f>1/(1-POWER(1-$F40*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>47.481600280957529</v>
+        <v>47.819751887369826</v>
       </c>
       <c r="K40" s="10">
         <f>1/(1-POWER(1-$F40*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.064960983515661</v>
+        <v>9.126619822082489</v>
       </c>
       <c r="L40" s="10">
         <f>1/(1-POWER(1-$F40*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>77.698299006688089</v>
+        <v>78.253846868491379</v>
       </c>
       <c r="M40" s="12">
         <f>1/(1-POWER(1-$F40*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>17.640344596567786</v>
+        <v>17.763766692007298</v>
       </c>
       <c r="N40" s="12">
         <f>1/(1-POWER(1-$F40*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>154.9199827506408</v>
+        <v>156.03109001607743</v>
       </c>
       <c r="O40" s="6">
         <f>1/(1-POWER(1-$F40*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>51.95809691416796</v>
+        <v>52.328455740305785</v>
       </c>
       <c r="P40" s="6">
         <f>1/(1-POWER(1-$F40*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="Q40" s="16">
         <f>1/(1-POWER(1-$F40*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>360.84560105190172</v>
+        <v>363.43819199656815</v>
       </c>
       <c r="R40" s="16">
         <f>1/(1-POWER(1-$F40*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3243.8083589698131</v>
+        <v>3267.1416921215396</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -12171,7 +12171,7 @@
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F41" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G41" s="3">
@@ -12179,48 +12179,48 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H41" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I41" s="8">
         <f>1/(1-POWER(1-$F41*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>5.7137417013118368</v>
+        <v>5.7512009380835991</v>
       </c>
       <c r="J41" s="8">
         <f>1/(1-POWER(1-$F41*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>47.481600280957529</v>
+        <v>47.819751887369826</v>
       </c>
       <c r="K41" s="10">
         <f>1/(1-POWER(1-$F41*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.064960983515661</v>
+        <v>9.126619822082489</v>
       </c>
       <c r="L41" s="10">
         <f>1/(1-POWER(1-$F41*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>77.698299006688089</v>
+        <v>78.253846868491379</v>
       </c>
       <c r="M41" s="12">
         <f>1/(1-POWER(1-$F41*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>17.640344596567786</v>
+        <v>17.763766692007298</v>
       </c>
       <c r="N41" s="12">
         <f>1/(1-POWER(1-$F41*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>154.9199827506408</v>
+        <v>156.03109001607743</v>
       </c>
       <c r="O41" s="6">
         <f>1/(1-POWER(1-$F41*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>51.95809691416796</v>
+        <v>52.328455740305785</v>
       </c>
       <c r="P41" s="6">
         <f>1/(1-POWER(1-$F41*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="Q41" s="16">
         <f>1/(1-POWER(1-$F41*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>360.84560105190172</v>
+        <v>363.43819199656815</v>
       </c>
       <c r="R41" s="16">
         <f>1/(1-POWER(1-$F41*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3243.8083589698131</v>
+        <v>3267.1416921215396</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -12241,7 +12241,7 @@
         <v>1.8749999999999999E-2</v>
       </c>
       <c r="F42" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.8749999999999985E-2</v>
       </c>
       <c r="G42" s="3">
@@ -12249,48 +12249,48 @@
         <v>0.31515325639173553</v>
       </c>
       <c r="H42" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.1730593916408716</v>
       </c>
       <c r="I42" s="8">
         <f>1/(1-POWER(1-$F42*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.4578458934330172</v>
+        <v>6.5006872150229773</v>
       </c>
       <c r="J42" s="8">
         <f>1/(1-POWER(1-$F42*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>54.196354855722817</v>
+        <v>54.582817222883541</v>
       </c>
       <c r="K42" s="10">
         <f>1/(1-POWER(1-$F42*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>10.289493630089176</v>
+        <v>10.359979540057177</v>
       </c>
       <c r="L42" s="10">
         <f>1/(1-POWER(1-$F42*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>88.729910402846656</v>
+        <v>89.364824306266769</v>
       </c>
       <c r="M42" s="12">
         <f>1/(1-POWER(1-$F42*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>20.091236650595796</v>
+        <v>20.232299777012749</v>
       </c>
       <c r="N42" s="12">
         <f>1/(1-POWER(1-$F42*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>176.98340751640595</v>
+        <v>178.25324542143156</v>
       </c>
       <c r="O42" s="6">
         <f>1/(1-POWER(1-$F42*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>59.312392255803132</v>
+        <v>59.73566257905977</v>
       </c>
       <c r="P42" s="6">
         <f>1/(1-POWER(1-$F42*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>529.99896651203778</v>
+        <v>533.80848919998323</v>
       </c>
       <c r="Q42" s="16">
         <f>1/(1-POWER(1-$F42*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>412.3270536965432</v>
+        <v>415.29001521748876</v>
       </c>
       <c r="R42" s="16">
         <f>1/(1-POWER(1-$F42*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3707.1416890942214</v>
+        <v>3733.8083555993026</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
@@ -12311,7 +12311,7 @@
         <v>1.8749999999999999E-2</v>
       </c>
       <c r="F43" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.8749999999999985E-2</v>
       </c>
       <c r="G43" s="3">
@@ -12319,48 +12319,48 @@
         <v>0.31515325639173553</v>
       </c>
       <c r="H43" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.1730593916408716</v>
       </c>
       <c r="I43" s="8">
         <f>1/(1-POWER(1-$F43*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.4578458934330172</v>
+        <v>6.5006872150229773</v>
       </c>
       <c r="J43" s="8">
         <f>1/(1-POWER(1-$F43*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>54.196354855722817</v>
+        <v>54.582817222883541</v>
       </c>
       <c r="K43" s="10">
         <f>1/(1-POWER(1-$F43*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>10.289493630089176</v>
+        <v>10.359979540057177</v>
       </c>
       <c r="L43" s="10">
         <f>1/(1-POWER(1-$F43*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>88.729910402846656</v>
+        <v>89.364824306266769</v>
       </c>
       <c r="M43" s="12">
         <f>1/(1-POWER(1-$F43*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>20.091236650595796</v>
+        <v>20.232299777012749</v>
       </c>
       <c r="N43" s="12">
         <f>1/(1-POWER(1-$F43*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>176.98340751640595</v>
+        <v>178.25324542143156</v>
       </c>
       <c r="O43" s="6">
         <f>1/(1-POWER(1-$F43*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>59.312392255803132</v>
+        <v>59.73566257905977</v>
       </c>
       <c r="P43" s="6">
         <f>1/(1-POWER(1-$F43*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>529.99896651203778</v>
+        <v>533.80848919998323</v>
       </c>
       <c r="Q43" s="16">
         <f>1/(1-POWER(1-$F43*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>412.3270536965432</v>
+        <v>415.29001521748876</v>
       </c>
       <c r="R43" s="16">
         <f>1/(1-POWER(1-$F43*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3707.1416890942214</v>
+        <v>3733.8083555993026</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
@@ -12381,7 +12381,7 @@
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F44" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G44" s="3">
@@ -12389,48 +12389,48 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H44" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I44" s="8">
         <f>1/(1-POWER(1-$F44*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>5.7137417013118368</v>
+        <v>5.7512009380835991</v>
       </c>
       <c r="J44" s="8">
         <f>1/(1-POWER(1-$F44*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>47.481600280957529</v>
+        <v>47.819751887369826</v>
       </c>
       <c r="K44" s="10">
         <f>1/(1-POWER(1-$F44*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.064960983515661</v>
+        <v>9.126619822082489</v>
       </c>
       <c r="L44" s="10">
         <f>1/(1-POWER(1-$F44*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>77.698299006688089</v>
+        <v>78.253846868491379</v>
       </c>
       <c r="M44" s="12">
         <f>1/(1-POWER(1-$F44*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>17.640344596567786</v>
+        <v>17.763766692007298</v>
       </c>
       <c r="N44" s="12">
         <f>1/(1-POWER(1-$F44*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>154.9199827506408</v>
+        <v>156.03109001607743</v>
       </c>
       <c r="O44" s="6">
         <f>1/(1-POWER(1-$F44*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>51.95809691416796</v>
+        <v>52.328455740305785</v>
       </c>
       <c r="P44" s="6">
         <f>1/(1-POWER(1-$F44*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="Q44" s="16">
         <f>1/(1-POWER(1-$F44*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>360.84560105190172</v>
+        <v>363.43819199656815</v>
       </c>
       <c r="R44" s="16">
         <f>1/(1-POWER(1-$F44*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3243.8083589698131</v>
+        <v>3267.1416921215396</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -12451,7 +12451,7 @@
         <v>0.02</v>
       </c>
       <c r="F45" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G45" s="3">
@@ -12459,48 +12459,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H45" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I45" s="8">
         <f>1/(1-POWER(1-$F45*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J45" s="8">
         <f>1/(1-POWER(1-$F45*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K45" s="10">
         <f>1/(1-POWER(1-$F45*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L45" s="10">
         <f>1/(1-POWER(1-$F45*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M45" s="12">
         <f>1/(1-POWER(1-$F45*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N45" s="12">
         <f>1/(1-POWER(1-$F45*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O45" s="6">
         <f>1/(1-POWER(1-$F45*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P45" s="6">
         <f>1/(1-POWER(1-$F45*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q45" s="16">
         <f>1/(1-POWER(1-$F45*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R45" s="16">
         <f>1/(1-POWER(1-$F45*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
@@ -12521,7 +12521,7 @@
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F46" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G46" s="3">
@@ -12529,48 +12529,48 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H46" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I46" s="8">
         <f>1/(1-POWER(1-$F46*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>5.7137417013118368</v>
+        <v>5.7512009380835991</v>
       </c>
       <c r="J46" s="8">
         <f>1/(1-POWER(1-$F46*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>47.481600280957529</v>
+        <v>47.819751887369826</v>
       </c>
       <c r="K46" s="10">
         <f>1/(1-POWER(1-$F46*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.064960983515661</v>
+        <v>9.126619822082489</v>
       </c>
       <c r="L46" s="10">
         <f>1/(1-POWER(1-$F46*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>77.698299006688089</v>
+        <v>78.253846868491379</v>
       </c>
       <c r="M46" s="12">
         <f>1/(1-POWER(1-$F46*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>17.640344596567786</v>
+        <v>17.763766692007298</v>
       </c>
       <c r="N46" s="12">
         <f>1/(1-POWER(1-$F46*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>154.9199827506408</v>
+        <v>156.03109001607743</v>
       </c>
       <c r="O46" s="6">
         <f>1/(1-POWER(1-$F46*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>51.95809691416796</v>
+        <v>52.328455740305785</v>
       </c>
       <c r="P46" s="6">
         <f>1/(1-POWER(1-$F46*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="Q46" s="16">
         <f>1/(1-POWER(1-$F46*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>360.84560105190172</v>
+        <v>363.43819199656815</v>
       </c>
       <c r="R46" s="16">
         <f>1/(1-POWER(1-$F46*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3243.8083589698131</v>
+        <v>3267.1416921215396</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -12591,7 +12591,7 @@
         <v>0.02</v>
       </c>
       <c r="F47" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G47" s="3">
@@ -12599,48 +12599,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H47" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I47" s="8">
         <f>1/(1-POWER(1-$F47*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J47" s="8">
         <f>1/(1-POWER(1-$F47*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K47" s="10">
         <f>1/(1-POWER(1-$F47*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L47" s="10">
         <f>1/(1-POWER(1-$F47*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M47" s="12">
         <f>1/(1-POWER(1-$F47*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N47" s="12">
         <f>1/(1-POWER(1-$F47*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O47" s="6">
         <f>1/(1-POWER(1-$F47*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P47" s="6">
         <f>1/(1-POWER(1-$F47*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q47" s="16">
         <f>1/(1-POWER(1-$F47*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R47" s="16">
         <f>1/(1-POWER(1-$F47*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
@@ -12661,7 +12661,7 @@
         <v>1.8749999999999999E-2</v>
       </c>
       <c r="F48" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.8749999999999985E-2</v>
       </c>
       <c r="G48" s="3">
@@ -12669,48 +12669,48 @@
         <v>0.31515325639173553</v>
       </c>
       <c r="H48" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.1730593916408716</v>
       </c>
       <c r="I48" s="8">
         <f>1/(1-POWER(1-$F48*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.4578458934330172</v>
+        <v>6.5006872150229773</v>
       </c>
       <c r="J48" s="8">
         <f>1/(1-POWER(1-$F48*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>54.196354855722817</v>
+        <v>54.582817222883541</v>
       </c>
       <c r="K48" s="10">
         <f>1/(1-POWER(1-$F48*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>10.289493630089176</v>
+        <v>10.359979540057177</v>
       </c>
       <c r="L48" s="10">
         <f>1/(1-POWER(1-$F48*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>88.729910402846656</v>
+        <v>89.364824306266769</v>
       </c>
       <c r="M48" s="12">
         <f>1/(1-POWER(1-$F48*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>20.091236650595796</v>
+        <v>20.232299777012749</v>
       </c>
       <c r="N48" s="12">
         <f>1/(1-POWER(1-$F48*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>176.98340751640595</v>
+        <v>178.25324542143156</v>
       </c>
       <c r="O48" s="6">
         <f>1/(1-POWER(1-$F48*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>59.312392255803132</v>
+        <v>59.73566257905977</v>
       </c>
       <c r="P48" s="6">
         <f>1/(1-POWER(1-$F48*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>529.99896651203778</v>
+        <v>533.80848919998323</v>
       </c>
       <c r="Q48" s="16">
         <f>1/(1-POWER(1-$F48*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>412.3270536965432</v>
+        <v>415.29001521748876</v>
       </c>
       <c r="R48" s="16">
         <f>1/(1-POWER(1-$F48*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3707.1416890942214</v>
+        <v>3733.8083555993026</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
@@ -12731,7 +12731,7 @@
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F49" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G49" s="3">
@@ -12739,48 +12739,48 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H49" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I49" s="8">
         <f>1/(1-POWER(1-$F49*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>5.7137417013118368</v>
+        <v>5.7512009380835991</v>
       </c>
       <c r="J49" s="8">
         <f>1/(1-POWER(1-$F49*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>47.481600280957529</v>
+        <v>47.819751887369826</v>
       </c>
       <c r="K49" s="10">
         <f>1/(1-POWER(1-$F49*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.064960983515661</v>
+        <v>9.126619822082489</v>
       </c>
       <c r="L49" s="10">
         <f>1/(1-POWER(1-$F49*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>77.698299006688089</v>
+        <v>78.253846868491379</v>
       </c>
       <c r="M49" s="12">
         <f>1/(1-POWER(1-$F49*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>17.640344596567786</v>
+        <v>17.763766692007298</v>
       </c>
       <c r="N49" s="12">
         <f>1/(1-POWER(1-$F49*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>154.9199827506408</v>
+        <v>156.03109001607743</v>
       </c>
       <c r="O49" s="6">
         <f>1/(1-POWER(1-$F49*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>51.95809691416796</v>
+        <v>52.328455740305785</v>
       </c>
       <c r="P49" s="6">
         <f>1/(1-POWER(1-$F49*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="Q49" s="16">
         <f>1/(1-POWER(1-$F49*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>360.84560105190172</v>
+        <v>363.43819199656815</v>
       </c>
       <c r="R49" s="16">
         <f>1/(1-POWER(1-$F49*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3243.8083589698131</v>
+        <v>3267.1416921215396</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
@@ -12801,7 +12801,7 @@
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F50" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G50" s="3">
@@ -12809,48 +12809,48 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H50" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I50" s="8">
         <f>1/(1-POWER(1-$F50*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>5.7137417013118368</v>
+        <v>5.7512009380835991</v>
       </c>
       <c r="J50" s="8">
         <f>1/(1-POWER(1-$F50*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>47.481600280957529</v>
+        <v>47.819751887369826</v>
       </c>
       <c r="K50" s="10">
         <f>1/(1-POWER(1-$F50*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.064960983515661</v>
+        <v>9.126619822082489</v>
       </c>
       <c r="L50" s="10">
         <f>1/(1-POWER(1-$F50*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>77.698299006688089</v>
+        <v>78.253846868491379</v>
       </c>
       <c r="M50" s="12">
         <f>1/(1-POWER(1-$F50*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>17.640344596567786</v>
+        <v>17.763766692007298</v>
       </c>
       <c r="N50" s="12">
         <f>1/(1-POWER(1-$F50*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>154.9199827506408</v>
+        <v>156.03109001607743</v>
       </c>
       <c r="O50" s="6">
         <f>1/(1-POWER(1-$F50*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>51.95809691416796</v>
+        <v>52.328455740305785</v>
       </c>
       <c r="P50" s="6">
         <f>1/(1-POWER(1-$F50*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="Q50" s="16">
         <f>1/(1-POWER(1-$F50*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>360.84560105190172</v>
+        <v>363.43819199656815</v>
       </c>
       <c r="R50" s="16">
         <f>1/(1-POWER(1-$F50*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3243.8083589698131</v>
+        <v>3267.1416921215396</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
@@ -12871,7 +12871,7 @@
         <v>0.02</v>
       </c>
       <c r="F51" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G51" s="3">
@@ -12879,48 +12879,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H51" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I51" s="8">
         <f>1/(1-POWER(1-$F51*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J51" s="8">
         <f>1/(1-POWER(1-$F51*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K51" s="10">
         <f>1/(1-POWER(1-$F51*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L51" s="10">
         <f>1/(1-POWER(1-$F51*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M51" s="12">
         <f>1/(1-POWER(1-$F51*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N51" s="12">
         <f>1/(1-POWER(1-$F51*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O51" s="6">
         <f>1/(1-POWER(1-$F51*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P51" s="6">
         <f>1/(1-POWER(1-$F51*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q51" s="16">
         <f>1/(1-POWER(1-$F51*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R51" s="16">
         <f>1/(1-POWER(1-$F51*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
@@ -12941,7 +12941,7 @@
         <v>0.02</v>
       </c>
       <c r="F52" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G52" s="3">
@@ -12949,48 +12949,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H52" s="3">
-        <f t="shared" ref="H52:H69" si="5">1/G52</f>
+        <f t="shared" ref="H52:H69" si="4">1/G52</f>
         <v>3.0084957370373568</v>
       </c>
       <c r="I52" s="8">
         <f>1/(1-POWER(1-$F52*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J52" s="8">
         <f>1/(1-POWER(1-$F52*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K52" s="10">
         <f>1/(1-POWER(1-$F52*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L52" s="10">
         <f>1/(1-POWER(1-$F52*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M52" s="12">
         <f>1/(1-POWER(1-$F52*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N52" s="12">
         <f>1/(1-POWER(1-$F52*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O52" s="6">
         <f>1/(1-POWER(1-$F52*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P52" s="6">
         <f>1/(1-POWER(1-$F52*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q52" s="16">
         <f>1/(1-POWER(1-$F52*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R52" s="16">
         <f>1/(1-POWER(1-$F52*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
@@ -13011,7 +13011,7 @@
         <v>0.02</v>
       </c>
       <c r="F53" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G53" s="3">
@@ -13019,48 +13019,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H53" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I53" s="8">
         <f>1/(1-POWER(1-$F53*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J53" s="8">
         <f>1/(1-POWER(1-$F53*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K53" s="10">
         <f>1/(1-POWER(1-$F53*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L53" s="10">
         <f>1/(1-POWER(1-$F53*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M53" s="12">
         <f>1/(1-POWER(1-$F53*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N53" s="12">
         <f>1/(1-POWER(1-$F53*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O53" s="6">
         <f>1/(1-POWER(1-$F53*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P53" s="6">
         <f>1/(1-POWER(1-$F53*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q53" s="16">
         <f>1/(1-POWER(1-$F53*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R53" s="16">
         <f>1/(1-POWER(1-$F53*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
@@ -13081,7 +13081,7 @@
         <v>0.02</v>
       </c>
       <c r="F54" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G54" s="3">
@@ -13089,48 +13089,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H54" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I54" s="8">
         <f>1/(1-POWER(1-$F54*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J54" s="8">
         <f>1/(1-POWER(1-$F54*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K54" s="10">
         <f>1/(1-POWER(1-$F54*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L54" s="10">
         <f>1/(1-POWER(1-$F54*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M54" s="12">
         <f>1/(1-POWER(1-$F54*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N54" s="12">
         <f>1/(1-POWER(1-$F54*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O54" s="6">
         <f>1/(1-POWER(1-$F54*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P54" s="6">
         <f>1/(1-POWER(1-$F54*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q54" s="16">
         <f>1/(1-POWER(1-$F54*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R54" s="16">
         <f>1/(1-POWER(1-$F54*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
@@ -13151,7 +13151,7 @@
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F55" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G55" s="3">
@@ -13159,48 +13159,48 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H55" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I55" s="8">
         <f>1/(1-POWER(1-$F55*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>5.7137417013118368</v>
+        <v>5.7512009380835991</v>
       </c>
       <c r="J55" s="8">
         <f>1/(1-POWER(1-$F55*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>47.481600280957529</v>
+        <v>47.819751887369826</v>
       </c>
       <c r="K55" s="10">
         <f>1/(1-POWER(1-$F55*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.064960983515661</v>
+        <v>9.126619822082489</v>
       </c>
       <c r="L55" s="10">
         <f>1/(1-POWER(1-$F55*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>77.698299006688089</v>
+        <v>78.253846868491379</v>
       </c>
       <c r="M55" s="12">
         <f>1/(1-POWER(1-$F55*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>17.640344596567786</v>
+        <v>17.763766692007298</v>
       </c>
       <c r="N55" s="12">
         <f>1/(1-POWER(1-$F55*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>154.9199827506408</v>
+        <v>156.03109001607743</v>
       </c>
       <c r="O55" s="6">
         <f>1/(1-POWER(1-$F55*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>51.95809691416796</v>
+        <v>52.328455740305785</v>
       </c>
       <c r="P55" s="6">
         <f>1/(1-POWER(1-$F55*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="Q55" s="16">
         <f>1/(1-POWER(1-$F55*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>360.84560105190172</v>
+        <v>363.43819199656815</v>
       </c>
       <c r="R55" s="16">
         <f>1/(1-POWER(1-$F55*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3243.8083589698131</v>
+        <v>3267.1416921215396</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
@@ -13221,7 +13221,7 @@
         <v>1.8749999999999999E-2</v>
       </c>
       <c r="F56" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.8749999999999985E-2</v>
       </c>
       <c r="G56" s="3">
@@ -13229,48 +13229,48 @@
         <v>0.31515325639173553</v>
       </c>
       <c r="H56" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.1730593916408716</v>
       </c>
       <c r="I56" s="8">
         <f>1/(1-POWER(1-$F56*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.4578458934330172</v>
+        <v>6.5006872150229773</v>
       </c>
       <c r="J56" s="8">
         <f>1/(1-POWER(1-$F56*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>54.196354855722817</v>
+        <v>54.582817222883541</v>
       </c>
       <c r="K56" s="10">
         <f>1/(1-POWER(1-$F56*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>10.289493630089176</v>
+        <v>10.359979540057177</v>
       </c>
       <c r="L56" s="10">
         <f>1/(1-POWER(1-$F56*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>88.729910402846656</v>
+        <v>89.364824306266769</v>
       </c>
       <c r="M56" s="12">
         <f>1/(1-POWER(1-$F56*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>20.091236650595796</v>
+        <v>20.232299777012749</v>
       </c>
       <c r="N56" s="12">
         <f>1/(1-POWER(1-$F56*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>176.98340751640595</v>
+        <v>178.25324542143156</v>
       </c>
       <c r="O56" s="6">
         <f>1/(1-POWER(1-$F56*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>59.312392255803132</v>
+        <v>59.73566257905977</v>
       </c>
       <c r="P56" s="6">
         <f>1/(1-POWER(1-$F56*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>529.99896651203778</v>
+        <v>533.80848919998323</v>
       </c>
       <c r="Q56" s="16">
         <f>1/(1-POWER(1-$F56*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>412.3270536965432</v>
+        <v>415.29001521748876</v>
       </c>
       <c r="R56" s="16">
         <f>1/(1-POWER(1-$F56*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3707.1416890942214</v>
+        <v>3733.8083555993026</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
@@ -13291,7 +13291,7 @@
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F57" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G57" s="3">
@@ -13299,48 +13299,48 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H57" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I57" s="8">
         <f>1/(1-POWER(1-$F57*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>5.7137417013118368</v>
+        <v>5.7512009380835991</v>
       </c>
       <c r="J57" s="8">
         <f>1/(1-POWER(1-$F57*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>47.481600280957529</v>
+        <v>47.819751887369826</v>
       </c>
       <c r="K57" s="10">
         <f>1/(1-POWER(1-$F57*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.064960983515661</v>
+        <v>9.126619822082489</v>
       </c>
       <c r="L57" s="10">
         <f>1/(1-POWER(1-$F57*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>77.698299006688089</v>
+        <v>78.253846868491379</v>
       </c>
       <c r="M57" s="12">
         <f>1/(1-POWER(1-$F57*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>17.640344596567786</v>
+        <v>17.763766692007298</v>
       </c>
       <c r="N57" s="12">
         <f>1/(1-POWER(1-$F57*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>154.9199827506408</v>
+        <v>156.03109001607743</v>
       </c>
       <c r="O57" s="6">
         <f>1/(1-POWER(1-$F57*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>51.95809691416796</v>
+        <v>52.328455740305785</v>
       </c>
       <c r="P57" s="6">
         <f>1/(1-POWER(1-$F57*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="Q57" s="16">
         <f>1/(1-POWER(1-$F57*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>360.84560105190172</v>
+        <v>363.43819199656815</v>
       </c>
       <c r="R57" s="16">
         <f>1/(1-POWER(1-$F57*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3243.8083589698131</v>
+        <v>3267.1416921215396</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
@@ -13361,7 +13361,7 @@
         <v>2.1428571428571429E-2</v>
       </c>
       <c r="F58" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1428571428571415E-2</v>
       </c>
       <c r="G58" s="3">
@@ -13369,48 +13369,48 @@
         <v>0.35158861821263243</v>
       </c>
       <c r="H58" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.8442331412310504</v>
       </c>
       <c r="I58" s="8">
         <f>1/(1-POWER(1-$F58*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>5.7137417013118368</v>
+        <v>5.7512009380835991</v>
       </c>
       <c r="J58" s="8">
         <f>1/(1-POWER(1-$F58*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>47.481600280957529</v>
+        <v>47.819751887369826</v>
       </c>
       <c r="K58" s="10">
         <f>1/(1-POWER(1-$F58*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.064960983515661</v>
+        <v>9.126619822082489</v>
       </c>
       <c r="L58" s="10">
         <f>1/(1-POWER(1-$F58*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>77.698299006688089</v>
+        <v>78.253846868491379</v>
       </c>
       <c r="M58" s="12">
         <f>1/(1-POWER(1-$F58*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>17.640344596567786</v>
+        <v>17.763766692007298</v>
       </c>
       <c r="N58" s="12">
         <f>1/(1-POWER(1-$F58*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>154.9199827506408</v>
+        <v>156.03109001607743</v>
       </c>
       <c r="O58" s="6">
         <f>1/(1-POWER(1-$F58*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>51.95809691416796</v>
+        <v>52.328455740305785</v>
       </c>
       <c r="P58" s="6">
         <f>1/(1-POWER(1-$F58*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>463.80851274980165</v>
+        <v>467.14184480110237</v>
       </c>
       <c r="Q58" s="16">
         <f>1/(1-POWER(1-$F58*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>360.84560105190172</v>
+        <v>363.43819199656815</v>
       </c>
       <c r="R58" s="16">
         <f>1/(1-POWER(1-$F58*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3243.8083589698131</v>
+        <v>3267.1416921215396</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
@@ -13431,7 +13431,7 @@
         <v>1.8749999999999999E-2</v>
       </c>
       <c r="F59" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.8749999999999985E-2</v>
       </c>
       <c r="G59" s="3">
@@ -13439,48 +13439,48 @@
         <v>0.31515325639173553</v>
       </c>
       <c r="H59" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.1730593916408716</v>
       </c>
       <c r="I59" s="8">
         <f>1/(1-POWER(1-$F59*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.4578458934330172</v>
+        <v>6.5006872150229773</v>
       </c>
       <c r="J59" s="8">
         <f>1/(1-POWER(1-$F59*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>54.196354855722817</v>
+        <v>54.582817222883541</v>
       </c>
       <c r="K59" s="10">
         <f>1/(1-POWER(1-$F59*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>10.289493630089176</v>
+        <v>10.359979540057177</v>
       </c>
       <c r="L59" s="10">
         <f>1/(1-POWER(1-$F59*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>88.729910402846656</v>
+        <v>89.364824306266769</v>
       </c>
       <c r="M59" s="12">
         <f>1/(1-POWER(1-$F59*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>20.091236650595796</v>
+        <v>20.232299777012749</v>
       </c>
       <c r="N59" s="12">
         <f>1/(1-POWER(1-$F59*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>176.98340751640595</v>
+        <v>178.25324542143156</v>
       </c>
       <c r="O59" s="6">
         <f>1/(1-POWER(1-$F59*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>59.312392255803132</v>
+        <v>59.73566257905977</v>
       </c>
       <c r="P59" s="6">
         <f>1/(1-POWER(1-$F59*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>529.99896651203778</v>
+        <v>533.80848919998323</v>
       </c>
       <c r="Q59" s="16">
         <f>1/(1-POWER(1-$F59*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>412.3270536965432</v>
+        <v>415.29001521748876</v>
       </c>
       <c r="R59" s="16">
         <f>1/(1-POWER(1-$F59*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3707.1416890942214</v>
+        <v>3733.8083555993026</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
@@ -13501,7 +13501,7 @@
         <v>1.8749999999999999E-2</v>
       </c>
       <c r="F60" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.8749999999999985E-2</v>
       </c>
       <c r="G60" s="3">
@@ -13509,48 +13509,48 @@
         <v>0.31515325639173553</v>
       </c>
       <c r="H60" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.1730593916408716</v>
       </c>
       <c r="I60" s="8">
         <f>1/(1-POWER(1-$F60*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.4578458934330172</v>
+        <v>6.5006872150229773</v>
       </c>
       <c r="J60" s="8">
         <f>1/(1-POWER(1-$F60*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>54.196354855722817</v>
+        <v>54.582817222883541</v>
       </c>
       <c r="K60" s="10">
         <f>1/(1-POWER(1-$F60*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>10.289493630089176</v>
+        <v>10.359979540057177</v>
       </c>
       <c r="L60" s="10">
         <f>1/(1-POWER(1-$F60*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>88.729910402846656</v>
+        <v>89.364824306266769</v>
       </c>
       <c r="M60" s="12">
         <f>1/(1-POWER(1-$F60*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>20.091236650595796</v>
+        <v>20.232299777012749</v>
       </c>
       <c r="N60" s="12">
         <f>1/(1-POWER(1-$F60*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>176.98340751640595</v>
+        <v>178.25324542143156</v>
       </c>
       <c r="O60" s="6">
         <f>1/(1-POWER(1-$F60*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>59.312392255803132</v>
+        <v>59.73566257905977</v>
       </c>
       <c r="P60" s="6">
         <f>1/(1-POWER(1-$F60*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>529.99896651203778</v>
+        <v>533.80848919998323</v>
       </c>
       <c r="Q60" s="16">
         <f>1/(1-POWER(1-$F60*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>412.3270536965432</v>
+        <v>415.29001521748876</v>
       </c>
       <c r="R60" s="16">
         <f>1/(1-POWER(1-$F60*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3707.1416890942214</v>
+        <v>3733.8083555993026</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
@@ -13571,7 +13571,7 @@
         <v>1.8749999999999999E-2</v>
       </c>
       <c r="F61" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.8749999999999985E-2</v>
       </c>
       <c r="G61" s="3">
@@ -13579,48 +13579,48 @@
         <v>0.31515325639173553</v>
       </c>
       <c r="H61" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.1730593916408716</v>
       </c>
       <c r="I61" s="8">
         <f>1/(1-POWER(1-$F61*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.4578458934330172</v>
+        <v>6.5006872150229773</v>
       </c>
       <c r="J61" s="8">
         <f>1/(1-POWER(1-$F61*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>54.196354855722817</v>
+        <v>54.582817222883541</v>
       </c>
       <c r="K61" s="10">
         <f>1/(1-POWER(1-$F61*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>10.289493630089176</v>
+        <v>10.359979540057177</v>
       </c>
       <c r="L61" s="10">
         <f>1/(1-POWER(1-$F61*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>88.729910402846656</v>
+        <v>89.364824306266769</v>
       </c>
       <c r="M61" s="12">
         <f>1/(1-POWER(1-$F61*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>20.091236650595796</v>
+        <v>20.232299777012749</v>
       </c>
       <c r="N61" s="12">
         <f>1/(1-POWER(1-$F61*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>176.98340751640595</v>
+        <v>178.25324542143156</v>
       </c>
       <c r="O61" s="6">
         <f>1/(1-POWER(1-$F61*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>59.312392255803132</v>
+        <v>59.73566257905977</v>
       </c>
       <c r="P61" s="6">
         <f>1/(1-POWER(1-$F61*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>529.99896651203778</v>
+        <v>533.80848919998323</v>
       </c>
       <c r="Q61" s="16">
         <f>1/(1-POWER(1-$F61*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>412.3270536965432</v>
+        <v>415.29001521748876</v>
       </c>
       <c r="R61" s="16">
         <f>1/(1-POWER(1-$F61*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3707.1416890942214</v>
+        <v>3733.8083555993026</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
@@ -13641,7 +13641,7 @@
         <v>0.02</v>
       </c>
       <c r="F62" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G62" s="3">
@@ -13649,48 +13649,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H62" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I62" s="8">
         <f>1/(1-POWER(1-$F62*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J62" s="8">
         <f>1/(1-POWER(1-$F62*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K62" s="10">
         <f>1/(1-POWER(1-$F62*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L62" s="10">
         <f>1/(1-POWER(1-$F62*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M62" s="12">
         <f>1/(1-POWER(1-$F62*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N62" s="12">
         <f>1/(1-POWER(1-$F62*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O62" s="6">
         <f>1/(1-POWER(1-$F62*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P62" s="6">
         <f>1/(1-POWER(1-$F62*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q62" s="16">
         <f>1/(1-POWER(1-$F62*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R62" s="16">
         <f>1/(1-POWER(1-$F62*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
@@ -13711,7 +13711,7 @@
         <v>1.8749999999999999E-2</v>
       </c>
       <c r="F63" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.8749999999999985E-2</v>
       </c>
       <c r="G63" s="3">
@@ -13719,48 +13719,48 @@
         <v>0.31515325639173553</v>
       </c>
       <c r="H63" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.1730593916408716</v>
       </c>
       <c r="I63" s="8">
         <f>1/(1-POWER(1-$F63*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.4578458934330172</v>
+        <v>6.5006872150229773</v>
       </c>
       <c r="J63" s="8">
         <f>1/(1-POWER(1-$F63*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>54.196354855722817</v>
+        <v>54.582817222883541</v>
       </c>
       <c r="K63" s="10">
         <f>1/(1-POWER(1-$F63*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>10.289493630089176</v>
+        <v>10.359979540057177</v>
       </c>
       <c r="L63" s="10">
         <f>1/(1-POWER(1-$F63*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>88.729910402846656</v>
+        <v>89.364824306266769</v>
       </c>
       <c r="M63" s="12">
         <f>1/(1-POWER(1-$F63*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>20.091236650595796</v>
+        <v>20.232299777012749</v>
       </c>
       <c r="N63" s="12">
         <f>1/(1-POWER(1-$F63*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>176.98340751640595</v>
+        <v>178.25324542143156</v>
       </c>
       <c r="O63" s="6">
         <f>1/(1-POWER(1-$F63*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>59.312392255803132</v>
+        <v>59.73566257905977</v>
       </c>
       <c r="P63" s="6">
         <f>1/(1-POWER(1-$F63*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>529.99896651203778</v>
+        <v>533.80848919998323</v>
       </c>
       <c r="Q63" s="16">
         <f>1/(1-POWER(1-$F63*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>412.3270536965432</v>
+        <v>415.29001521748876</v>
       </c>
       <c r="R63" s="16">
         <f>1/(1-POWER(1-$F63*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3707.1416890942214</v>
+        <v>3733.8083555993026</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
@@ -13781,7 +13781,7 @@
         <v>0.02</v>
       </c>
       <c r="F64" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G64" s="3">
@@ -13789,48 +13789,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H64" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I64" s="8">
         <f>1/(1-POWER(1-$F64*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J64" s="8">
         <f>1/(1-POWER(1-$F64*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K64" s="10">
         <f>1/(1-POWER(1-$F64*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L64" s="10">
         <f>1/(1-POWER(1-$F64*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M64" s="12">
         <f>1/(1-POWER(1-$F64*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N64" s="12">
         <f>1/(1-POWER(1-$F64*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O64" s="6">
         <f>1/(1-POWER(1-$F64*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P64" s="6">
         <f>1/(1-POWER(1-$F64*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q64" s="16">
         <f>1/(1-POWER(1-$F64*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R64" s="16">
         <f>1/(1-POWER(1-$F64*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
@@ -13851,7 +13851,7 @@
         <v>0.02</v>
       </c>
       <c r="F65" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G65" s="3">
@@ -13859,48 +13859,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H65" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I65" s="8">
         <f>1/(1-POWER(1-$F65*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J65" s="8">
         <f>1/(1-POWER(1-$F65*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K65" s="10">
         <f>1/(1-POWER(1-$F65*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L65" s="10">
         <f>1/(1-POWER(1-$F65*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M65" s="12">
         <f>1/(1-POWER(1-$F65*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N65" s="12">
         <f>1/(1-POWER(1-$F65*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O65" s="6">
         <f>1/(1-POWER(1-$F65*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P65" s="6">
         <f>1/(1-POWER(1-$F65*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q65" s="16">
         <f>1/(1-POWER(1-$F65*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R65" s="16">
         <f>1/(1-POWER(1-$F65*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
@@ -13921,7 +13921,7 @@
         <v>0.02</v>
       </c>
       <c r="F66" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G66" s="3">
@@ -13929,48 +13929,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H66" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I66" s="8">
         <f>1/(1-POWER(1-$F66*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J66" s="8">
         <f>1/(1-POWER(1-$F66*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K66" s="10">
         <f>1/(1-POWER(1-$F66*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L66" s="10">
         <f>1/(1-POWER(1-$F66*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M66" s="12">
         <f>1/(1-POWER(1-$F66*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N66" s="12">
         <f>1/(1-POWER(1-$F66*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O66" s="6">
         <f>1/(1-POWER(1-$F66*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P66" s="6">
         <f>1/(1-POWER(1-$F66*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q66" s="16">
         <f>1/(1-POWER(1-$F66*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R66" s="16">
         <f>1/(1-POWER(1-$F66*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
@@ -13991,7 +13991,7 @@
         <v>0.02</v>
       </c>
       <c r="F67" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G67" s="3">
@@ -13999,48 +13999,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H67" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I67" s="8">
         <f>1/(1-POWER(1-$F67*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J67" s="8">
         <f>1/(1-POWER(1-$F67*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K67" s="10">
         <f>1/(1-POWER(1-$F67*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L67" s="10">
         <f>1/(1-POWER(1-$F67*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M67" s="12">
         <f>1/(1-POWER(1-$F67*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N67" s="12">
         <f>1/(1-POWER(1-$F67*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O67" s="6">
         <f>1/(1-POWER(1-$F67*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P67" s="6">
         <f>1/(1-POWER(1-$F67*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q67" s="16">
         <f>1/(1-POWER(1-$F67*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R67" s="16">
         <f>1/(1-POWER(1-$F67*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
@@ -14061,7 +14061,7 @@
         <v>0.02</v>
       </c>
       <c r="F68" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G68" s="3">
@@ -14069,48 +14069,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H68" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I68" s="8">
         <f>1/(1-POWER(1-$F68*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J68" s="8">
         <f>1/(1-POWER(1-$F68*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K68" s="10">
         <f>1/(1-POWER(1-$F68*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L68" s="10">
         <f>1/(1-POWER(1-$F68*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M68" s="12">
         <f>1/(1-POWER(1-$F68*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N68" s="12">
         <f>1/(1-POWER(1-$F68*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O68" s="6">
         <f>1/(1-POWER(1-$F68*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P68" s="6">
         <f>1/(1-POWER(1-$F68*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q68" s="16">
         <f>1/(1-POWER(1-$F68*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R68" s="16">
         <f>1/(1-POWER(1-$F68*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
@@ -14131,7 +14131,7 @@
         <v>0.02</v>
       </c>
       <c r="F69" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9999999999999987E-2</v>
       </c>
       <c r="G69" s="3">
@@ -14139,48 +14139,48 @@
         <v>0.33239202824490588</v>
       </c>
       <c r="H69" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.0084957370373568</v>
       </c>
       <c r="I69" s="8">
         <f>1/(1-POWER(1-$F69*$F$3*$F$8,Donnees!$D$4))</f>
-        <v>6.0857267969823825</v>
+        <v>6.1258775581006057</v>
       </c>
       <c r="J69" s="8">
         <f>1/(1-POWER(1-$F69*$F$3*$F$9,Donnees!$D$4))</f>
-        <v>50.838970189131004</v>
+        <v>51.201277228705251</v>
       </c>
       <c r="K69" s="10">
         <f>1/(1-POWER(1-$F69*$F$4*$F$8,Donnees!$D$4))</f>
-        <v>9.6771866564579643</v>
+        <v>9.7432593227673596</v>
       </c>
       <c r="L69" s="10">
         <f>1/(1-POWER(1-$F69*$F$4*$F$9,Donnees!$D$4))</f>
-        <v>83.214100215587194</v>
+        <v>83.809331130297309</v>
       </c>
       <c r="M69" s="12">
         <f>1/(1-POWER(1-$F69*$F$5*$F$8,Donnees!$D$4))</f>
-        <v>18.865770363543039</v>
+        <v>18.998013119688618</v>
       </c>
       <c r="N69" s="12">
         <f>1/(1-POWER(1-$F69*$F$5*$F$9,Donnees!$D$4))</f>
-        <v>165.95169288991335</v>
+        <v>167.14216549121571</v>
       </c>
       <c r="O69" s="6">
         <f>1/(1-POWER(1-$F69*$F$6*$F$8,Donnees!$D$4))</f>
-        <v>55.635237848282955</v>
+        <v>56.032052471159972</v>
       </c>
       <c r="P69" s="6">
         <f>1/(1-POWER(1-$F69*$F$6*$F$9,Donnees!$D$4))</f>
-        <v>496.90373888289122</v>
+        <v>500.47516625842803</v>
       </c>
       <c r="Q69" s="16">
         <f>1/(1-POWER(1-$F69*$F$7*$F$8,Donnees!$D$4))</f>
-        <v>386.58632641271407</v>
+        <v>389.3641026523818</v>
       </c>
       <c r="R69" s="16">
         <f>1/(1-POWER(1-$F69*$F$7*$F$9,Donnees!$D$4))</f>
-        <v>3475.4750239175241</v>
+        <v>3500.4750237455487</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
@@ -14202,35 +14202,35 @@
       </c>
       <c r="I71" s="14" cm="1">
         <f t="array" ref="I71">SUM((1-_xlfn._xlws.FILTER(1/I$20:I$69,(1/I$20:I$69)&lt;&gt;""))^($H71))</f>
-        <v>0.2434613276379263</v>
+        <v>0.25282118995293479</v>
       </c>
       <c r="J71" s="14" cm="1">
         <f t="array" ref="J71">SUM((1-_xlfn._xlws.FILTER(1/J$20:J$69,(1/J$20:J$69)&lt;&gt;""))^($H71))</f>
-        <v>27.569539872237119</v>
+        <v>27.686946592554253</v>
       </c>
       <c r="K71" s="14" cm="1">
         <f t="array" ref="K71">SUM((1-_xlfn._xlws.FILTER(1/K$20:K$69,(1/K$20:K$69)&lt;&gt;""))^($H71))</f>
-        <v>1.9369651090038544</v>
+        <v>1.9822724643440246</v>
       </c>
       <c r="L71" s="14" cm="1">
         <f t="array" ref="L71">SUM((1-_xlfn._xlws.FILTER(1/L$20:L$69,(1/L$20:L$69)&lt;&gt;""))^($H71))</f>
-        <v>34.798337938919637</v>
+        <v>34.888511641558161</v>
       </c>
       <c r="M71" s="14" cm="1">
         <f t="array" ref="M71">SUM((1-_xlfn._xlws.FILTER(1/M$20:M$69,(1/M$20:M$69)&lt;&gt;""))^($H71))</f>
-        <v>9.8087689322632077</v>
+        <v>9.9233317112353596</v>
       </c>
       <c r="N71" s="14" cm="1">
         <f t="array" ref="N71">SUM((1-_xlfn._xlws.FILTER(1/N$20:N$69,(1/N$20:N$69)&lt;&gt;""))^($H71))</f>
-        <v>41.710876920863612</v>
+        <v>41.764905773737368</v>
       </c>
       <c r="O71" s="14" cm="1">
         <f t="array" ref="O71">SUM((1-_xlfn._xlws.FILTER(1/O$20:O$69,(1/O$20:O$69)&lt;&gt;""))^($H71))</f>
-        <v>29.03341989239447</v>
+        <v>29.146301200516572</v>
       </c>
       <c r="P71" s="14" cm="1">
         <f t="array" ref="P71">SUM((1-_xlfn._xlws.FILTER(1/P$20:P$69,(1/P$20:P$69)&lt;&gt;""))^($H71))</f>
-        <v>47.068081600348016</v>
+        <v>47.088400628583898</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
@@ -14239,35 +14239,35 @@
       </c>
       <c r="I72" s="14" cm="1">
         <f t="array" ref="I72">SUM((1-_xlfn._xlws.FILTER(1/I$20:I$69,(1/I$20:I$69)&lt;&gt;""))^($H72))</f>
-        <v>6.0746850639769249E-24</v>
+        <v>8.9839961290572016E-24</v>
       </c>
       <c r="J72" s="14" cm="1">
         <f t="array" ref="J72">SUM((1-_xlfn._xlws.FILTER(1/J$20:J$69,(1/J$20:J$69)&lt;&gt;""))^($H72))</f>
-        <v>3.9711157108312689E-2</v>
+        <v>4.1751256430935246E-2</v>
       </c>
       <c r="K72" s="14" cm="1">
         <f t="array" ref="K72">SUM((1-_xlfn._xlws.FILTER(1/K$20:K$69,(1/K$20:K$69)&lt;&gt;""))^($H72))</f>
-        <v>1.2521163371041199E-14</v>
+        <v>1.5903633723943963E-14</v>
       </c>
       <c r="L72" s="14" cm="1">
         <f t="array" ref="L72">SUM((1-_xlfn._xlws.FILTER(1/L$20:L$69,(1/L$20:L$69)&lt;&gt;""))^($H72))</f>
-        <v>0.63046827505992153</v>
+        <v>0.65028135657011221</v>
       </c>
       <c r="M72" s="14" cm="1">
         <f t="array" ref="M72">SUM((1-_xlfn._xlws.FILTER(1/M$20:M$69,(1/M$20:M$69)&lt;&gt;""))^($H72))</f>
-        <v>3.2307203383089968E-7</v>
+        <v>3.6665848268600179E-7</v>
       </c>
       <c r="N72" s="14" cm="1">
         <f t="array" ref="N72">SUM((1-_xlfn._xlws.FILTER(1/N$20:N$69,(1/N$20:N$69)&lt;&gt;""))^($H72))</f>
-        <v>5.5588260647850234</v>
+        <v>5.6463515485136497</v>
       </c>
       <c r="O72" s="14" cm="1">
         <f t="array" ref="O72">SUM((1-_xlfn._xlws.FILTER(1/O$20:O$69,(1/O$20:O$69)&lt;&gt;""))^($H72))</f>
-        <v>7.3148239691921149E-2</v>
+        <v>7.6583913475761017E-2</v>
       </c>
       <c r="P72" s="14" cm="1">
         <f t="array" ref="P72">SUM((1-_xlfn._xlws.FILTER(1/P$20:P$69,(1/P$20:P$69)&lt;&gt;""))^($H72))</f>
-        <v>23.992810344773858</v>
+        <v>24.118807206138069</v>
       </c>
     </row>
   </sheetData>

--- a/catalogue_astronomie.xlsx
+++ b/catalogue_astronomie.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Derfence\Documents\Gatcha\client-android-standalone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8143B11E-62EE-46C9-AAA3-7D6E492D7768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0C60F9-ADB5-499E-B840-E99AB75AE156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogue" sheetId="1" r:id="rId1"/>
@@ -2223,9 +2223,6 @@
     <t>equipment_mount_3</t>
   </si>
   <si>
-    <t>Pousse les tirages vers des cartes plus rares pendant plusieurs packs.</t>
-  </si>
-  <si>
     <t>EquipmentChancePercent</t>
   </si>
   <si>
@@ -2470,6 +2467,9 @@
   </si>
   <si>
     <t>holographicSkyPercent</t>
+  </si>
+  <si>
+    <t>Améliore grandement la probabilité de gagner en rareté.</t>
   </si>
 </sst>
 </file>
@@ -3668,7 +3668,7 @@
         <v>51</v>
       </c>
       <c r="F3" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="G3" t="s">
         <v>52</v>
@@ -3683,7 +3683,7 @@
         <v>54</v>
       </c>
       <c r="K3" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="L3" t="s">
         <v>55</v>
@@ -3734,7 +3734,7 @@
         <v>64</v>
       </c>
       <c r="AB3" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AC3" t="s">
         <v>57</v>
@@ -3835,7 +3835,7 @@
         <v>78</v>
       </c>
       <c r="AB4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AC4" t="s">
         <v>57</v>
@@ -3936,7 +3936,7 @@
         <v>89</v>
       </c>
       <c r="AB5" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="AC5" t="s">
         <v>57</v>
@@ -3971,7 +3971,7 @@
         <v>93</v>
       </c>
       <c r="F6" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G6" t="s">
         <v>52</v>
@@ -3986,7 +3986,7 @@
         <v>54</v>
       </c>
       <c r="K6" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="L6" t="s">
         <v>55</v>
@@ -4037,7 +4037,7 @@
         <v>100</v>
       </c>
       <c r="AB6" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AC6" t="s">
         <v>57</v>
@@ -4072,7 +4072,7 @@
         <v>104</v>
       </c>
       <c r="F7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="G7" t="s">
         <v>52</v>
@@ -4087,7 +4087,7 @@
         <v>54</v>
       </c>
       <c r="K7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="L7" t="s">
         <v>106</v>
@@ -4138,7 +4138,7 @@
         <v>111</v>
       </c>
       <c r="AB7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AC7" t="s">
         <v>15</v>
@@ -4254,7 +4254,7 @@
         <v>124</v>
       </c>
       <c r="AB8" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AC8" t="s">
         <v>57</v>
@@ -4289,7 +4289,7 @@
         <v>127</v>
       </c>
       <c r="F9" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="G9" t="s">
         <v>128</v>
@@ -4304,7 +4304,7 @@
         <v>54</v>
       </c>
       <c r="K9" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="L9" t="s">
         <v>130</v>
@@ -4405,7 +4405,7 @@
         <v>142</v>
       </c>
       <c r="F10" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G10" t="s">
         <v>52</v>
@@ -4420,7 +4420,7 @@
         <v>54</v>
       </c>
       <c r="K10" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="L10" t="s">
         <v>55</v>
@@ -4471,7 +4471,7 @@
         <v>150</v>
       </c>
       <c r="AB10" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AC10" t="s">
         <v>57</v>
@@ -4572,7 +4572,7 @@
         <v>162</v>
       </c>
       <c r="AB11" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AC11" t="s">
         <v>57</v>
@@ -4607,7 +4607,7 @@
         <v>166</v>
       </c>
       <c r="F12" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="G12" t="s">
         <v>52</v>
@@ -4622,7 +4622,7 @@
         <v>54</v>
       </c>
       <c r="K12" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="L12" t="s">
         <v>106</v>
@@ -4673,7 +4673,7 @@
         <v>171</v>
       </c>
       <c r="AB12" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AC12" t="s">
         <v>15</v>
@@ -4857,7 +4857,7 @@
         <v>191</v>
       </c>
       <c r="F14" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G14" t="s">
         <v>128</v>
@@ -4872,7 +4872,7 @@
         <v>54</v>
       </c>
       <c r="K14" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="L14" t="s">
         <v>193</v>
@@ -5056,7 +5056,7 @@
         <v>208</v>
       </c>
       <c r="F16" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="G16" t="s">
         <v>52</v>
@@ -5071,7 +5071,7 @@
         <v>54</v>
       </c>
       <c r="K16" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="L16" t="s">
         <v>210</v>
@@ -5122,7 +5122,7 @@
         <v>215</v>
       </c>
       <c r="AB16" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AC16" t="s">
         <v>180</v>
@@ -5190,7 +5190,7 @@
         <v>222</v>
       </c>
       <c r="F17" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G17" t="s">
         <v>52</v>
@@ -5205,7 +5205,7 @@
         <v>54</v>
       </c>
       <c r="K17" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="L17" t="s">
         <v>106</v>
@@ -5306,7 +5306,7 @@
         <v>231</v>
       </c>
       <c r="F18" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G18" t="s">
         <v>70</v>
@@ -5321,7 +5321,7 @@
         <v>54</v>
       </c>
       <c r="K18" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="L18" t="s">
         <v>233</v>
@@ -5422,7 +5422,7 @@
         <v>241</v>
       </c>
       <c r="F19" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="G19" t="s">
         <v>128</v>
@@ -5437,7 +5437,7 @@
         <v>54</v>
       </c>
       <c r="K19" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="L19" t="s">
         <v>243</v>
@@ -5571,7 +5571,7 @@
         <v>255</v>
       </c>
       <c r="AB20" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AC20" t="s">
         <v>180</v>
@@ -5639,7 +5639,7 @@
         <v>259</v>
       </c>
       <c r="F21" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G21" t="s">
         <v>70</v>
@@ -5654,7 +5654,7 @@
         <v>54</v>
       </c>
       <c r="K21" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="L21" t="s">
         <v>233</v>
@@ -5705,7 +5705,7 @@
         <v>264</v>
       </c>
       <c r="AB21" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AC21" t="s">
         <v>132</v>
@@ -5937,7 +5937,7 @@
         <v>284</v>
       </c>
       <c r="AB23" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AC23" t="s">
         <v>180</v>
@@ -6139,7 +6139,7 @@
         <v>304</v>
       </c>
       <c r="F25" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="G25" t="s">
         <v>305</v>
@@ -6154,7 +6154,7 @@
         <v>54</v>
       </c>
       <c r="K25" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="L25" t="s">
         <v>278</v>
@@ -6205,7 +6205,7 @@
         <v>312</v>
       </c>
       <c r="AB25" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AC25" t="s">
         <v>180</v>
@@ -6273,7 +6273,7 @@
         <v>318</v>
       </c>
       <c r="F26" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G26" t="s">
         <v>305</v>
@@ -6288,7 +6288,7 @@
         <v>54</v>
       </c>
       <c r="K26" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="L26" t="s">
         <v>278</v>
@@ -6339,7 +6339,7 @@
         <v>325</v>
       </c>
       <c r="AB26" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="AC26" t="s">
         <v>180</v>
@@ -6473,7 +6473,7 @@
         <v>336</v>
       </c>
       <c r="AB27" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AC27" t="s">
         <v>180</v>
@@ -6556,7 +6556,7 @@
         <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="L28" t="s">
         <v>278</v>
@@ -6607,7 +6607,7 @@
         <v>348</v>
       </c>
       <c r="AB28" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="AC28" t="s">
         <v>180</v>
@@ -6669,7 +6669,7 @@
         <v>353</v>
       </c>
       <c r="F29" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G29" t="s">
         <v>70</v>
@@ -6684,7 +6684,7 @@
         <v>54</v>
       </c>
       <c r="K29" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="L29" t="s">
         <v>278</v>
@@ -6803,7 +6803,7 @@
         <v>366</v>
       </c>
       <c r="F30" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G30" t="s">
         <v>52</v>
@@ -6818,7 +6818,7 @@
         <v>54</v>
       </c>
       <c r="K30" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="L30" t="s">
         <v>278</v>
@@ -6869,7 +6869,7 @@
         <v>372</v>
       </c>
       <c r="AB30" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AC30" t="s">
         <v>180</v>
@@ -7003,7 +7003,7 @@
         <v>384</v>
       </c>
       <c r="AB31" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AC31" t="s">
         <v>180</v>
@@ -7137,7 +7137,7 @@
         <v>396</v>
       </c>
       <c r="AB32" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="AC32" t="s">
         <v>180</v>
@@ -7271,7 +7271,7 @@
         <v>405</v>
       </c>
       <c r="AB33" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AC33" t="s">
         <v>180</v>
@@ -7405,7 +7405,7 @@
         <v>415</v>
       </c>
       <c r="AB34" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AC34" t="s">
         <v>180</v>
@@ -7607,7 +7607,7 @@
         <v>430</v>
       </c>
       <c r="F36" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="G36" t="s">
         <v>52</v>
@@ -7622,7 +7622,7 @@
         <v>54</v>
       </c>
       <c r="K36" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="L36" t="s">
         <v>278</v>
@@ -7673,7 +7673,7 @@
         <v>436</v>
       </c>
       <c r="AB36" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="AC36" t="s">
         <v>180</v>
@@ -7741,7 +7741,7 @@
         <v>442</v>
       </c>
       <c r="F37" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G37" t="s">
         <v>52</v>
@@ -7756,7 +7756,7 @@
         <v>54</v>
       </c>
       <c r="K37" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="L37" t="s">
         <v>278</v>
@@ -7807,7 +7807,7 @@
         <v>447</v>
       </c>
       <c r="AB37" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AC37" t="s">
         <v>180</v>
@@ -7941,7 +7941,7 @@
         <v>459</v>
       </c>
       <c r="AB38" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AC38" t="s">
         <v>180</v>
@@ -8009,7 +8009,7 @@
         <v>464</v>
       </c>
       <c r="F39" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="G39" t="s">
         <v>305</v>
@@ -8024,7 +8024,7 @@
         <v>54</v>
       </c>
       <c r="K39" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="L39" t="s">
         <v>278</v>
@@ -8209,7 +8209,7 @@
         <v>482</v>
       </c>
       <c r="AB40" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AC40" t="s">
         <v>180</v>
@@ -8292,7 +8292,7 @@
         <v>54</v>
       </c>
       <c r="K41" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="L41" t="s">
         <v>278</v>
@@ -8846,7 +8846,7 @@
         <v>546</v>
       </c>
       <c r="AB45" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="AC45" t="s">
         <v>57</v>
@@ -8881,7 +8881,7 @@
         <v>549</v>
       </c>
       <c r="F46" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="G46" t="s">
         <v>305</v>
@@ -8896,7 +8896,7 @@
         <v>54</v>
       </c>
       <c r="K46" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L46" t="s">
         <v>551</v>
@@ -8947,7 +8947,7 @@
         <v>555</v>
       </c>
       <c r="AB46" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AC46" t="s">
         <v>180</v>
@@ -9131,7 +9131,7 @@
         <v>568</v>
       </c>
       <c r="F48" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G48" t="s">
         <v>52</v>
@@ -9146,7 +9146,7 @@
         <v>54</v>
       </c>
       <c r="K48" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="L48" t="s">
         <v>233</v>
@@ -9197,7 +9197,7 @@
         <v>573</v>
       </c>
       <c r="AB48" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AC48" t="s">
         <v>132</v>
@@ -9247,7 +9247,7 @@
         <v>574</v>
       </c>
       <c r="F49" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G49" t="s">
         <v>52</v>
@@ -9262,7 +9262,7 @@
         <v>54</v>
       </c>
       <c r="K49" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="L49" t="s">
         <v>106</v>
@@ -9363,7 +9363,7 @@
         <v>580</v>
       </c>
       <c r="F50" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="G50" t="s">
         <v>52</v>
@@ -9378,7 +9378,7 @@
         <v>54</v>
       </c>
       <c r="K50" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="L50" t="s">
         <v>55</v>
@@ -9429,7 +9429,7 @@
         <v>588</v>
       </c>
       <c r="AB50" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="AC50" t="s">
         <v>57</v>
@@ -9735,7 +9735,7 @@
         <v>697</v>
       </c>
       <c r="C2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -9756,7 +9756,7 @@
         <v>16</v>
       </c>
       <c r="J2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -9767,7 +9767,7 @@
         <v>697</v>
       </c>
       <c r="C3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -9799,7 +9799,7 @@
         <v>697</v>
       </c>
       <c r="C4" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -9820,7 +9820,7 @@
         <v>4</v>
       </c>
       <c r="J4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -9831,7 +9831,7 @@
         <v>706</v>
       </c>
       <c r="C5" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -9846,13 +9846,13 @@
         <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="I5">
         <v>16</v>
       </c>
       <c r="J5" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -9863,7 +9863,7 @@
         <v>706</v>
       </c>
       <c r="C6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -9878,7 +9878,7 @@
         <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -9895,7 +9895,7 @@
         <v>706</v>
       </c>
       <c r="C7" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -9910,13 +9910,13 @@
         <v>18</v>
       </c>
       <c r="H7" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -9927,7 +9927,7 @@
         <v>714</v>
       </c>
       <c r="C8" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -9948,7 +9948,7 @@
         <v>16</v>
       </c>
       <c r="J8" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -9959,7 +9959,7 @@
         <v>714</v>
       </c>
       <c r="C9" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -9980,7 +9980,7 @@
         <v>10</v>
       </c>
       <c r="J9" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9991,7 +9991,7 @@
         <v>714</v>
       </c>
       <c r="C10" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -10012,7 +10012,7 @@
         <v>4</v>
       </c>
       <c r="J10" t="s">
-        <v>721</v>
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -10097,19 +10097,19 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B10" s="2">
         <f>1/7</f>
         <v>0.14285714285714285</v>
       </c>
       <c r="D10" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B11" s="1">
         <f>D4-B12</f>
@@ -10121,7 +10121,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B12" s="1">
         <f>D11*D4/100</f>
@@ -10219,7 +10219,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -10656,31 +10656,31 @@
         <v>658</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>659</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="M19" s="11" t="s">
         <v>660</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="O19" s="5" t="s">
         <v>661</v>
       </c>
       <c r="P19" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="Q19" s="16" t="s">
         <v>800</v>
       </c>
-      <c r="Q19" s="16" t="s">
+      <c r="R19" s="16" t="s">
         <v>801</v>
-      </c>
-      <c r="R19" s="16" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -10691,7 +10691,7 @@
         <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D20" t="s">
         <v>52</v>
@@ -10901,7 +10901,7 @@
         <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D23" t="s">
         <v>52</v>
@@ -10971,7 +10971,7 @@
         <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D24" t="s">
         <v>52</v>
@@ -11111,7 +11111,7 @@
         <v>127</v>
       </c>
       <c r="C26" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D26" t="s">
         <v>128</v>
@@ -11181,7 +11181,7 @@
         <v>142</v>
       </c>
       <c r="C27" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D27" t="s">
         <v>52</v>
@@ -11321,7 +11321,7 @@
         <v>166</v>
       </c>
       <c r="C29" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D29" t="s">
         <v>52</v>
@@ -11461,7 +11461,7 @@
         <v>191</v>
       </c>
       <c r="C31" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D31" t="s">
         <v>128</v>
@@ -11601,7 +11601,7 @@
         <v>208</v>
       </c>
       <c r="C33" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D33" t="s">
         <v>52</v>
@@ -11671,7 +11671,7 @@
         <v>222</v>
       </c>
       <c r="C34" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D34" t="s">
         <v>52</v>
@@ -11741,7 +11741,7 @@
         <v>231</v>
       </c>
       <c r="C35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D35" t="s">
         <v>70</v>
@@ -11811,7 +11811,7 @@
         <v>241</v>
       </c>
       <c r="C36" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D36" t="s">
         <v>128</v>
@@ -11951,7 +11951,7 @@
         <v>259</v>
       </c>
       <c r="C38" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D38" t="s">
         <v>70</v>
@@ -12231,7 +12231,7 @@
         <v>304</v>
       </c>
       <c r="C42" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D42" t="s">
         <v>305</v>
@@ -12301,7 +12301,7 @@
         <v>318</v>
       </c>
       <c r="C43" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -12511,7 +12511,7 @@
         <v>353</v>
       </c>
       <c r="C46" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D46" t="s">
         <v>70</v>
@@ -12581,7 +12581,7 @@
         <v>366</v>
       </c>
       <c r="C47" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D47" t="s">
         <v>52</v>
@@ -13001,7 +13001,7 @@
         <v>430</v>
       </c>
       <c r="C53" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D53" t="s">
         <v>52</v>
@@ -13071,7 +13071,7 @@
         <v>442</v>
       </c>
       <c r="C54" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D54" t="s">
         <v>52</v>
@@ -13211,7 +13211,7 @@
         <v>464</v>
       </c>
       <c r="C56" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D56" t="s">
         <v>305</v>
@@ -13701,7 +13701,7 @@
         <v>549</v>
       </c>
       <c r="C63" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D63" t="s">
         <v>305</v>
@@ -13841,7 +13841,7 @@
         <v>568</v>
       </c>
       <c r="C65" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D65" t="s">
         <v>52</v>
@@ -13911,7 +13911,7 @@
         <v>574</v>
       </c>
       <c r="C66" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D66" t="s">
         <v>52</v>
@@ -13981,7 +13981,7 @@
         <v>580</v>
       </c>
       <c r="C67" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D67" t="s">
         <v>52</v>

--- a/catalogue_astronomie.xlsx
+++ b/catalogue_astronomie.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Derfence\Documents\Gatcha\client-android-standalone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9107F19A-7CC7-45A9-B6B5-4550501839D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1603081-F129-444F-9E04-C9AB8A503CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogue" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2802" uniqueCount="1192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2876" uniqueCount="1249">
   <si>
     <t>rowType</t>
   </si>
@@ -3634,6 +3634,177 @@
   </si>
   <si>
     <t>~92 km</t>
+  </si>
+  <si>
+    <t>visualMagnitudeValue</t>
+  </si>
+  <si>
+    <t>visualMagnitudeLabel</t>
+  </si>
+  <si>
+    <t>3.08</t>
+  </si>
+  <si>
+    <t>2.12</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>0.76</t>
+  </si>
+  <si>
+    <t>-0.05</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>mag. 0,9 max. 2020</t>
+  </si>
+  <si>
+    <t>3.7 / 3.8</t>
+  </si>
+  <si>
+    <t>mag. 2,1 max. 1986</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>5.8</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>3.44</t>
+  </si>
+  <si>
+    <t>5.72</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>8.8</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>6.94</t>
+  </si>
+  <si>
+    <t>8.41</t>
+  </si>
+  <si>
+    <t>6.53</t>
+  </si>
+  <si>
+    <t>1.85</t>
+  </si>
+  <si>
+    <t>2.02</t>
+  </si>
+  <si>
+    <t>-1.46</t>
+  </si>
+  <si>
+    <t>mag. -2,5 max.</t>
+  </si>
+  <si>
+    <t>mag. 5,4 max.</t>
+  </si>
+  <si>
+    <t>mag. 13,8 max.</t>
+  </si>
+  <si>
+    <t>mag. 16,9 max.</t>
+  </si>
+  <si>
+    <t>mag. 18,4 max.</t>
+  </si>
+  <si>
+    <t>mag. -12,9 max.</t>
+  </si>
+  <si>
+    <t>mag. 11,4 max.</t>
+  </si>
+  <si>
+    <t>mag. 4,8 max.</t>
+  </si>
+  <si>
+    <t>mag. 5,1 max.</t>
+  </si>
+  <si>
+    <t>mag. 4,4 max.</t>
+  </si>
+  <si>
+    <t>mag. 5,5 max.</t>
+  </si>
+  <si>
+    <t>mag. 8,1 max.</t>
+  </si>
+  <si>
+    <t>mag. 11,5 max.</t>
+  </si>
+  <si>
+    <t>mag. 12,6 max.</t>
+  </si>
+  <si>
+    <t>mag. 9,4 max.</t>
+  </si>
+  <si>
+    <t>mag. 10,1 max.</t>
+  </si>
+  <si>
+    <t>mag. 10,0 max.</t>
+  </si>
+  <si>
+    <t>mag. 10,8 max.</t>
+  </si>
+  <si>
+    <t>mag. 16,1 max.</t>
+  </si>
+  <si>
+    <t>mag. 14,0 max.</t>
+  </si>
+  <si>
+    <t>mag. 14,6 max.</t>
+  </si>
+  <si>
+    <t>mag. 13,4 max.</t>
   </si>
 </sst>
 </file>
@@ -4245,9 +4416,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{766E9171-3232-47EC-BA2E-778CC8804D8D}" name="Table1" displayName="Table1" ref="A1:AT101" totalsRowShown="0">
-  <autoFilter ref="A1:AT101" xr:uid="{766E9171-3232-47EC-BA2E-778CC8804D8D}"/>
-  <tableColumns count="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{766E9171-3232-47EC-BA2E-778CC8804D8D}" name="Table1" displayName="Table1" ref="A1:AV101" totalsRowShown="0">
+  <autoFilter ref="A1:AV101" xr:uid="{766E9171-3232-47EC-BA2E-778CC8804D8D}"/>
+  <tableColumns count="48">
     <tableColumn id="1" xr3:uid="{CF26DF04-235C-4543-9468-CBFEC3C5D050}" name="rowType"/>
     <tableColumn id="2" xr3:uid="{ADA284B2-47B5-4993-B053-72939A7D8D1D}" name="extensionId"/>
     <tableColumn id="3" xr3:uid="{1116EFE8-A680-430E-9CE0-9643A53DFCD5}" name="extensionName"/>
@@ -4294,6 +4465,8 @@
     <tableColumn id="44" xr3:uid="{BBDD5EAF-BDA3-42CC-BB76-59426B03E62C}" name="visualSizeLabel"/>
     <tableColumn id="45" xr3:uid="{00D5AC37-AA0E-4F87-88F6-5922E20A5912}" name="absoluteMagnitudeValue"/>
     <tableColumn id="46" xr3:uid="{DEEBB93F-0947-4A72-B1B6-E9094EB4A9CB}" name="absoluteMagnitudeLabel"/>
+    <tableColumn id="47" xr3:uid="{036DD14B-8E3C-4671-9BF6-20524CAAEB77}" name="visualMagnitudeValue"/>
+    <tableColumn id="48" xr3:uid="{9A5A1026-77D3-4A0E-826F-537EB719245D}" name="visualMagnitudeLabel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4616,51 +4789,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AT101"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AV101"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.453125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="33.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.1796875" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="3" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.26953125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="2" bestFit="1" customWidth="1"/>
     <col min="23" max="25" width="3" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="136.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="31.7265625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="136.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="9" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="24.54296875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="25.26953125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="7" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="6" bestFit="1" customWidth="1"/>
     <col min="36" max="38" width="3" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="40" max="42" width="3" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="33.1796875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="5.7265625" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4799,8 +4972,14 @@
       <c r="AT1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -4814,7 +4993,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -4914,8 +5093,14 @@
       <c r="AT3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU3">
+        <v>3.08</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="4" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>50</v>
       </c>
@@ -5015,8 +5200,14 @@
       <c r="AT4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU4">
+        <v>2.12</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -5116,8 +5307,14 @@
       <c r="AT5" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU5">
+        <v>2.1</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>50</v>
       </c>
@@ -5217,8 +5414,14 @@
       <c r="AT6" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU6">
+        <v>0.76</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -5334,7 +5537,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>50</v>
       </c>
@@ -5434,8 +5637,14 @@
       <c r="AT8" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU8">
+        <v>-0.05</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -5551,7 +5760,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -5651,8 +5860,14 @@
       <c r="AT10" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU10">
+        <v>0.42</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -5752,8 +5967,14 @@
       <c r="AT11" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU11">
+        <v>0.08</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -5869,7 +6090,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -6002,8 +6223,14 @@
       <c r="AT13" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU13">
+        <v>3.6</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="14" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -6085,8 +6312,14 @@
       <c r="AC14" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU14">
+        <v>0.9</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="15" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>50</v>
       </c>
@@ -6202,7 +6435,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>50</v>
       </c>
@@ -6335,8 +6568,14 @@
       <c r="AT16" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="17" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU16">
+        <v>3.7</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="17" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -6452,7 +6691,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="18" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -6568,7 +6807,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="19" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -6650,8 +6889,14 @@
       <c r="AC19" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="20" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU19">
+        <v>2.1</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="20" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -6784,8 +7029,14 @@
       <c r="AT20" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="21" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU20">
+        <v>0.5</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="21" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -6901,7 +7152,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="22" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -7017,7 +7268,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="23" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -7150,8 +7401,14 @@
       <c r="AT23" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="24" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU23">
+        <v>5.8</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="24" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -7284,8 +7541,14 @@
       <c r="AT24" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="25" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU24">
+        <v>5.8</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="25" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -7418,8 +7681,14 @@
       <c r="AT25" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="26" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU25">
+        <v>6.4</v>
+      </c>
+      <c r="AV25" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="26" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -7552,8 +7821,14 @@
       <c r="AT26" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="27" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU26">
+        <v>6</v>
+      </c>
+      <c r="AV26" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="27" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>50</v>
       </c>
@@ -7686,8 +7961,14 @@
       <c r="AT27" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="28" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU27">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AV27" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="28" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -7814,8 +8095,14 @@
       <c r="AR28" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="29" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU28">
+        <v>2.5</v>
+      </c>
+      <c r="AV28" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="29" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -7948,8 +8235,14 @@
       <c r="AT29" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="30" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU29">
+        <v>7.4</v>
+      </c>
+      <c r="AV29" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="30" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>50</v>
       </c>
@@ -8082,8 +8375,14 @@
       <c r="AT30" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="31" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU30">
+        <v>3.44</v>
+      </c>
+      <c r="AV30" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="31" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -8216,8 +8515,14 @@
       <c r="AT31" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="32" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU31">
+        <v>5.72</v>
+      </c>
+      <c r="AV31" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="32" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>50</v>
       </c>
@@ -8350,8 +8655,14 @@
       <c r="AT32" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="33" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU32">
+        <v>6.2</v>
+      </c>
+      <c r="AV32" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="33" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -8484,8 +8795,14 @@
       <c r="AT33" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="34" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU33">
+        <v>7.4</v>
+      </c>
+      <c r="AV33" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="34" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -8618,8 +8935,14 @@
       <c r="AT34" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="35" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU34">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AV34" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="35" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -8752,8 +9075,14 @@
       <c r="AT35" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="36" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU35">
+        <v>4.5</v>
+      </c>
+      <c r="AV35" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="36" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -8886,8 +9215,14 @@
       <c r="AT36" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="37" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU36">
+        <v>4</v>
+      </c>
+      <c r="AV36" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="37" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -9020,8 +9355,14 @@
       <c r="AT37" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="38" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU37">
+        <v>1.6</v>
+      </c>
+      <c r="AV37" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="38" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>50</v>
       </c>
@@ -9154,8 +9495,14 @@
       <c r="AT38" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="39" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU38">
+        <v>6</v>
+      </c>
+      <c r="AV38" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="39" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -9288,8 +9635,14 @@
       <c r="AT39" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="40" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU39">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AV39" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="40" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -9422,8 +9775,14 @@
       <c r="AT40" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="41" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU40">
+        <v>4.2</v>
+      </c>
+      <c r="AV40" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="41" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -9556,8 +9915,14 @@
       <c r="AT41" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="42" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU41">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AV41" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="42" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -9690,8 +10055,14 @@
       <c r="AT42" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="43" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU42">
+        <v>6.94</v>
+      </c>
+      <c r="AV42" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="43" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -9824,8 +10195,14 @@
       <c r="AT43" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="44" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU43">
+        <v>8.41</v>
+      </c>
+      <c r="AV43" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="44" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>50</v>
       </c>
@@ -9925,8 +10302,14 @@
       <c r="AT44" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="45" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU44">
+        <v>6.53</v>
+      </c>
+      <c r="AV44" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="45" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -10026,8 +10409,14 @@
       <c r="AT45" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="46" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU45">
+        <v>1.85</v>
+      </c>
+      <c r="AV45" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="46" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -10160,8 +10549,14 @@
       <c r="AT46" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="47" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU46">
+        <v>4</v>
+      </c>
+      <c r="AV46" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="47" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -10277,7 +10672,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="48" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -10393,7 +10788,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="49" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -10509,7 +10904,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="50" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -10609,8 +11004,14 @@
       <c r="AT50" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="51" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU50">
+        <v>2.02</v>
+      </c>
+      <c r="AV50" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="51" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -10710,8 +11111,14 @@
       <c r="AT51" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="52" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU51">
+        <v>-1.46</v>
+      </c>
+      <c r="AV51" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="52" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -10827,7 +11234,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="53" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>46</v>
       </c>
@@ -10841,7 +11248,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="54" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>50</v>
       </c>
@@ -10920,8 +11327,14 @@
       <c r="AT54" t="s">
         <v>1027</v>
       </c>
-    </row>
-    <row r="55" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU54">
+        <v>-2.5</v>
+      </c>
+      <c r="AV54" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="55" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -11000,8 +11413,14 @@
       <c r="AT55" t="s">
         <v>1031</v>
       </c>
-    </row>
-    <row r="56" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU55">
+        <v>-4.9000000000000004</v>
+      </c>
+      <c r="AV55" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="56" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>50</v>
       </c>
@@ -11075,7 +11494,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="57" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>50</v>
       </c>
@@ -11154,8 +11573,14 @@
       <c r="AT57" t="s">
         <v>1038</v>
       </c>
-    </row>
-    <row r="58" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU57">
+        <v>-2.9</v>
+      </c>
+      <c r="AV57" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="58" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>50</v>
       </c>
@@ -11234,8 +11659,14 @@
       <c r="AT58" t="s">
         <v>1038</v>
       </c>
-    </row>
-    <row r="59" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU58">
+        <v>-2.9</v>
+      </c>
+      <c r="AV58" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="59" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>50</v>
       </c>
@@ -11314,8 +11745,14 @@
       <c r="AT59" t="s">
         <v>1045</v>
       </c>
-    </row>
-    <row r="60" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU59">
+        <v>-0.5</v>
+      </c>
+      <c r="AV59" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="60" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>50</v>
       </c>
@@ -11394,8 +11831,14 @@
       <c r="AT60" t="s">
         <v>1049</v>
       </c>
-    </row>
-    <row r="61" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU60">
+        <v>5.4</v>
+      </c>
+      <c r="AV60" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="61" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>50</v>
       </c>
@@ -11474,8 +11917,14 @@
       <c r="AT61" t="s">
         <v>1053</v>
       </c>
-    </row>
-    <row r="62" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU61">
+        <v>7.7</v>
+      </c>
+      <c r="AV61" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="62" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>50</v>
       </c>
@@ -11554,8 +12003,14 @@
       <c r="AT62" t="s">
         <v>1057</v>
       </c>
-    </row>
-    <row r="63" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU62">
+        <v>6.7</v>
+      </c>
+      <c r="AV62" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="63" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>50</v>
       </c>
@@ -11634,8 +12089,14 @@
       <c r="AT63" t="s">
         <v>1061</v>
       </c>
-    </row>
-    <row r="64" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU63">
+        <v>13.8</v>
+      </c>
+      <c r="AV63" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="64" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>50</v>
       </c>
@@ -11714,8 +12175,14 @@
       <c r="AT64" t="s">
         <v>1065</v>
       </c>
-    </row>
-    <row r="65" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU64">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="AV64" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="65" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>50</v>
       </c>
@@ -11794,8 +12261,14 @@
       <c r="AT65" t="s">
         <v>1069</v>
       </c>
-    </row>
-    <row r="66" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU65">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="AV65" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="66" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>50</v>
       </c>
@@ -11874,8 +12347,14 @@
       <c r="AT66" t="s">
         <v>1073</v>
       </c>
-    </row>
-    <row r="67" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU66">
+        <v>-12.9</v>
+      </c>
+      <c r="AV66" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="67" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>50</v>
       </c>
@@ -11954,8 +12433,14 @@
       <c r="AT67" t="s">
         <v>1077</v>
       </c>
-    </row>
-    <row r="68" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU67">
+        <v>10.4</v>
+      </c>
+      <c r="AV67" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="68" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>50</v>
       </c>
@@ -12034,8 +12519,14 @@
       <c r="AT68" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="69" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU68">
+        <v>11.4</v>
+      </c>
+      <c r="AV68" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="69" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>50</v>
       </c>
@@ -12114,8 +12605,14 @@
       <c r="AT69" t="s">
         <v>1085</v>
       </c>
-    </row>
-    <row r="70" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU69">
+        <v>4.8</v>
+      </c>
+      <c r="AV69" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="70" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>50</v>
       </c>
@@ -12194,8 +12691,14 @@
       <c r="AT70" t="s">
         <v>1049</v>
       </c>
-    </row>
-    <row r="71" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU70">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AV70" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="71" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>50</v>
       </c>
@@ -12274,8 +12777,14 @@
       <c r="AT71" t="s">
         <v>1092</v>
       </c>
-    </row>
-    <row r="72" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU71">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AV71" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="72" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>50</v>
       </c>
@@ -12354,8 +12863,14 @@
       <c r="AT72" t="s">
         <v>1096</v>
       </c>
-    </row>
-    <row r="73" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU72">
+        <v>5.5</v>
+      </c>
+      <c r="AV72" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="73" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>50</v>
       </c>
@@ -12434,8 +12949,14 @@
       <c r="AT73" t="s">
         <v>1100</v>
       </c>
-    </row>
-    <row r="74" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU73">
+        <v>8.1</v>
+      </c>
+      <c r="AV73" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="74" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>50</v>
       </c>
@@ -12514,8 +13035,14 @@
       <c r="AT74" t="s">
         <v>1104</v>
       </c>
-    </row>
-    <row r="75" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU74">
+        <v>11.5</v>
+      </c>
+      <c r="AV74" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="75" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>50</v>
       </c>
@@ -12594,8 +13121,14 @@
       <c r="AT75" t="s">
         <v>1108</v>
       </c>
-    </row>
-    <row r="76" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU75">
+        <v>12.6</v>
+      </c>
+      <c r="AV75" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="76" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>50</v>
       </c>
@@ -12674,8 +13207,14 @@
       <c r="AT76" t="s">
         <v>1112</v>
       </c>
-    </row>
-    <row r="77" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU76">
+        <v>9.4</v>
+      </c>
+      <c r="AV76" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="77" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>50</v>
       </c>
@@ -12754,8 +13293,14 @@
       <c r="AT77" t="s">
         <v>1116</v>
       </c>
-    </row>
-    <row r="78" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU77">
+        <v>10.1</v>
+      </c>
+      <c r="AV77" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="78" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>50</v>
       </c>
@@ -12834,8 +13379,14 @@
       <c r="AT78" t="s">
         <v>1120</v>
       </c>
-    </row>
-    <row r="79" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU78">
+        <v>10</v>
+      </c>
+      <c r="AV78" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="79" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>50</v>
       </c>
@@ -12914,8 +13465,14 @@
       <c r="AT79" t="s">
         <v>1120</v>
       </c>
-    </row>
-    <row r="80" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU79">
+        <v>10.8</v>
+      </c>
+      <c r="AV79" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="80" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>50</v>
       </c>
@@ -12994,8 +13551,14 @@
       <c r="AT80" t="s">
         <v>1127</v>
       </c>
-    </row>
-    <row r="81" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU80">
+        <v>14.1</v>
+      </c>
+      <c r="AV80" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="81" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>50</v>
       </c>
@@ -13074,8 +13637,14 @@
       <c r="AT81" t="s">
         <v>1131</v>
       </c>
-    </row>
-    <row r="82" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU81">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="AV81" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="82" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>50</v>
       </c>
@@ -13154,8 +13723,14 @@
       <c r="AT82" t="s">
         <v>1135</v>
       </c>
-    </row>
-    <row r="83" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU82">
+        <v>13.5</v>
+      </c>
+      <c r="AV82" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="83" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>50</v>
       </c>
@@ -13234,8 +13809,14 @@
       <c r="AT83" t="s">
         <v>1127</v>
       </c>
-    </row>
-    <row r="84" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU83">
+        <v>14</v>
+      </c>
+      <c r="AV83" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="84" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>50</v>
       </c>
@@ -13314,8 +13895,14 @@
       <c r="AT84" t="s">
         <v>1142</v>
       </c>
-    </row>
-    <row r="85" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU84">
+        <v>14.6</v>
+      </c>
+      <c r="AV84" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="85" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>50</v>
       </c>
@@ -13394,8 +13981,14 @@
       <c r="AT85" t="s">
         <v>1146</v>
       </c>
-    </row>
-    <row r="86" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU85">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="AV85" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="86" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>50</v>
       </c>
@@ -13474,8 +14067,14 @@
       <c r="AT86" t="s">
         <v>1150</v>
       </c>
-    </row>
-    <row r="87" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU86">
+        <v>13.4</v>
+      </c>
+      <c r="AV86" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="87" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>50</v>
       </c>
@@ -13554,8 +14153,14 @@
       <c r="AT87" t="s">
         <v>1069</v>
       </c>
-    </row>
-    <row r="88" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU87">
+        <v>18.7</v>
+      </c>
+      <c r="AV87" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="88" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>50</v>
       </c>
@@ -13634,8 +14239,14 @@
       <c r="AT88" t="s">
         <v>1157</v>
       </c>
-    </row>
-    <row r="89" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU88">
+        <v>13.9</v>
+      </c>
+      <c r="AV88" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="89" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>50</v>
       </c>
@@ -13706,7 +14317,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="90" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>50</v>
       </c>
@@ -13777,7 +14388,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="91" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>50</v>
       </c>
@@ -13848,7 +14459,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="92" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>50</v>
       </c>
@@ -13919,7 +14530,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="93" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>50</v>
       </c>
@@ -13990,7 +14601,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="94" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>50</v>
       </c>
@@ -14061,7 +14672,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="95" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>50</v>
       </c>
@@ -14132,7 +14743,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="96" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>50</v>
       </c>
@@ -14203,7 +14814,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="97" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>50</v>
       </c>
@@ -14274,7 +14885,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="98" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>50</v>
       </c>
@@ -14345,7 +14956,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="99" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>50</v>
       </c>
@@ -14416,7 +15027,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="100" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>50</v>
       </c>
@@ -14487,7 +15098,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="101" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>50</v>
       </c>
@@ -14569,21 +15180,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D42EB6-033C-42BF-9E1D-DED894C3BFBF}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="64.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="64.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>687</v>
       </c>
@@ -14615,7 +15226,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>696</v>
       </c>
@@ -14647,7 +15258,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>700</v>
       </c>
@@ -14679,7 +15290,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>703</v>
       </c>
@@ -14711,7 +15322,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>705</v>
       </c>
@@ -14743,7 +15354,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>708</v>
       </c>
@@ -14775,7 +15386,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>711</v>
       </c>
@@ -14807,7 +15418,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>713</v>
       </c>
@@ -14839,7 +15450,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>717</v>
       </c>
@@ -14871,7 +15482,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>719</v>
       </c>
@@ -14911,23 +15522,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" customWidth="1"/>
-    <col min="7" max="7" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" customWidth="1"/>
+    <col min="4" max="4" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.453125" customWidth="1"/>
+    <col min="7" max="7" width="24.81640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>612</v>
       </c>
@@ -14938,7 +15549,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>613</v>
       </c>
@@ -14950,7 +15561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>646</v>
       </c>
@@ -14959,7 +15570,7 @@
         <v>9.8571428571428577</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>647</v>
       </c>
@@ -14967,7 +15578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>648</v>
       </c>
@@ -14975,7 +15586,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>649</v>
       </c>
@@ -14983,7 +15594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>795</v>
       </c>
@@ -14995,7 +15606,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>794</v>
       </c>
@@ -15007,7 +15618,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>793</v>
       </c>
@@ -15016,7 +15627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>650</v>
       </c>
@@ -15039,7 +15650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>651</v>
       </c>
@@ -15061,7 +15672,7 @@
         <v>1.6666666666666667</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>652</v>
       </c>
@@ -15083,7 +15694,7 @@
         <v>3.3333333333333335</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>653</v>
       </c>
@@ -15105,7 +15716,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>721</v>
       </c>
@@ -15121,35 +15732,35 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R121"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.54296875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -15175,7 +15786,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>54</v>
       </c>
@@ -15205,7 +15816,7 @@
         <v>0.10144927536231883</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -15235,7 +15846,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -15265,7 +15876,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>54</v>
       </c>
@@ -15295,7 +15906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -15325,7 +15936,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -15355,7 +15966,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -15385,12 +15996,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -15410,7 +16021,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -15435,7 +16046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -15460,7 +16071,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>305</v>
       </c>
@@ -15485,7 +16096,7 @@
         <v>2.9999999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>128</v>
       </c>
@@ -15510,12 +16121,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -15571,7 +16182,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -15641,7 +16252,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -15711,7 +16322,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -15781,7 +16392,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -15851,7 +16462,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -15921,7 +16532,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -15991,7 +16602,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -16061,7 +16672,7 @@
         <v>11129.322066265169</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>47</v>
       </c>
@@ -16131,7 +16742,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -16201,7 +16812,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>47</v>
       </c>
@@ -16271,7 +16882,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>47</v>
       </c>
@@ -16341,7 +16952,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>47</v>
       </c>
@@ -16411,7 +17022,7 @@
         <v>11129.322066265169</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>47</v>
       </c>
@@ -16481,7 +17092,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -16551,7 +17162,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -16621,7 +17232,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>47</v>
       </c>
@@ -16691,7 +17302,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>47</v>
       </c>
@@ -16761,7 +17372,7 @@
         <v>11129.322066265169</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>47</v>
       </c>
@@ -16831,7 +17442,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>47</v>
       </c>
@@ -16901,7 +17512,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -16971,7 +17582,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -17041,7 +17652,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>47</v>
       </c>
@@ -17111,7 +17722,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -17181,7 +17792,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -17251,7 +17862,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -17321,7 +17932,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -17391,7 +18002,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -17461,7 +18072,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -17531,7 +18142,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -17601,7 +18212,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -17671,7 +18282,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>47</v>
       </c>
@@ -17741,7 +18352,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>47</v>
       </c>
@@ -17811,7 +18422,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>47</v>
       </c>
@@ -17881,7 +18492,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>47</v>
       </c>
@@ -17951,7 +18562,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -18021,7 +18632,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>47</v>
       </c>
@@ -18091,7 +18702,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>47</v>
       </c>
@@ -18161,7 +18772,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>47</v>
       </c>
@@ -18231,7 +18842,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>47</v>
       </c>
@@ -18301,7 +18912,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>47</v>
       </c>
@@ -18371,7 +18982,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>47</v>
       </c>
@@ -18441,7 +19052,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>47</v>
       </c>
@@ -18511,7 +19122,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>47</v>
       </c>
@@ -18581,7 +19192,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>47</v>
       </c>
@@ -18651,7 +19262,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>47</v>
       </c>
@@ -18721,7 +19332,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>47</v>
       </c>
@@ -18791,7 +19402,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>47</v>
       </c>
@@ -18861,7 +19472,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>47</v>
       </c>
@@ -18931,7 +19542,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>47</v>
       </c>
@@ -19001,7 +19612,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>47</v>
       </c>
@@ -19071,7 +19682,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
         <v>962</v>
       </c>
@@ -19138,7 +19749,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
         <v>963</v>
       </c>
@@ -19205,7 +19816,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
         <v>964</v>
       </c>
@@ -19272,7 +19883,7 @@
         <v>11129.322066265169</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
         <v>965</v>
       </c>
@@ -19339,7 +19950,7 @@
         <v>11129.322066265169</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
         <v>966</v>
       </c>
@@ -19406,7 +20017,7 @@
         <v>11129.322066265169</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
         <v>967</v>
       </c>
@@ -19473,7 +20084,7 @@
         <v>11129.322066265169</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
         <v>968</v>
       </c>
@@ -19540,7 +20151,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>969</v>
       </c>
@@ -19607,7 +20218,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
         <v>970</v>
       </c>
@@ -19674,7 +20285,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>971</v>
       </c>
@@ -19741,7 +20352,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>972</v>
       </c>
@@ -19808,7 +20419,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="81" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>973</v>
       </c>
@@ -19875,7 +20486,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="82" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>974</v>
       </c>
@@ -19942,7 +20553,7 @@
         <v>11129.322066265169</v>
       </c>
     </row>
-    <row r="83" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
         <v>975</v>
       </c>
@@ -20009,7 +20620,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="84" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>976</v>
       </c>
@@ -20076,7 +20687,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="85" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>977</v>
       </c>
@@ -20143,7 +20754,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="86" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>978</v>
       </c>
@@ -20210,7 +20821,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="87" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>979</v>
       </c>
@@ -20277,7 +20888,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="88" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>980</v>
       </c>
@@ -20344,7 +20955,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="89" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>981</v>
       </c>
@@ -20411,7 +21022,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="90" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
         <v>982</v>
       </c>
@@ -20478,7 +21089,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="91" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
         <v>983</v>
       </c>
@@ -20545,7 +21156,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="92" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
         <v>984</v>
       </c>
@@ -20612,7 +21223,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="93" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
         <v>985</v>
       </c>
@@ -20679,7 +21290,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="94" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
         <v>986</v>
       </c>
@@ -20746,7 +21357,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="95" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
         <v>987</v>
       </c>
@@ -20813,7 +21424,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="96" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
         <v>988</v>
       </c>
@@ -20880,7 +21491,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="97" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
         <v>989</v>
       </c>
@@ -20947,7 +21558,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="98" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
         <v>990</v>
       </c>
@@ -21014,7 +21625,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="99" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
         <v>991</v>
       </c>
@@ -21081,7 +21692,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="100" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
         <v>992</v>
       </c>
@@ -21148,7 +21759,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="101" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
         <v>993</v>
       </c>
@@ -21215,7 +21826,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="102" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
         <v>994</v>
       </c>
@@ -21282,7 +21893,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="103" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
         <v>995</v>
       </c>
@@ -21349,7 +21960,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="104" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
         <v>996</v>
       </c>
@@ -21416,7 +22027,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="105" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
         <v>997</v>
       </c>
@@ -21483,7 +22094,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="106" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
         <v>998</v>
       </c>
@@ -21550,7 +22161,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="107" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
         <v>999</v>
       </c>
@@ -21617,7 +22228,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="108" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
         <v>1015</v>
       </c>
@@ -21684,7 +22295,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="109" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
         <v>1000</v>
       </c>
@@ -21751,7 +22362,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="110" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
         <v>1001</v>
       </c>
@@ -21818,7 +22429,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="111" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B111" t="s">
         <v>1002</v>
       </c>
@@ -21885,7 +22496,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="112" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
         <v>1003</v>
       </c>
@@ -21952,7 +22563,7 @@
         <v>5796.7495240968374</v>
       </c>
     </row>
-    <row r="113" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
         <v>1004</v>
       </c>
@@ -22019,7 +22630,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="114" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
         <v>1005</v>
       </c>
@@ -22086,7 +22697,7 @@
         <v>7883.4083438508196</v>
       </c>
     </row>
-    <row r="115" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B115" t="s">
         <v>1006</v>
       </c>
@@ -22153,7 +22764,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="116" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
         <v>1007</v>
       </c>
@@ -22168,7 +22779,7 @@
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="F116" s="3">
-        <f t="shared" ref="F116:F147" si="8">E116/$E$118</f>
+        <f t="shared" ref="F116:F117" si="8">E116/$E$118</f>
         <v>1.0483266240429404E-2</v>
       </c>
       <c r="G116" s="3">
@@ -22220,7 +22831,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="117" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
         <v>1008</v>
       </c>
@@ -22287,7 +22898,7 @@
         <v>6677.7832477698757</v>
       </c>
     </row>
-    <row r="118" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:18" x14ac:dyDescent="0.35">
       <c r="E118" s="4">
         <f>SUM(E20:E117)</f>
         <v>0.99364705882352855</v>
@@ -22299,7 +22910,7 @@
       <c r="G118" s="3"/>
       <c r="H118" s="3"/>
     </row>
-    <row r="119" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:18" x14ac:dyDescent="0.35">
       <c r="G119" s="15"/>
       <c r="H119" s="13">
         <v>30</v>
@@ -22345,7 +22956,7 @@
         <v>97.572384699567749</v>
       </c>
     </row>
-    <row r="120" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:18" x14ac:dyDescent="0.35">
       <c r="H120" s="13">
         <v>365</v>
       </c>
@@ -22390,7 +23001,7 @@
         <v>92.925091763287085</v>
       </c>
     </row>
-    <row r="121" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:18" x14ac:dyDescent="0.35">
       <c r="H121" s="13">
         <v>1200</v>
       </c>
